--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BH16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="n">
         <v>2.34</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
@@ -1154,10 +1154,10 @@
         <v>2.16</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>2.16</v>
+        <v>3.9</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>3.65</v>
       </c>
       <c r="G5" t="n">
-        <v>2.64</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1.61</v>
+        <v>2.32</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="n">
-        <v>3.85</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>2.54</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.76</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,61 +1718,61 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.96</v>
+        <v>3.65</v>
       </c>
       <c r="G7" t="n">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="H7" t="n">
-        <v>3.75</v>
+        <v>2.28</v>
       </c>
       <c r="I7" t="n">
-        <v>5.8</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1781,123 +1781,123 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,66 +1907,66 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.65</v>
+        <v>2.46</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="J8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S8" t="n">
         <v>3.4</v>
       </c>
-      <c r="K8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.96</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>2.26</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AB8" t="n">
         <v>12</v>
@@ -1993,105 +1993,105 @@
         <v>7.6</v>
       </c>
       <c r="AD8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG8" t="n">
         <v>12</v>
       </c>
-      <c r="AE8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ8" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AK8" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AN8" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AS8" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="AT8" t="n">
         <v>10.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY8" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX8" t="n">
+      <c r="AZ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC8" t="n">
         <v>21</v>
       </c>
-      <c r="AY8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>26</v>
-      </c>
       <c r="BD8" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="BF8" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="BG8" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,66 +2101,66 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="I9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.25</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>1.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.96</v>
+        <v>2.48</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2169,116 +2169,116 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
@@ -2300,32 +2300,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.96</v>
       </c>
-      <c r="G10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>18:15:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18:15:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>2.46</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="H13" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>2.72</v>
       </c>
       <c r="K13" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
@@ -3076,28 +3076,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45</v>
+        <v>1.96</v>
       </c>
       <c r="H14" t="n">
-        <v>3.05</v>
+        <v>2.04</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="K14" t="n">
         <v>1000</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,42 +3265,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="G15" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="H15" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.04</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,42 +3459,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,201 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-18 02:13:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Paraguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Club Sportivo Ameliano</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Nacional (Par)</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2026-04-18 02:13:36</t>
+          <t>2026-04-18 04:46:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH16"/>
+  <dimension ref="A1:BH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Gornik Leczna</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="G3" t="n">
-        <v>2.34</v>
+        <v>1.91</v>
       </c>
       <c r="H3" t="n">
-        <v>3.45</v>
+        <v>2.14</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1136,31 +1136,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.59</v>
+        <v>2.24</v>
       </c>
       <c r="G4" t="n">
-        <v>1.86</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>2.16</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>9.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.44</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.65</v>
+        <v>1.59</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>1.86</v>
       </c>
       <c r="H5" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,66 +1713,66 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.65</v>
       </c>
-      <c r="G7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1781,123 +1781,123 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,66 +1907,66 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.46</v>
+        <v>1.97</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="I8" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="Q8" t="n">
         <v>1.96</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1975,123 +1975,123 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,66 +2101,66 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="H9" t="n">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>2.94</v>
+        <v>2.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N9" t="n">
         <v>3.25</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P9" t="n">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2169,123 +2169,123 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,66 +2295,66 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H10" t="n">
         <v>3.15</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.55</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.96</v>
-      </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>1.37</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,123 +2363,123 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:15:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:15:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1.96</v>
+        <v>3.7</v>
       </c>
       <c r="H14" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="J14" t="n">
-        <v>2.04</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,42 +3265,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.76</v>
+        <v>2.46</v>
       </c>
       <c r="G15" t="n">
-        <v>1.86</v>
+        <v>2.82</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>2.72</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>1.37</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.98</v>
+        <v>2.42</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,201 +3442,589 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-18 04:46:10</t>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Maringa</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Brusque FC</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I17" t="n">
+        <v>11</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>950</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:18:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Club Sportivo Ameliano</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Nacional (Par)</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q18" t="n">
         <v>1.01</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>2026-04-18 04:46:10</t>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-18 07:18:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.75</v>
+        <v>980</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="K4" t="n">
         <v>3.55</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="G7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>3.75</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -1954,7 +1954,7 @@
         <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I9" t="n">
         <v>2.28</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.3</v>
       </c>
       <c r="J9" t="n">
         <v>3.45</v>
@@ -2139,28 +2139,28 @@
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
         <v>1.42</v>
       </c>
       <c r="P9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q9" t="n">
         <v>2.24</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
         <v>4.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2172,13 +2172,13 @@
         <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
         <v>1000</v>
@@ -2187,7 +2187,7 @@
         <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2199,7 +2199,7 @@
         <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2238,7 +2238,7 @@
         <v>10</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
         <v>10</v>
@@ -2253,32 +2253,32 @@
         <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF9" t="n">
         <v>5</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
         <v>16</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>2.5</v>
       </c>
       <c r="H10" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
         <v>3.25</v>
@@ -2324,7 +2324,7 @@
         <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2363,16 +2363,16 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
         <v>12</v>
@@ -2393,10 +2393,10 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AJ10" t="n">
         <v>32</v>
@@ -2405,31 +2405,31 @@
         <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM10" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU10" t="n">
         <v>7.2</v>
@@ -2441,7 +2441,7 @@
         <v>29</v>
       </c>
       <c r="AX10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY10" t="n">
         <v>10.5</v>
@@ -2450,29 +2450,29 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE10" t="n">
         <v>55</v>
       </c>
       <c r="BF10" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BG10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.15</v>
+        <v>2.84</v>
       </c>
       <c r="G12" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="H12" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="K12" t="n">
         <v>2.96</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I14" t="n">
         <v>2.88</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -3670,25 +3670,25 @@
         <v>1.63</v>
       </c>
       <c r="G17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H17" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-18 07:18:45</t>
+          <t>2026-04-18 09:51:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>Botosani</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MAS Taborsko</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="G2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3</v>
+      </c>
+      <c r="X2" t="n">
         <v>1000</v>
       </c>
-      <c r="H2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="Y2" t="n">
         <v>1000</v>
       </c>
-      <c r="J2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="Z2" t="n">
         <v>1000</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF2" t="n">
         <v>1.01</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,33 +937,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gornik Leczna</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>2.16</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.16</v>
+        <v>1.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Gornik Leczna</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>1.55</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>2.14</v>
       </c>
       <c r="I4" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.98</v>
+        <v>2.16</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1330,31 +1330,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.59</v>
+        <v>2.26</v>
       </c>
       <c r="G5" t="n">
-        <v>1.86</v>
+        <v>2.32</v>
       </c>
       <c r="H5" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>1.59</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.35</v>
+        <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="I7" t="n">
-        <v>2.58</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.36</v>
+        <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>3.75</v>
+        <v>1.68</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>2.04</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,11 +1951,11 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.64</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.98</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,66 +2101,66 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Leixoes</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -2169,123 +2169,123 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,66 +2295,66 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.46</v>
+        <v>3.65</v>
       </c>
       <c r="G10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I10" t="n">
         <v>2.5</v>
       </c>
-      <c r="H10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.25</v>
-      </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,123 +2363,123 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,66 +2489,66 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.96</v>
+        <v>3.65</v>
       </c>
       <c r="G11" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="H11" t="n">
-        <v>2.78</v>
+        <v>2.26</v>
       </c>
       <c r="I11" t="n">
-        <v>2.98</v>
+        <v>2.28</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2557,123 +2557,123 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,37 +2683,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.84</v>
+        <v>1.79</v>
       </c>
       <c r="G12" t="n">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="I12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K12" t="n">
         <v>1000</v>
       </c>
-      <c r="J12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.96</v>
-      </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,66 +2877,66 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2945,123 +2945,123 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Estoril Praia</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.48</v>
+        <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I14" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="J14" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="G15" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9</v>
+        <v>2.98</v>
       </c>
       <c r="J15" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.54</v>
+        <v>3.15</v>
       </c>
       <c r="G16" t="n">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,42 +3653,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>18:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,201 +3830,977 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-18 09:51:25</t>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-18 12:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Floresta EC</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Ferroviaria</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-18 12:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Maringa</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Brusque FC</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-18 12:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-18 12:24:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Club Sportivo Ameliano</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Nacional (Par)</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q22" t="n">
         <v>1.01</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-04-18 09:51:25</t>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-18 12:24:05</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BH26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>1.38</v>
       </c>
       <c r="G2" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="H2" t="n">
         <v>8.4</v>
@@ -775,152 +775,152 @@
         <v>5.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.12</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
         <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V2" t="n">
         <v>1.09</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19.5</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>40</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY2" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AV2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>3.9</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="BE2" t="n">
-        <v>40</v>
+        <v>4.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
@@ -1151,28 +1151,28 @@
         <v>1.91</v>
       </c>
       <c r="H4" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="J4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N4" t="n">
         <v>2.16</v>
       </c>
-      <c r="K4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
         <v>2.16</v>
@@ -1181,134 +1181,134 @@
         <v>1.58</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H5" t="n">
         <v>3.5</v>
@@ -1351,158 +1351,158 @@
         <v>3.7</v>
       </c>
       <c r="J5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.4</v>
       </c>
-      <c r="K5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P5" t="n">
         <v>2.02</v>
       </c>
       <c r="Q5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S5" t="n">
         <v>1.89</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
@@ -1551,16 +1551,16 @@
         <v>1000</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P6" t="n">
         <v>2.44</v>
@@ -1569,134 +1569,134 @@
         <v>1.44</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
@@ -1742,162 +1742,162 @@
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
         <v>1.63</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Farul Constanta</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>1.27</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Porto B</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Leixoes</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:05:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.65</v>
+        <v>2.72</v>
       </c>
       <c r="G10" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.36</v>
+        <v>1.36</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="J10" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.26</v>
+        <v>1.73</v>
       </c>
       <c r="I11" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>1.77</v>
       </c>
       <c r="T11" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AA11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AB11" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG11" t="n">
         <v>29</v>
       </c>
-      <c r="AF11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AI11" t="n">
         <v>48</v>
       </c>
       <c r="AJ11" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>2.02</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR11" t="n">
-        <v>12</v>
+        <v>1.95</v>
       </c>
       <c r="AS11" t="n">
-        <v>26</v>
+        <v>2.04</v>
       </c>
       <c r="AT11" t="n">
-        <v>10.5</v>
+        <v>2.04</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>1.89</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>1.92</v>
       </c>
       <c r="AW11" t="n">
-        <v>23</v>
+        <v>2.02</v>
       </c>
       <c r="AX11" t="n">
-        <v>21</v>
+        <v>2.12</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>2.04</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>2.04</v>
       </c>
       <c r="BA11" t="n">
-        <v>38</v>
+        <v>2.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>13</v>
+        <v>2.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>26</v>
+        <v>2.14</v>
       </c>
       <c r="BD11" t="n">
-        <v>32</v>
+        <v>2.14</v>
       </c>
       <c r="BE11" t="n">
-        <v>14</v>
+        <v>2.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>48</v>
+        <v>2.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>19.5</v>
+        <v>2.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Leixoes</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,66 +2877,66 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.48</v>
+        <v>3.65</v>
       </c>
       <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I13" t="n">
         <v>2.5</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.15</v>
       </c>
-      <c r="I13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.96</v>
+        <v>2.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2945,123 +2945,123 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Estoril Praia</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.15</v>
+        <v>1.52</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5</v>
+        <v>1.54</v>
       </c>
       <c r="H14" t="n">
-        <v>2.34</v>
+        <v>7.2</v>
       </c>
       <c r="I14" t="n">
-        <v>2.52</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>1.42</v>
+        <v>4.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.96</v>
+        <v>1.97</v>
       </c>
       <c r="G15" t="n">
-        <v>3.15</v>
+        <v>2.16</v>
       </c>
       <c r="H15" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>2.98</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.48</v>
+        <v>1.99</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,66 +3459,66 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="H16" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.33</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
-        <v>1.37</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,123 +3527,123 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,66 +3653,66 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3721,123 +3721,123 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Estoril Praia</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.48</v>
+        <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="I18" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="J18" t="n">
-        <v>1.31</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="G19" t="n">
-        <v>2.82</v>
+        <v>3.55</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>2.98</v>
       </c>
       <c r="J19" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.54</v>
+        <v>3.15</v>
       </c>
       <c r="G20" t="n">
-        <v>1.96</v>
+        <v>3.55</v>
       </c>
       <c r="H20" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="K20" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,42 +4429,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>18:15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.88</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,201 +4606,977 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-18 12:24:05</t>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-18 14:56:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Floresta EC</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Ferroviaria</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-18 14:56:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Maringa</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Brusque FC</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-18 14:56:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-18 14:56:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Club Sportivo Ameliano</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Nacional (Par)</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>2026-04-18 12:24:05</t>
+      <c r="Q26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-18 14:56:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH26"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Botosani</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Metaloglobus Bucuresti</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.38</v>
+        <v>2.96</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47</v>
+        <v>3.3</v>
       </c>
       <c r="H2" t="n">
-        <v>8.4</v>
+        <v>2.7</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>2.96</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7</v>
+        <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>2.66</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="V2" t="n">
-        <v>1.09</v>
+        <v>1.51</v>
       </c>
       <c r="W2" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="Z2" t="n">
-        <v>100</v>
+        <v>18.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>390</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD2" t="n">
         <v>14</v>
       </c>
-      <c r="AD2" t="n">
-        <v>42</v>
-      </c>
       <c r="AE2" t="n">
-        <v>180</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AS2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC2" t="n">
         <v>32</v>
       </c>
-      <c r="AI2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>13</v>
-      </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.3</v>
+        <v>110</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.9</v>
+        <v>38</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.3</v>
+        <v>32</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Czech 2 Liga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SK Artis Brno</t>
+          <t>Botosani</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MAS Taborsko</t>
+          <t>FC Metaloglobus Bucuresti</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="G3" t="n">
-        <v>2.44</v>
+        <v>1.47</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.67</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.69</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Czech 2 Liga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,60 +1131,60 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>SK Artis Brno</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gornik Leczna</t>
+          <t>MAS Taborsko</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="G4" t="n">
-        <v>1.91</v>
+        <v>2.44</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="K4" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Polissya Zhytomyr</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.89</v>
       </c>
-      <c r="T5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.02</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR5" t="n">
         <v>27</v>
       </c>
-      <c r="AA5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH5" t="n">
+      <c r="AS5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>16</v>
       </c>
-      <c r="AI5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>14</v>
-      </c>
       <c r="BA5" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="BB5" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.4</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
-        <v>9.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>11.5</v>
+        <v>100</v>
       </c>
       <c r="BF5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,73 +1519,73 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Gornik Leczna</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.59</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.44</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W6" t="n">
         <v>2.08</v>
       </c>
-      <c r="T6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.16</v>
-      </c>
       <c r="X6" t="n">
         <v>1000</v>
       </c>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,112 +1718,112 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="H7" t="n">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.1</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>1.63</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
@@ -1835,69 +1835,69 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,28 +1912,28 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -1942,25 +1942,25 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>2.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.27</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.02</v>
+        <v>1.63</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,112 +2106,112 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="G9" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U9" t="n">
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,69 +2223,69 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IK Brage</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.72</v>
+        <v>2.24</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="H10" t="n">
-        <v>1.36</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>1.73</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Farul Constanta</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6</v>
+        <v>1.59</v>
       </c>
       <c r="G11" t="n">
-        <v>6.4</v>
+        <v>1.86</v>
       </c>
       <c r="H11" t="n">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.89</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,79 +2527,79 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.55</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.18</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2.12</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.19</v>
+        <v>2.16</v>
       </c>
       <c r="X11" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
@@ -2611,69 +2611,69 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:05:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Porto B</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Leixoes</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="H13" t="n">
-        <v>2.36</v>
+        <v>1.71</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>1.89</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE13" t="n">
         <v>2.76</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Leixoes</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.52</v>
+        <v>2.58</v>
       </c>
       <c r="G14" t="n">
-        <v>1.54</v>
+        <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>7.2</v>
+        <v>2.58</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>4.7</v>
+        <v>110</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.97</v>
+        <v>3.65</v>
       </c>
       <c r="G15" t="n">
-        <v>2.16</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>2.32</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>2.48</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P15" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="Q15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.99</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.65</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>2.28</v>
       </c>
       <c r="O16" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.26</v>
+        <v>1.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3</v>
+        <v>2.06</v>
       </c>
       <c r="T16" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR16" t="n">
         <v>25</v>
       </c>
-      <c r="AG16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>12</v>
-      </c>
       <c r="AS16" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB16" t="n">
         <v>18</v>
       </c>
-      <c r="AX16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ16" t="n">
+      <c r="BC16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD16" t="n">
         <v>18</v>
       </c>
-      <c r="BA16" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>32</v>
-      </c>
       <c r="BE16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="BF16" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>1.52</v>
       </c>
       <c r="G17" t="n">
-        <v>2.48</v>
+        <v>1.54</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2</v>
+        <v>7.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="Q17" t="n">
         <v>1.96</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
         <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>2.26</v>
+        <v>1.81</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC17" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y17" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>22</v>
-      </c>
       <c r="BD17" t="n">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>55</v>
+        <v>8.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>28</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Estoril Praia</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="H18" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="I18" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.96</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.96</v>
+        <v>2.02</v>
       </c>
       <c r="G19" t="n">
-        <v>3.55</v>
+        <v>2.16</v>
       </c>
       <c r="H19" t="n">
-        <v>2.42</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>2.98</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H20" t="n">
         <v>3.15</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.55</v>
       </c>
-      <c r="H20" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.96</v>
-      </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:15:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Estoril Praia</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="H22" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="I22" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="J22" t="n">
         <v>2.66</v>
       </c>
       <c r="K22" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P22" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="G23" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>2.98</v>
       </c>
       <c r="J23" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.54</v>
+        <v>3.15</v>
       </c>
       <c r="G24" t="n">
-        <v>1.96</v>
+        <v>3.55</v>
       </c>
       <c r="H24" t="n">
-        <v>2.08</v>
+        <v>2.74</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,42 +5205,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Zamora FC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Caracas</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="G25" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="I25" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>
@@ -5399,17 +5399,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -5576,7 +5576,1559 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-18 14:56:36</t>
+          <t>2026-04-18 17:26:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Carabobo FC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Academia Anzoategui FC</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:26:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:26:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Floresta EC</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ferroviaria</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:26:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Maringa</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Brusque FC</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:26:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Deportivo La Guaira</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Portuguesa FC</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:26:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:26:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Club Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Nacional (Par)</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:26:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Juventud De Las Piedras</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H34" t="n">
+        <v>10</v>
+      </c>
+      <c r="I34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:26:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -898,7 +898,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB2" t="n">
         <v>40</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
         <v>1.73</v>
@@ -1020,7 +1020,7 @@
         <v>10.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD3" t="n">
         <v>42</v>
@@ -1047,7 +1047,7 @@
         <v>18</v>
       </c>
       <c r="AL3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM3" t="n">
         <v>180</v>
@@ -1062,13 +1062,13 @@
         <v>17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT3" t="n">
         <v>7.4</v>
@@ -1077,10 +1077,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX3" t="n">
         <v>7.4</v>
@@ -1089,10 +1089,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB3" t="n">
         <v>10</v>
@@ -1101,20 +1101,20 @@
         <v>13</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF3" t="n">
         <v>4.9</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.36</v>
+        <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
         <v>1.67</v>
@@ -1178,13 +1178,13 @@
         <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.97</v>
+        <v>1.32</v>
       </c>
       <c r="R4" t="n">
         <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>1.97</v>
+        <v>1.32</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -1339,64 +1339,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="n">
         <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U5" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
         <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="X5" t="n">
         <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
         <v>42</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AC5" t="n">
         <v>9.199999999999999</v>
@@ -1420,16 +1420,16 @@
         <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK5" t="n">
         <v>26</v>
@@ -1441,7 +1441,7 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1450,7 +1450,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
         <v>27</v>
@@ -1459,50 +1459,50 @@
         <v>85</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU5" t="n">
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD5" t="n">
         <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF5" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BG5" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -1557,16 +1557,16 @@
         <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G7" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="H7" t="n">
         <v>3.6</v>
       </c>
       <c r="I7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1775,19 +1775,19 @@
         <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="X7" t="n">
         <v>16</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
         <v>65</v>
@@ -1799,7 +1799,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE7" t="n">
         <v>40</v>
@@ -1835,16 +1835,16 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>9.4</v>
@@ -1856,41 +1856,41 @@
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
         <v>17.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
         <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G8" t="n">
         <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>2.98</v>
+        <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -1969,7 +1969,7 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
         <v>1.62</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
         <v>1.75</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>2.3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I10" t="n">
         <v>3.7</v>
@@ -2336,13 +2336,13 @@
         <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
@@ -2414,19 +2414,19 @@
         <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AP10" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT10" t="n">
         <v>9.6</v>
@@ -2435,10 +2435,10 @@
         <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX10" t="n">
         <v>13</v>
@@ -2450,19 +2450,19 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC10" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF10" t="n">
         <v>11.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>6.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
         <v>8.6</v>
@@ -2524,7 +2524,7 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
         <v>2.44</v>
@@ -2539,7 +2539,7 @@
         <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
         <v>2.08</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -2721,16 +2721,16 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
         <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
         <v>1.32</v>
@@ -2748,7 +2748,7 @@
         <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
         <v>21</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>4.6</v>
       </c>
       <c r="G13" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="I13" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
         <v>4.5</v>
@@ -2924,70 +2924,70 @@
         <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
         <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="U13" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="V13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA13" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AB13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AF13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AG13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AH13" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI13" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK13" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
         <v>120</v>
@@ -2996,65 +2996,65 @@
         <v>80</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.82</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS13" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU13" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.38</v>
+        <v>8.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.54</v>
+        <v>13.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.64</v>
+        <v>3.85</v>
       </c>
       <c r="AY13" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.56</v>
+        <v>15.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.66</v>
+        <v>23</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.82</v>
+        <v>7.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="G14" t="n">
         <v>3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="I14" t="n">
         <v>3.45</v>
@@ -3100,7 +3100,7 @@
         <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>110</v>
+        <v>6.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,22 +3109,22 @@
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="O14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R14" t="n">
         <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -3294,13 +3294,13 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N15" t="n">
         <v>2.5</v>
@@ -3312,7 +3312,7 @@
         <v>1.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R15" t="n">
         <v>1.17</v>
@@ -3327,7 +3327,7 @@
         <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W15" t="n">
         <v>1.33</v>
@@ -3342,7 +3342,7 @@
         <v>13.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AB15" t="n">
         <v>9.800000000000001</v>
@@ -3369,7 +3369,7 @@
         <v>70</v>
       </c>
       <c r="AJ15" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK15" t="n">
         <v>70</v>
@@ -3408,41 +3408,41 @@
         <v>11</v>
       </c>
       <c r="AW15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY15" t="n">
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BA15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB15" t="n">
         <v>10.5</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BC15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE15" t="n">
         <v>11</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BF15" t="n">
         <v>10.5</v>
       </c>
-      <c r="BD15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>11</v>
-      </c>
       <c r="BG15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H16" t="n">
         <v>3.7</v>
       </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="K16" t="n">
         <v>1000</v>
@@ -3521,10 +3521,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3581,52 +3581,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -3697,13 +3697,13 @@
         <v>1.34</v>
       </c>
       <c r="P17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
         <v>3.4</v>
@@ -3727,10 +3727,10 @@
         <v>24</v>
       </c>
       <c r="Z17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA17" t="n">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="AB17" t="n">
         <v>7.8</v>
@@ -3742,7 +3742,7 @@
         <v>30</v>
       </c>
       <c r="AE17" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF17" t="n">
         <v>8.800000000000001</v>
@@ -3754,7 +3754,7 @@
         <v>27</v>
       </c>
       <c r="AI17" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ17" t="n">
         <v>15</v>
@@ -3766,13 +3766,13 @@
         <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN17" t="n">
         <v>10.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -3781,10 +3781,10 @@
         <v>18.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -3793,10 +3793,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX17" t="n">
         <v>7.4</v>
@@ -3808,7 +3808,7 @@
         <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
@@ -3817,20 +3817,20 @@
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
         <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G18" t="n">
         <v>3.75</v>
@@ -3870,7 +3870,7 @@
         <v>2.26</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J18" t="n">
         <v>3.45</v>
@@ -3879,13 +3879,13 @@
         <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.42</v>
@@ -3909,7 +3909,7 @@
         <v>1.99</v>
       </c>
       <c r="V18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W18" t="n">
         <v>1.36</v>
@@ -3924,7 +3924,7 @@
         <v>13</v>
       </c>
       <c r="AA18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB18" t="n">
         <v>12</v>
@@ -3996,7 +3996,7 @@
         <v>23</v>
       </c>
       <c r="AY18" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>18.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -4085,13 +4085,13 @@
         <v>1.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
       <c r="Q19" t="n">
         <v>1.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
         <v>2</v>
@@ -4100,7 +4100,7 @@
         <v>1.76</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V19" t="n">
         <v>1.3</v>
@@ -4163,52 +4163,52 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
         <v>1.01</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G20" t="n">
         <v>2.5</v>
@@ -4264,7 +4264,7 @@
         <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.42</v>
@@ -4321,7 +4321,7 @@
         <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE20" t="n">
         <v>34</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>3.15</v>
       </c>
       <c r="G21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H21" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I21" t="n">
         <v>2.46</v>
@@ -4461,7 +4461,7 @@
         <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
@@ -4473,13 +4473,13 @@
         <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q21" t="n">
         <v>1.97</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
         <v>3.4</v>
@@ -4509,7 +4509,7 @@
         <v>34</v>
       </c>
       <c r="AB21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
@@ -4533,7 +4533,7 @@
         <v>40</v>
       </c>
       <c r="AJ21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK21" t="n">
         <v>44</v>
@@ -4545,7 +4545,7 @@
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
@@ -4560,7 +4560,7 @@
         <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
         <v>11</v>
@@ -4584,29 +4584,29 @@
         <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF21" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
         <v>16</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -4637,40 +4637,40 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="G22" t="n">
         <v>3.05</v>
       </c>
       <c r="H22" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I22" t="n">
         <v>4.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K22" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
         <v>1.52</v>
       </c>
       <c r="O22" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="P22" t="n">
         <v>1.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="R22" t="n">
         <v>1.14</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -4849,16 +4849,16 @@
         <v>3.25</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P23" t="n">
         <v>1.59</v>
@@ -4867,134 +4867,134 @@
         <v>2.48</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -5040,19 +5040,19 @@
         <v>2.7</v>
       </c>
       <c r="K24" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="P24" t="n">
         <v>1.37</v>
@@ -5061,134 +5061,134 @@
         <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="G25" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="H25" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K25" t="n">
         <v>3.4</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P25" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q25" t="n">
         <v>2.42</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -5431,152 +5431,152 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P26" t="n">
         <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -5625,152 +5625,152 @@
         <v>1000</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P27" t="n">
         <v>1.79</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
         <v>2.6</v>
       </c>
       <c r="I28" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>2.76</v>
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Q28" t="n">
         <v>3.05</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.46</v>
+        <v>1.25</v>
       </c>
       <c r="G29" t="n">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="H29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I29" t="n">
         <v>4.9</v>
       </c>
       <c r="J29" t="n">
-        <v>2.72</v>
+        <v>1.97</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -6392,10 +6392,10 @@
         <v>2.14</v>
       </c>
       <c r="I31" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>3.35</v>
+        <v>2.16</v>
       </c>
       <c r="K31" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>1.72</v>
       </c>
       <c r="G32" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="H32" t="n">
         <v>4.8</v>
@@ -6589,7 +6589,7 @@
         <v>6.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
         <v>4.3</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
         <v>1.86</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-18 17:26:57</t>
+          <t>2026-04-18 19:55:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -760,13 +760,13 @@
         <v>2.96</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
         <v>2.7</v>
       </c>
       <c r="I2" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J2" t="n">
         <v>2.96</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -1169,22 +1169,22 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.32</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>1.32</v>
+        <v>1.94</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H5" t="n">
         <v>4.4</v>
@@ -1351,7 +1351,7 @@
         <v>5.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>4.1</v>
@@ -1366,19 +1366,19 @@
         <v>2.96</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
         <v>1.88</v>
@@ -1387,13 +1387,13 @@
         <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
         <v>16</v>
@@ -1408,7 +1408,7 @@
         <v>8.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
         <v>23</v>
@@ -1420,7 +1420,7 @@
         <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
         <v>26</v>
@@ -1429,13 +1429,13 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
@@ -1447,7 +1447,7 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>10.5</v>
@@ -1456,19 +1456,19 @@
         <v>27</v>
       </c>
       <c r="AS5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AT5" t="n">
         <v>5.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AX5" t="n">
         <v>8.6</v>
@@ -1486,23 +1486,23 @@
         <v>18</v>
       </c>
       <c r="BC5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE5" t="n">
         <v>110</v>
       </c>
       <c r="BF5" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.18</v>
       </c>
       <c r="G7" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H7" t="n">
         <v>3.6</v>
@@ -1763,7 +1763,7 @@
         <v>1.87</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
         <v>3.2</v>
@@ -1778,7 +1778,7 @@
         <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X7" t="n">
         <v>16</v>
@@ -1856,7 +1856,7 @@
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX7" t="n">
         <v>6.4</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.62</v>
+        <v>1.16</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2139,31 +2139,31 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>1.75</v>
+        <v>2.54</v>
       </c>
       <c r="T9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         <v>1.72</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V10" t="n">
         <v>1.37</v>
@@ -2423,7 +2423,7 @@
         <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS10" t="n">
         <v>10.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G11" t="n">
         <v>1.86</v>
@@ -2518,7 +2518,7 @@
         <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,16 +2527,16 @@
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="R11" t="n">
         <v>1.53</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -2718,149 +2718,149 @@
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V12" t="n">
         <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.06</v>
+        <v>9.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.06</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.06</v>
+        <v>30</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.06</v>
+        <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.06</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.06</v>
+        <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.06</v>
+        <v>4.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.06</v>
+        <v>15</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.06</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.06</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.06</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.06</v>
+        <v>32</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.06</v>
+        <v>4.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.06</v>
+        <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.06</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.06</v>
+        <v>19</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.06</v>
+        <v>17.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>4.6</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H13" t="n">
         <v>1.73</v>
       </c>
       <c r="I13" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
         <v>4.5</v>
@@ -2921,7 +2921,7 @@
         <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1.75</v>
@@ -2942,7 +2942,7 @@
         <v>2.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -3005,7 +3005,7 @@
         <v>7.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
         <v>13.5</v>
@@ -3017,10 +3017,10 @@
         <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AX13" t="n">
         <v>3.85</v>
@@ -3029,10 +3029,10 @@
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>23</v>
+        <v>3.8</v>
       </c>
       <c r="BB13" t="n">
         <v>4.1</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -3109,13 +3109,13 @@
         <v>1.04</v>
       </c>
       <c r="N14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
         <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q14" t="n">
         <v>1.89</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
         <v>1.17</v>
       </c>
       <c r="S15" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
         <v>1.99</v>
@@ -3327,10 +3327,10 @@
         <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
         <v>8.4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
         <v>10.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G20" t="n">
         <v>2.5</v>
@@ -4264,7 +4264,7 @@
         <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L20" t="n">
         <v>1.42</v>
@@ -4300,7 +4300,7 @@
         <v>1.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X20" t="n">
         <v>14</v>
@@ -4321,7 +4321,7 @@
         <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
         <v>34</v>
@@ -4348,7 +4348,7 @@
         <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="n">
         <v>19</v>
@@ -4375,7 +4375,7 @@
         <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
         <v>30</v>
@@ -4402,17 +4402,17 @@
         <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF20" t="n">
         <v>17.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
         <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="U21" t="n">
         <v>2.16</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -4637,40 +4637,40 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="G22" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J22" t="n">
         <v>2.68</v>
       </c>
       <c r="K22" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
         <v>1.52</v>
       </c>
       <c r="O22" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P22" t="n">
         <v>1.52</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="R22" t="n">
         <v>1.14</v>
@@ -4685,10 +4685,10 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N23" t="n">
         <v>1.59</v>
@@ -4873,128 +4873,128 @@
         <v>4.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U23" t="n">
         <v>1.61</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W23" t="n">
         <v>1.46</v>
       </c>
       <c r="X23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY23" t="n">
         <v>12</v>
       </c>
-      <c r="Y23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>2.58</v>
+        <v>6.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB23" t="n">
-        <v>2.74</v>
+        <v>8</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.74</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.84</v>
+        <v>9.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.84</v>
+        <v>9.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>3.15</v>
       </c>
       <c r="G24" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H24" t="n">
         <v>2.74</v>
@@ -5079,10 +5079,10 @@
         <v>1.4</v>
       </c>
       <c r="X24" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Z24" t="n">
         <v>21</v>
@@ -5094,7 +5094,7 @@
         <v>9.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD24" t="n">
         <v>18.5</v>
@@ -5118,7 +5118,7 @@
         <v>90</v>
       </c>
       <c r="AK24" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL24" t="n">
         <v>140</v>
@@ -5142,7 +5142,7 @@
         <v>12</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT24" t="n">
         <v>6.8</v>
@@ -5154,7 +5154,7 @@
         <v>13</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.2</v>
+        <v>38</v>
       </c>
       <c r="AX24" t="n">
         <v>15</v>
@@ -5163,32 +5163,32 @@
         <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G25" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="H25" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
         <v>3.05</v>
@@ -5243,22 +5243,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="O25" t="n">
         <v>1.01</v>
       </c>
       <c r="P25" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.42</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>2.42</v>
+        <v>2.14</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5267,10 +5267,10 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
         <v>1.42</v>
@@ -5521,52 +5521,52 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -5610,28 +5610,28 @@
         <v>1.4</v>
       </c>
       <c r="G27" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H27" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O27" t="n">
         <v>1.32</v>
@@ -5640,13 +5640,13 @@
         <v>1.79</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="R27" t="n">
         <v>1.08</v>
       </c>
       <c r="S27" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -5658,7 +5658,7 @@
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="H28" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J28" t="n">
         <v>2.76</v>
@@ -5819,152 +5819,152 @@
         <v>3.05</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="P28" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="G29" t="n">
         <v>3.45</v>
@@ -6013,16 +6013,16 @@
         <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P29" t="n">
         <v>1.37</v>
@@ -6031,134 +6031,134 @@
         <v>2.42</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -6195,28 +6195,28 @@
         <v>1.96</v>
       </c>
       <c r="H30" t="n">
-        <v>2.08</v>
+        <v>4.7</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P30" t="n">
         <v>1.55</v>
@@ -6225,134 +6225,134 @@
         <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -6389,28 +6389,28 @@
         <v>1.91</v>
       </c>
       <c r="H31" t="n">
-        <v>2.14</v>
+        <v>4.3</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J31" t="n">
-        <v>2.16</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P31" t="n">
         <v>1.59</v>
@@ -6419,134 +6419,134 @@
         <v>2.06</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -6577,34 +6577,34 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G32" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="H32" t="n">
         <v>4.8</v>
       </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="K32" t="n">
         <v>4.3</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
         <v>1.07</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P32" t="n">
         <v>1.89</v>
@@ -6613,134 +6613,134 @@
         <v>1.92</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -6789,152 +6789,152 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P33" t="n">
         <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>1.37</v>
       </c>
       <c r="G34" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="H34" t="n">
         <v>10</v>
@@ -6983,16 +6983,16 @@
         <v>5.9</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P34" t="n">
         <v>1.86</v>
@@ -7001,134 +7001,134 @@
         <v>1.94</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-18 19:55:23</t>
+          <t>2026-04-18 22:23:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.38</v>
       </c>
       <c r="G3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H3" t="n">
         <v>8.4</v>
@@ -1002,7 +1002,7 @@
         <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X3" t="n">
         <v>24</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.04</v>
       </c>
       <c r="G4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
         <v>3.15</v>
@@ -1157,7 +1157,7 @@
         <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
         <v>4.2</v>
@@ -1196,7 +1196,7 @@
         <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
         <v>4.4</v>
@@ -1381,16 +1381,16 @@
         <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="V5" t="n">
         <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,79 +1718,79 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G7" t="n">
         <v>2.3</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I7" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
         <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U7" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
         <v>1.76</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB7" t="n">
         <v>11</v>
@@ -1802,102 +1802,102 @@
         <v>15.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
         <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
         <v>48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL7" t="n">
         <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.5</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU7" t="n">
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX7" t="n">
         <v>13</v>
       </c>
-      <c r="AW7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB7" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB7" t="n">
-        <v>8</v>
-      </c>
       <c r="BC7" t="n">
-        <v>17.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,55 +1912,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.16</v>
+        <v>1.69</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="I8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.85</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.7</v>
-      </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>2.18</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,28 +2106,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.16</v>
+        <v>2.6</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2136,37 +2136,37 @@
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.36</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="H10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.55</v>
       </c>
-      <c r="I10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>24</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.4</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.61</v>
+        <v>2.18</v>
       </c>
       <c r="G11" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="H11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="O11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD11" t="n">
         <v>8</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
@@ -2724,10 +2724,10 @@
         <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="P12" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
         <v>1.89</v>
@@ -2736,10 +2736,10 @@
         <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
         <v>2.22</v>
@@ -2748,7 +2748,7 @@
         <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
         <v>18</v>
@@ -2808,13 +2808,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>30</v>
+        <v>4.6</v>
       </c>
       <c r="AT12" t="n">
         <v>9.4</v>
@@ -2826,7 +2826,7 @@
         <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX12" t="n">
         <v>15</v>
@@ -2835,13 +2835,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA12" t="n">
         <v>4.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="BC12" t="n">
         <v>4.5</v>
@@ -2850,7 +2850,7 @@
         <v>4.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF12" t="n">
         <v>19</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -2900,10 +2900,10 @@
         <v>1.73</v>
       </c>
       <c r="I13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
         <v>4.5</v>
@@ -2933,16 +2933,16 @@
         <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="V13" t="n">
         <v>2.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -2999,13 +2999,13 @@
         <v>12.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
         <v>7.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS13" t="n">
         <v>13.5</v>
@@ -3014,7 +3014,7 @@
         <v>14</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AV13" t="n">
         <v>7.6</v>
@@ -3032,7 +3032,7 @@
         <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.8</v>
+        <v>23</v>
       </c>
       <c r="BB13" t="n">
         <v>4.1</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
         <v>1.68</v>
       </c>
       <c r="W15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
         <v>8.4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
         <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -3697,10 +3697,10 @@
         <v>1.34</v>
       </c>
       <c r="P17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1.9</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.93</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
         <v>15</v>
       </c>
       <c r="AY20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ20" t="n">
         <v>15.5</v>
@@ -4402,17 +4402,17 @@
         <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BF20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
         <v>4.1</v>
       </c>
       <c r="J22" t="n">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="K22" t="n">
         <v>3.65</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
         <v>2.96</v>
       </c>
       <c r="G23" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H23" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I23" t="n">
         <v>2.98</v>
@@ -4855,10 +4855,10 @@
         <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>1.59</v>
+        <v>2.76</v>
       </c>
       <c r="O23" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P23" t="n">
         <v>1.59</v>
@@ -4867,22 +4867,22 @@
         <v>2.48</v>
       </c>
       <c r="R23" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
         <v>2.02</v>
       </c>
       <c r="U23" t="n">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X23" t="n">
         <v>9.4</v>
@@ -4930,7 +4930,7 @@
         <v>65</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN23" t="n">
         <v>1000</v>
@@ -4948,7 +4948,7 @@
         <v>15.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT23" t="n">
         <v>8</v>
@@ -4960,7 +4960,7 @@
         <v>11.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AX23" t="n">
         <v>16.5</v>
@@ -4969,32 +4969,32 @@
         <v>12</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BB23" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="O27" t="n">
         <v>1.32</v>
@@ -5643,7 +5643,7 @@
         <v>1.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
         <v>1.8</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="H28" t="n">
         <v>2.66</v>
       </c>
       <c r="I28" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="J28" t="n">
         <v>2.76</v>
@@ -5822,149 +5822,149 @@
         <v>1.64</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P28" t="n">
         <v>1.41</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.4</v>
       </c>
       <c r="Q28" t="n">
         <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="S28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X28" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>6.2</v>
       </c>
-      <c r="T28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="AR28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS28" t="n">
         <v>10</v>
       </c>
-      <c r="Z28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC28" t="n">
+      <c r="AT28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC28" t="n">
         <v>10</v>
       </c>
-      <c r="AD28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>95</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BD28" t="n">
-        <v>2.7</v>
+        <v>11</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.7</v>
+        <v>11.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>2.66</v>
+        <v>11</v>
       </c>
       <c r="BG28" t="n">
-        <v>2.66</v>
+        <v>10</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="G29" t="n">
         <v>3.45</v>
@@ -6010,7 +6010,7 @@
         <v>1.97</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6031,7 +6031,7 @@
         <v>2.42</v>
       </c>
       <c r="R29" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="S29" t="n">
         <v>2.42</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
         <v>4.7</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="J30" t="n">
         <v>3.1</v>
@@ -6225,7 +6225,7 @@
         <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
@@ -6237,7 +6237,7 @@
         <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
         <v>2.04</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
         <v>1.59</v>
       </c>
       <c r="O31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P31" t="n">
         <v>1.59</v>
@@ -6419,7 +6419,7 @@
         <v>2.06</v>
       </c>
       <c r="R31" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
         <v>2.06</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G32" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="H32" t="n">
         <v>4.8</v>
       </c>
       <c r="I32" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
         <v>3.75</v>
@@ -6619,16 +6619,16 @@
         <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U32" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="V32" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X32" t="n">
         <v>18</v>
@@ -6697,25 +6697,25 @@
         <v>4.1</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW32" t="n">
         <v>4.1</v>
       </c>
       <c r="AX32" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY32" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ32" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA32" t="n">
         <v>4.1</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -6795,22 +6795,22 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P33" t="n">
         <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="R33" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>
@@ -6986,13 +6986,13 @@
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P34" t="n">
         <v>1.86</v>
@@ -7001,16 +7001,16 @@
         <v>1.94</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="V34" t="n">
         <v>1.07</v>
@@ -7128,7 +7128,589 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-18 22:23:07</t>
+          <t>2026-04-19 00:48:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Univ Catolica (Chile)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Union La Calera</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X35" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-19 00:48:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>21:45:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-19 00:48:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X37" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-19 00:48:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -775,7 +775,7 @@
         <v>3.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
@@ -886,13 +886,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>15.5</v>
@@ -901,7 +901,7 @@
         <v>44</v>
       </c>
       <c r="BB2" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
         <v>32</v>
@@ -913,14 +913,14 @@
         <v>110</v>
       </c>
       <c r="BF2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BG2" t="n">
         <v>32</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -1145,37 +1145,37 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G4" t="n">
         <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
         <v>1.94</v>
@@ -1193,10 +1193,10 @@
         <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1366,7 +1366,7 @@
         <v>2.96</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
         <v>1.67</v>
@@ -1381,58 +1381,58 @@
         <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC5" t="n">
         <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1441,7 +1441,7 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1450,43 +1450,43 @@
         <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU5" t="n">
         <v>6</v>
       </c>
       <c r="AV5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>36</v>
@@ -1495,14 +1495,14 @@
         <v>110</v>
       </c>
       <c r="BF5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -1533,40 +1533,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="G6" t="n">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="I6" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="O6" t="n">
         <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
@@ -1581,10 +1581,10 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="W6" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -1757,10 +1757,10 @@
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R7" t="n">
         <v>1.4</v>
@@ -1796,7 +1796,7 @@
         <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>15.5</v>
@@ -1814,13 +1814,13 @@
         <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
         <v>28</v>
       </c>
       <c r="AK7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
         <v>36</v>
@@ -1835,13 +1835,13 @@
         <v>46</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
         <v>10.5</v>
@@ -1853,10 +1853,10 @@
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX7" t="n">
         <v>13</v>
@@ -1871,7 +1871,7 @@
         <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
         <v>8.199999999999999</v>
@@ -1880,17 +1880,17 @@
         <v>30</v>
       </c>
       <c r="BE7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
         <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="G8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
         <v>4.4</v>
@@ -1939,41 +1939,41 @@
         <v>5.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
         <v>1.48</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W8" t="n">
         <v>2.08</v>
       </c>
-      <c r="T8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.18</v>
-      </c>
       <c r="X8" t="n">
         <v>1000</v>
       </c>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -1999,10 +1999,10 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2014,7 +2014,7 @@
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2023,68 +2023,68 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -2115,28 +2115,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="I9" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
         <v>2.1</v>
@@ -2148,13 +2148,13 @@
         <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,10 +2163,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -2309,58 +2309,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="H10" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>24</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
         <v>2.3</v>
@@ -2512,7 +2512,7 @@
         <v>3.6</v>
       </c>
       <c r="I11" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
         <v>3.4</v>
@@ -2521,7 +2521,7 @@
         <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
@@ -2536,7 +2536,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
@@ -2551,7 +2551,7 @@
         <v>2.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
         <v>1.76</v>
@@ -2611,10 +2611,10 @@
         <v>44</v>
       </c>
       <c r="AP11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR11" t="n">
         <v>7.8</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
@@ -2715,7 +2715,7 @@
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2736,7 +2736,7 @@
         <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="T12" t="n">
         <v>1.71</v>
@@ -2748,7 +2748,7 @@
         <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X12" t="n">
         <v>18</v>
@@ -2808,7 +2808,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AR12" t="n">
         <v>14</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>4.6</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="I13" t="n">
         <v>1.87</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
         <v>4.5</v>
@@ -2918,31 +2918,31 @@
         <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="R13" t="n">
         <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
         <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="V13" t="n">
         <v>2.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -3002,25 +3002,25 @@
         <v>15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS13" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
         <v>14</v>
       </c>
       <c r="AU13" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX13" t="n">
         <v>3.85</v>
@@ -3029,10 +3029,10 @@
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>23</v>
+        <v>3.8</v>
       </c>
       <c r="BB13" t="n">
         <v>4.1</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -3088,43 +3088,43 @@
         <v>2.36</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H14" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="I14" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J14" t="n">
         <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="O14" t="n">
         <v>1.33</v>
       </c>
       <c r="P14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
         <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3133,10 +3133,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -3327,10 +3327,10 @@
         <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
         <v>8.4</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G16" t="n">
         <v>2.14</v>
@@ -3494,7 +3494,7 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
         <v>2.28</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
         <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -3700,7 +3700,7 @@
         <v>1.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
@@ -3745,7 +3745,7 @@
         <v>140</v>
       </c>
       <c r="AF17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG17" t="n">
         <v>10.5</v>
@@ -3781,10 +3781,10 @@
         <v>18.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -3793,10 +3793,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX17" t="n">
         <v>7.4</v>
@@ -3808,7 +3808,7 @@
         <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
@@ -3817,20 +3817,20 @@
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF17" t="n">
         <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
         <v>1.84</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
         <v>1.31</v>
@@ -4282,7 +4282,7 @@
         <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R20" t="n">
         <v>1.39</v>
@@ -4315,7 +4315,7 @@
         <v>55</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC20" t="n">
         <v>7.6</v>
@@ -4333,7 +4333,7 @@
         <v>11.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
         <v>44</v>
@@ -4348,7 +4348,7 @@
         <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN20" t="n">
         <v>19</v>
@@ -4402,17 +4402,17 @@
         <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF20" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG20" t="n">
         <v>28</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -4461,34 +4461,34 @@
         <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
         <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="U21" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V21" t="n">
         <v>1.68</v>
@@ -4500,7 +4500,7 @@
         <v>14.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
         <v>18.5</v>
@@ -4530,25 +4530,25 @@
         <v>17.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ21" t="n">
         <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL21" t="n">
         <v>55</v>
       </c>
       <c r="AM21" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN21" t="n">
         <v>34</v>
       </c>
       <c r="AO21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP21" t="n">
         <v>12.5</v>
@@ -4560,7 +4560,7 @@
         <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT21" t="n">
         <v>11</v>
@@ -4584,29 +4584,29 @@
         <v>15</v>
       </c>
       <c r="BA21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF21" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>7.2</v>
       </c>
       <c r="BG21" t="n">
         <v>16</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -4637,100 +4637,100 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G22" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H22" t="n">
         <v>3.15</v>
       </c>
       <c r="I22" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="J22" t="n">
         <v>2.86</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N22" t="n">
-        <v>1.52</v>
+        <v>2.58</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="P22" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q22" t="n">
         <v>2.52</v>
       </c>
       <c r="R22" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -4739,68 +4739,68 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I23" t="n">
         <v>2.96</v>
       </c>
-      <c r="G23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>2.98</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>3.25</v>
@@ -4879,10 +4879,10 @@
         <v>1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W23" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X23" t="n">
         <v>9.4</v>
@@ -4891,7 +4891,7 @@
         <v>9</v>
       </c>
       <c r="Z23" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AA23" t="n">
         <v>50</v>
@@ -4909,7 +4909,7 @@
         <v>42</v>
       </c>
       <c r="AF23" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG23" t="n">
         <v>14</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
         <v>130</v>
       </c>
       <c r="AO24" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AP24" t="n">
         <v>5.7</v>
@@ -5142,7 +5142,7 @@
         <v>12</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT24" t="n">
         <v>6.8</v>
@@ -5163,22 +5163,22 @@
         <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA24" t="n">
         <v>5.5</v>
       </c>
       <c r="BB24" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC24" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>5.3</v>
       </c>
       <c r="BD24" t="n">
         <v>5.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF24" t="n">
         <v>5.5</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G25" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="H25" t="n">
         <v>3.6</v>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
         <v>3.05</v>
@@ -5240,43 +5240,43 @@
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N25" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O25" t="n">
         <v>1.47</v>
       </c>
-      <c r="O25" t="n">
-        <v>1.01</v>
-      </c>
       <c r="P25" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>2.14</v>
+        <v>4.8</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V25" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5285,25 +5285,25 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="G27" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="H27" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K27" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="L27" t="n">
         <v>1.32</v>
@@ -5631,22 +5631,22 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="O27" t="n">
         <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -5655,10 +5655,10 @@
         <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W27" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
         <v>1.7</v>
       </c>
       <c r="P28" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q28" t="n">
         <v>3.1</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -6007,10 +6007,10 @@
         <v>4.9</v>
       </c>
       <c r="J29" t="n">
-        <v>1.97</v>
+        <v>1.09</v>
       </c>
       <c r="K29" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6019,7 +6019,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.37</v>
+        <v>2.46</v>
       </c>
       <c r="O29" t="n">
         <v>1.01</v>
@@ -6046,7 +6046,7 @@
         <v>1.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
         <v>4.7</v>
       </c>
       <c r="I30" t="n">
-        <v>85</v>
+        <v>9.4</v>
       </c>
       <c r="J30" t="n">
         <v>3.1</v>
@@ -6213,13 +6213,13 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O30" t="n">
         <v>1.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="n">
         <v>2</v>
@@ -6237,7 +6237,7 @@
         <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W30" t="n">
         <v>2.04</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -6383,58 +6383,58 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N31" t="n">
         <v>1.68</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.59</v>
       </c>
       <c r="O31" t="n">
         <v>1.02</v>
       </c>
       <c r="P31" t="n">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>2.06</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W31" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6491,40 +6491,40 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AS31" t="n">
         <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW31" t="n">
         <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BB31" t="n">
         <v>1.01</v>
@@ -6533,7 +6533,7 @@
         <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>4.8</v>
       </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
         <v>3.75</v>
@@ -6610,16 +6610,16 @@
         <v>1.89</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R32" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="T32" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U32" t="n">
         <v>1.82</v>
@@ -6652,7 +6652,7 @@
         <v>25</v>
       </c>
       <c r="AE32" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF32" t="n">
         <v>13</v>
@@ -6724,7 +6724,7 @@
         <v>14</v>
       </c>
       <c r="BC32" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD32" t="n">
         <v>3.9</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -6965,25 +6965,25 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G34" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="J34" t="n">
         <v>4.6</v>
       </c>
       <c r="K34" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M34" t="n">
         <v>1.06</v>
@@ -6995,7 +6995,7 @@
         <v>1.32</v>
       </c>
       <c r="P34" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q34" t="n">
         <v>1.94</v>
@@ -7004,19 +7004,19 @@
         <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="T34" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U34" t="n">
         <v>1.54</v>
       </c>
       <c r="V34" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W34" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X34" t="n">
         <v>18</v>
@@ -7067,7 +7067,7 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
@@ -7076,10 +7076,10 @@
         <v>10.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR34" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AS34" t="n">
         <v>1.01</v>
@@ -7088,10 +7088,10 @@
         <v>5.2</v>
       </c>
       <c r="AU34" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AW34" t="n">
         <v>160</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -7270,13 +7270,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR35" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS35" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT35" t="n">
         <v>7.4</v>
@@ -7285,10 +7285,10 @@
         <v>8.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW35" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX35" t="n">
         <v>8</v>
@@ -7297,7 +7297,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>5.9</v>
+        <v>19</v>
       </c>
       <c r="BA35" t="n">
         <v>7</v>
@@ -7309,10 +7309,10 @@
         <v>13.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF35" t="n">
         <v>6.2</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
         <v>1.36</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
         <v>1.12</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
         <v>3.8</v>
       </c>
       <c r="K37" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7577,7 +7577,7 @@
         <v>1.33</v>
       </c>
       <c r="P37" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q37" t="n">
         <v>2</v>
@@ -7592,7 +7592,7 @@
         <v>1.82</v>
       </c>
       <c r="U37" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V37" t="n">
         <v>1.17</v>
@@ -7643,7 +7643,7 @@
         <v>20</v>
       </c>
       <c r="AL37" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM37" t="n">
         <v>160</v>
@@ -7706,11 +7706,11 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG37" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-19 00:48:58</t>
+          <t>2026-04-19 03:13:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -769,13 +769,13 @@
         <v>2.94</v>
       </c>
       <c r="J2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
@@ -814,25 +814,25 @@
         <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
         <v>21</v>
@@ -841,28 +841,28 @@
         <v>15</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
         <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AK2" t="n">
         <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="n">
         <v>200</v>
       </c>
       <c r="AN2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO2" t="n">
         <v>60</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>50</v>
       </c>
       <c r="AP2" t="n">
         <v>6.6</v>
@@ -886,22 +886,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AX2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BC2" t="n">
         <v>32</v>
@@ -913,14 +913,14 @@
         <v>110</v>
       </c>
       <c r="BF2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BG2" t="n">
         <v>32</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
         <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
         <v>2.18</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -1145,64 +1145,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>1.78</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="R4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.26</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.3</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z4" t="n">
         <v>1000</v>
@@ -1211,10 +1211,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1226,7 +1226,7 @@
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1253,10 +1253,10 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
         <v>1.01</v>
@@ -1265,10 +1265,10 @@
         <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
         <v>1.01</v>
@@ -1277,13 +1277,13 @@
         <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY4" t="n">
         <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA4" t="n">
         <v>1.01</v>
@@ -1301,14 +1301,14 @@
         <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
         <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -1351,13 +1351,13 @@
         <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="K5" t="n">
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.09</v>
@@ -1366,31 +1366,31 @@
         <v>2.96</v>
       </c>
       <c r="O5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G6" t="n">
         <v>1.74</v>
@@ -1542,25 +1542,25 @@
         <v>5.2</v>
       </c>
       <c r="I6" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
         <v>2.22</v>
@@ -1569,134 +1569,134 @@
         <v>1.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
         <v>2.34</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -1757,13 +1757,13 @@
         <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
         <v>3.15</v>
@@ -1781,10 +1781,10 @@
         <v>1.76</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
         <v>27</v>
@@ -1799,19 +1799,19 @@
         <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
         <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
         <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="n">
         <v>60</v>
@@ -1820,13 +1820,13 @@
         <v>28</v>
       </c>
       <c r="AK7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL7" t="n">
         <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
         <v>16</v>
@@ -1835,16 +1835,16 @@
         <v>46</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT7" t="n">
         <v>9.6</v>
@@ -1853,10 +1853,10 @@
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AX7" t="n">
         <v>13</v>
@@ -1871,26 +1871,26 @@
         <v>40</v>
       </c>
       <c r="BB7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD7" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>30</v>
-      </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF7" t="n">
         <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -1930,10 +1930,10 @@
         <v>4.4</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
         <v>5.4</v>
@@ -1951,7 +1951,7 @@
         <v>1.18</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q8" t="n">
         <v>1.48</v>
@@ -1960,7 +1960,7 @@
         <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="T8" t="n">
         <v>1.61</v>
@@ -1969,10 +1969,10 @@
         <v>2.34</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2029,16 +2029,16 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
         <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
         <v>9.800000000000001</v>
@@ -2050,7 +2050,7 @@
         <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
@@ -2062,7 +2062,7 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
         <v>14</v>
@@ -2071,20 +2071,20 @@
         <v>12.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>5.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>2.18</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H9" t="n">
         <v>3.1</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
@@ -2148,13 +2148,13 @@
         <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,10 +2163,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W9" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G10" t="n">
         <v>2.68</v>
@@ -2324,37 +2324,37 @@
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P10" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="U10" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="V10" t="n">
         <v>1.54</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>4</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AR10" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
@@ -2533,10 +2533,10 @@
         <v>1.29</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -2697,25 +2697,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G12" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I12" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2724,19 +2724,19 @@
         <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P12" t="n">
         <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
         <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
         <v>1.71</v>
@@ -2748,7 +2748,7 @@
         <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X12" t="n">
         <v>18</v>
@@ -2772,13 +2772,13 @@
         <v>14.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
@@ -2787,34 +2787,34 @@
         <v>46</v>
       </c>
       <c r="AJ12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK12" t="n">
         <v>36</v>
       </c>
       <c r="AL12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM12" t="n">
         <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT12" t="n">
         <v>9.4</v>
@@ -2826,41 +2826,41 @@
         <v>9.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB12" t="n">
         <v>4.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BG12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>4.6</v>
       </c>
       <c r="G13" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="H13" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="I13" t="n">
         <v>1.87</v>
@@ -2906,7 +2906,7 @@
         <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2921,28 +2921,28 @@
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
         <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
         <v>2.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
@@ -2999,28 +2999,28 @@
         <v>12.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AT13" t="n">
         <v>14</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX13" t="n">
         <v>3.85</v>
@@ -3029,10 +3029,10 @@
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.8</v>
+        <v>23</v>
       </c>
       <c r="BB13" t="n">
         <v>4.1</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>2.48</v>
       </c>
       <c r="I14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J14" t="n">
         <v>3.05</v>
@@ -3109,22 +3109,22 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R14" t="n">
         <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>1.92</v>
+        <v>1.32</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3133,7 +3133,7 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
         <v>1.45</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -3282,19 +3282,19 @@
         <v>3.65</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I15" t="n">
         <v>2.48</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,16 +3303,16 @@
         <v>1.14</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="O15" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
         <v>1.17</v>
@@ -3321,7 +3321,7 @@
         <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>1.6</v>
@@ -3330,7 +3330,7 @@
         <v>1.67</v>
       </c>
       <c r="W15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
         <v>8.4</v>
@@ -3387,7 +3387,7 @@
         <v>46</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ15" t="n">
         <v>6.2</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="G16" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M16" t="n">
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>2.28</v>
+        <v>5.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="R16" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="W16" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G17" t="n">
         <v>1.54</v>
       </c>
       <c r="H17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I17" t="n">
         <v>8</v>
@@ -3682,10 +3682,10 @@
         <v>4.4</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
@@ -3700,7 +3700,7 @@
         <v>1.89</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
@@ -3745,7 +3745,7 @@
         <v>140</v>
       </c>
       <c r="AF17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG17" t="n">
         <v>10.5</v>
@@ -3781,10 +3781,10 @@
         <v>18.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -3793,10 +3793,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX17" t="n">
         <v>7.4</v>
@@ -3808,7 +3808,7 @@
         <v>21</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
@@ -3817,20 +3817,20 @@
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
         <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -3861,25 +3861,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="G18" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="H18" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="I18" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -3891,7 +3891,7 @@
         <v>1.42</v>
       </c>
       <c r="P18" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
         <v>2.26</v>
@@ -3909,40 +3909,40 @@
         <v>1.99</v>
       </c>
       <c r="V18" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="W18" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X18" t="n">
         <v>11</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC18" t="n">
         <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
         <v>24</v>
       </c>
       <c r="AG18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>19.5</v>
@@ -3954,10 +3954,10 @@
         <v>75</v>
       </c>
       <c r="AK18" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM18" t="n">
         <v>130</v>
@@ -3966,7 +3966,7 @@
         <v>60</v>
       </c>
       <c r="AO18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP18" t="n">
         <v>10</v>
@@ -3975,10 +3975,10 @@
         <v>8</v>
       </c>
       <c r="AR18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
         <v>11</v>
@@ -3990,25 +3990,25 @@
         <v>10.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>18.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB18" t="n">
         <v>32</v>
       </c>
       <c r="BC18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BD18" t="n">
         <v>32</v>
@@ -4017,14 +4017,14 @@
         <v>42</v>
       </c>
       <c r="BF18" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="BG18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H19" t="n">
         <v>4</v>
@@ -4070,49 +4070,49 @@
         <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>1.84</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>1.35</v>
       </c>
       <c r="P19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.32</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.3</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z19" t="n">
         <v>1000</v>
@@ -4121,34 +4121,34 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>1000</v>
@@ -4157,68 +4157,68 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I20" t="n">
         <v>3.15</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>3.5</v>
@@ -4291,16 +4291,16 @@
         <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U20" t="n">
         <v>2.26</v>
       </c>
       <c r="V20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X20" t="n">
         <v>14</v>
@@ -4312,7 +4312,7 @@
         <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB20" t="n">
         <v>11.5</v>
@@ -4321,13 +4321,13 @@
         <v>7.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE20" t="n">
         <v>34</v>
       </c>
       <c r="AF20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
         <v>11.5</v>
@@ -4363,7 +4363,7 @@
         <v>12.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS20" t="n">
         <v>48</v>
@@ -4375,7 +4375,7 @@
         <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW20" t="n">
         <v>30</v>
@@ -4387,7 +4387,7 @@
         <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
         <v>40</v>
@@ -4396,13 +4396,13 @@
         <v>30</v>
       </c>
       <c r="BC20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF20" t="n">
         <v>17.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
         <v>3.35</v>
@@ -4455,7 +4455,7 @@
         <v>2.46</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
         <v>3.65</v>
@@ -4476,7 +4476,7 @@
         <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R21" t="n">
         <v>1.37</v>
@@ -4485,7 +4485,7 @@
         <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U21" t="n">
         <v>2.18</v>
@@ -4494,7 +4494,7 @@
         <v>1.68</v>
       </c>
       <c r="W21" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X21" t="n">
         <v>14.5</v>
@@ -4509,7 +4509,7 @@
         <v>34</v>
       </c>
       <c r="AB21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC21" t="n">
         <v>8</v>
@@ -4536,7 +4536,7 @@
         <v>55</v>
       </c>
       <c r="AK21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL21" t="n">
         <v>55</v>
@@ -4560,7 +4560,7 @@
         <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT21" t="n">
         <v>11</v>
@@ -4584,29 +4584,29 @@
         <v>15</v>
       </c>
       <c r="BA21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF21" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>7.4</v>
       </c>
       <c r="BG21" t="n">
         <v>16</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G22" t="n">
         <v>2.8</v>
@@ -4646,13 +4646,13 @@
         <v>3.15</v>
       </c>
       <c r="I22" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4664,31 +4664,31 @@
         <v>2.58</v>
       </c>
       <c r="O22" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P22" t="n">
         <v>1.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R22" t="n">
         <v>1.19</v>
       </c>
       <c r="S22" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="T22" t="n">
         <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X22" t="n">
         <v>10.5</v>
@@ -4709,13 +4709,13 @@
         <v>8.6</v>
       </c>
       <c r="AD22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
         <v>18.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>19</v>
       </c>
       <c r="AG22" t="n">
         <v>15.5</v>
@@ -4745,7 +4745,7 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ22" t="n">
         <v>7.2</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
         <v>3.25</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M23" t="n">
         <v>1.12</v>
@@ -4972,13 +4972,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BA23" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BB23" t="n">
         <v>10.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BD23" t="n">
         <v>11</v>
@@ -4990,11 +4990,11 @@
         <v>10.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
         <v>2.98</v>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="M24" t="n">
         <v>1.18</v>
@@ -5079,10 +5079,10 @@
         <v>1.4</v>
       </c>
       <c r="X24" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Z24" t="n">
         <v>21</v>
@@ -5094,7 +5094,7 @@
         <v>9.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD24" t="n">
         <v>18.5</v>
@@ -5142,7 +5142,7 @@
         <v>12</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AT24" t="n">
         <v>6.8</v>
@@ -5154,7 +5154,7 @@
         <v>13</v>
       </c>
       <c r="AW24" t="n">
-        <v>38</v>
+        <v>4.3</v>
       </c>
       <c r="AX24" t="n">
         <v>15</v>
@@ -5163,32 +5163,32 @@
         <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>50</v>
+        <v>4.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O25" t="n">
         <v>1.47</v>
@@ -5270,7 +5270,7 @@
         <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X25" t="n">
         <v>12</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -5455,10 +5455,10 @@
         <v>1.42</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -5607,58 +5607,58 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="G27" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="L27" t="n">
         <v>1.32</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="O27" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="V27" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -5804,10 +5804,10 @@
         <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H28" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I28" t="n">
         <v>2.92</v>
@@ -5831,7 +5831,7 @@
         <v>1.7</v>
       </c>
       <c r="P28" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q28" t="n">
         <v>3.1</v>
@@ -5852,7 +5852,7 @@
         <v>1.52</v>
       </c>
       <c r="W28" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X28" t="n">
         <v>7</v>
@@ -5930,7 +5930,7 @@
         <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>40</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX28" t="n">
         <v>18.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -5995,145 +5995,145 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="G29" t="n">
-        <v>3.45</v>
+        <v>2.86</v>
       </c>
       <c r="H29" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I29" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
         <v>2.46</v>
       </c>
       <c r="O29" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="P29" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R29" t="n">
         <v>1.17</v>
       </c>
       <c r="S29" t="n">
-        <v>2.42</v>
+        <v>5.4</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V29" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS29" t="n">
         <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW29" t="n">
         <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA29" t="n">
         <v>1.01</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -6189,58 +6189,58 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="G30" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="H30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K30" t="n">
         <v>4.7</v>
       </c>
-      <c r="I30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>7.4</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>1.57</v>
+        <v>3.05</v>
       </c>
       <c r="O30" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P30" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Q30" t="n">
         <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V30" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W30" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6255,10 +6255,10 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD30" t="n">
         <v>1000</v>
@@ -6267,10 +6267,10 @@
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
         <v>1000</v>
@@ -6297,10 +6297,10 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR30" t="n">
         <v>1.01</v>
@@ -6309,10 +6309,10 @@
         <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV30" t="n">
         <v>1.01</v>
@@ -6321,10 +6321,10 @@
         <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ30" t="n">
         <v>1.01</v>
@@ -6333,7 +6333,7 @@
         <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC30" t="n">
         <v>1.01</v>
@@ -6345,14 +6345,14 @@
         <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG30" t="n">
         <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="G31" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="H31" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="I31" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
@@ -6410,31 +6410,31 @@
         <v>1.68</v>
       </c>
       <c r="O31" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P31" t="n">
         <v>1.68</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>2.08</v>
       </c>
       <c r="T31" t="n">
-        <v>2.02</v>
+        <v>1.03</v>
       </c>
       <c r="U31" t="n">
-        <v>1.7</v>
+        <v>1.03</v>
       </c>
       <c r="V31" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W31" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6527,10 +6527,10 @@
         <v>75</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD31" t="n">
         <v>34</v>
@@ -6539,14 +6539,14 @@
         <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG31" t="n">
         <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G32" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H32" t="n">
         <v>4.8</v>
@@ -6610,16 +6610,16 @@
         <v>1.89</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="R32" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S32" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U32" t="n">
         <v>1.82</v>
@@ -6628,7 +6628,7 @@
         <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X32" t="n">
         <v>18</v>
@@ -6688,7 +6688,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR32" t="n">
         <v>3.95</v>
@@ -6697,25 +6697,25 @@
         <v>4.1</v>
       </c>
       <c r="AT32" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AW32" t="n">
         <v>4.1</v>
       </c>
       <c r="AX32" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY32" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BA32" t="n">
         <v>4.1</v>
@@ -6724,7 +6724,7 @@
         <v>14</v>
       </c>
       <c r="BC32" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BD32" t="n">
         <v>3.9</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -6813,10 +6813,10 @@
         <v>1.51</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G34" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="H34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I34" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="J34" t="n">
         <v>4.6</v>
@@ -6983,7 +6983,7 @@
         <v>5.8</v>
       </c>
       <c r="L34" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M34" t="n">
         <v>1.06</v>
@@ -6995,7 +6995,7 @@
         <v>1.32</v>
       </c>
       <c r="P34" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q34" t="n">
         <v>1.94</v>
@@ -7004,19 +7004,19 @@
         <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="T34" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
         <v>1.54</v>
       </c>
       <c r="V34" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W34" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="X34" t="n">
         <v>18</v>
@@ -7043,7 +7043,7 @@
         <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG34" t="n">
         <v>13</v>
@@ -7067,7 +7067,7 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
@@ -7079,7 +7079,7 @@
         <v>21</v>
       </c>
       <c r="AR34" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AS34" t="n">
         <v>1.01</v>
@@ -7088,13 +7088,13 @@
         <v>5.2</v>
       </c>
       <c r="AU34" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV34" t="n">
         <v>32</v>
       </c>
       <c r="AW34" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AX34" t="n">
         <v>5.6</v>
@@ -7103,10 +7103,10 @@
         <v>7.8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA34" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BB34" t="n">
         <v>8.4</v>
@@ -7115,10 +7115,10 @@
         <v>12.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE34" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BF34" t="n">
         <v>5.9</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>1.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H35" t="n">
         <v>6.6</v>
@@ -7174,7 +7174,7 @@
         <v>4.2</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L35" t="n">
         <v>1.31</v>
@@ -7210,7 +7210,7 @@
         <v>1.14</v>
       </c>
       <c r="W35" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X35" t="n">
         <v>21</v>
@@ -7243,7 +7243,7 @@
         <v>10.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
@@ -7300,7 +7300,7 @@
         <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB35" t="n">
         <v>12</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -7359,10 +7359,10 @@
         <v>2.4</v>
       </c>
       <c r="H36" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I36" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J36" t="n">
         <v>2.78</v>
@@ -7386,7 +7386,7 @@
         <v>1.36</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R36" t="n">
         <v>1.12</v>
@@ -7395,13 +7395,13 @@
         <v>8</v>
       </c>
       <c r="T36" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U36" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V36" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W36" t="n">
         <v>1.71</v>
@@ -7410,7 +7410,7 @@
         <v>6.4</v>
       </c>
       <c r="Y36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z36" t="n">
         <v>1000</v>
@@ -7419,7 +7419,7 @@
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC36" t="n">
         <v>7.4</v>
@@ -7467,10 +7467,10 @@
         <v>8.6</v>
       </c>
       <c r="AR36" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS36" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT36" t="n">
         <v>5.3</v>
@@ -7479,10 +7479,10 @@
         <v>6.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX36" t="n">
         <v>10.5</v>
@@ -7491,32 +7491,32 @@
         <v>12</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA36" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC36" t="n">
         <v>36</v>
       </c>
       <c r="BD36" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE36" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF36" t="n">
         <v>38</v>
       </c>
       <c r="BG36" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>
@@ -7574,13 +7574,13 @@
         <v>3.55</v>
       </c>
       <c r="O37" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P37" t="n">
         <v>1.88</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R37" t="n">
         <v>1.32</v>
@@ -7589,10 +7589,10 @@
         <v>3.6</v>
       </c>
       <c r="T37" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="U37" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V37" t="n">
         <v>1.17</v>
@@ -7661,7 +7661,7 @@
         <v>15.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>38</v>
+        <v>6.8</v>
       </c>
       <c r="AS37" t="n">
         <v>7.6</v>
@@ -7697,7 +7697,7 @@
         <v>16</v>
       </c>
       <c r="BD37" t="n">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="BE37" t="n">
         <v>7.6</v>
@@ -7706,11 +7706,11 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG37" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-19 03:13:00</t>
+          <t>2026-04-19 05:36:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH37"/>
+  <dimension ref="A1:BH38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -841,7 +841,7 @@
         <v>15</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
         <v>70</v>
@@ -859,7 +859,7 @@
         <v>200</v>
       </c>
       <c r="AN2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO2" t="n">
         <v>60</v>
@@ -874,7 +874,7 @@
         <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
         <v>6.8</v>
@@ -886,7 +886,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -898,29 +898,29 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
         <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
         <v>1.36</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H5" t="n">
         <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
         <v>1.49</v>
@@ -1372,25 +1372,25 @@
         <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R5" t="n">
         <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="V5" t="n">
         <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
@@ -1453,10 +1453,10 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
         <v>5.9</v>
@@ -1468,7 +1468,7 @@
         <v>14.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
         <v>9</v>
@@ -1480,7 +1480,7 @@
         <v>16.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
         <v>19</v>
@@ -1489,27 +1489,27 @@
         <v>19</v>
       </c>
       <c r="BD5" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>15.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Finnish Ykkonen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Miedz Legnica</t>
+          <t>KPV</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gornik Leczna</t>
+          <t>FC Jazz</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="G6" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7</v>
+        <v>26</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.88</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.76</v>
+        <v>1.96</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>2.34</v>
+        <v>2.96</v>
       </c>
       <c r="X6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Miedz Legnica</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Gornik Leczna</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.24</v>
+        <v>1.65</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="H7" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>1.39</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.99</v>
+        <v>1.39</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="R7" t="n">
         <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="T7" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.76</v>
+        <v>2.34</v>
       </c>
       <c r="X7" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Z7" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AL7" t="n">
         <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV7" t="n">
         <v>16</v>
       </c>
-      <c r="AO7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AW7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB7" t="n">
         <v>13</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BC7" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.66</v>
+        <v>2.18</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
-        <v>2.52</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="U8" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
-        <v>2.18</v>
+        <v>1.76</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF8" t="n">
         <v>15.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW8" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AX8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AZ8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA8" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY8" t="n">
+      <c r="BB8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG8" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="G9" t="n">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>2.86</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,34 +2139,34 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.66</v>
+        <v>1.26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.04</v>
+        <v>2.66</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="W9" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2223,69 +2223,69 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,67 +2300,67 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="G10" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
         <v>2.72</v>
       </c>
       <c r="I10" t="n">
-        <v>2.86</v>
+        <v>3.9</v>
       </c>
       <c r="J10" t="n">
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>1.69</v>
       </c>
       <c r="T10" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,69 +2417,69 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.86</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="T11" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="U11" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
         <v>15.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO11" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB11" t="n">
         <v>14</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BC11" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>12</v>
+        <v>5.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,42 +2683,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IK Brage</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.68</v>
+        <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="H12" t="n">
-        <v>2.64</v>
+        <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
         <v>3.85</v>
@@ -2727,147 +2727,147 @@
         <v>1.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U12" t="n">
         <v>2.22</v>
       </c>
       <c r="V12" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AJ12" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AK12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL12" t="n">
         <v>36</v>
       </c>
-      <c r="AL12" t="n">
-        <v>46</v>
-      </c>
       <c r="AM12" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV12" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AW12" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.7</v>
+        <v>8.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF12" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:05:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Farul Constanta</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>IK Brage</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X13" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW13" t="n">
         <v>4.6</v>
       </c>
-      <c r="G13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X13" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AX13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BA13" t="n">
-        <v>23</v>
+        <v>4.7</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Porto B</t>
+          <t>Farul Constanta</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leixoes</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.36</v>
+        <v>4.6</v>
       </c>
       <c r="G14" t="n">
-        <v>3.25</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.48</v>
+        <v>1.74</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4</v>
+        <v>1.87</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.84</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>1.32</v>
+        <v>2.66</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>2.16</v>
       </c>
       <c r="W14" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Porto B</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Leixoes</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="G15" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="H15" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="I15" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="J15" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>2.46</v>
+        <v>1.84</v>
       </c>
       <c r="O15" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
         <v>1.48</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.67</v>
-      </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="X15" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.82</v>
+        <v>3.65</v>
       </c>
       <c r="G16" t="n">
-        <v>2.04</v>
+        <v>3.95</v>
       </c>
       <c r="H16" t="n">
-        <v>3.75</v>
+        <v>2.34</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>2.48</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="N16" t="n">
-        <v>5.8</v>
+        <v>2.46</v>
       </c>
       <c r="O16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.17</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.67</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.97</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>28</v>
+        <v>7.2</v>
       </c>
       <c r="Z16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA16" t="n">
         <v>44</v>
       </c>
-      <c r="AA16" t="n">
-        <v>90</v>
-      </c>
       <c r="AB16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG16" t="n">
         <v>17</v>
       </c>
-      <c r="AC16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH16" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AI16" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AJ16" t="n">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="AL16" t="n">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="AM16" t="n">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.6</v>
+        <v>130</v>
       </c>
       <c r="AO16" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19</v>
+        <v>6.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA16" t="n">
         <v>10</v>
       </c>
-      <c r="AU16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX16" t="n">
+      <c r="BB16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE16" t="n">
         <v>11</v>
       </c>
-      <c r="AY16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>4</v>
-      </c>
       <c r="BF16" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>20</v>
+        <v>9.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="G17" t="n">
-        <v>1.54</v>
+        <v>1.99</v>
       </c>
       <c r="H17" t="n">
-        <v>7.4</v>
+        <v>3.75</v>
       </c>
       <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X17" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU17" t="n">
         <v>8</v>
       </c>
-      <c r="J17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="AV17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BB17" t="n">
         <v>15.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>12</v>
       </c>
       <c r="BC17" t="n">
         <v>14.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="BF17" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.55</v>
       </c>
-      <c r="G18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.3</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="V18" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>1.38</v>
+        <v>2.84</v>
       </c>
       <c r="X18" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="Y18" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU18" t="n">
         <v>8.6</v>
       </c>
-      <c r="Z18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AV18" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW18" t="n">
-        <v>25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>21</v>
       </c>
-      <c r="AY18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BA18" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB18" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="BC18" t="n">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE18" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="BF18" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3.55</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>3.6</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>2.38</v>
       </c>
       <c r="J19" t="n">
         <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V19" t="n">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="W19" t="n">
-        <v>1.88</v>
+        <v>1.38</v>
       </c>
       <c r="X19" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="n">
-        <v>17.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG19" t="n">
         <v>15</v>
       </c>
-      <c r="AG19" t="n">
-        <v>13</v>
-      </c>
       <c r="AH19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO19" t="n">
         <v>24</v>
       </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT19" t="n">
         <v>11</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.4</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.65</v>
+        <v>18.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.1</v>
+        <v>42</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.8</v>
+        <v>32</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.75</v>
+        <v>42</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.95</v>
+        <v>32</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.2</v>
+        <v>42</v>
       </c>
       <c r="BF19" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.1</v>
+        <v>22</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="H20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I20" t="n">
+        <v>110</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.1</v>
       </c>
-      <c r="I20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="T20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X20" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR20" t="n">
         <v>4</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X20" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AS20" t="n">
-        <v>48</v>
+        <v>4.3</v>
       </c>
       <c r="AT20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX20" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>15</v>
-      </c>
       <c r="AY20" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>3.8</v>
       </c>
       <c r="BA20" t="n">
-        <v>40</v>
+        <v>4.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>30</v>
+        <v>3.95</v>
       </c>
       <c r="BC20" t="n">
-        <v>24</v>
+        <v>3.9</v>
       </c>
       <c r="BD20" t="n">
-        <v>34</v>
+        <v>4.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>70</v>
+        <v>4.3</v>
       </c>
       <c r="BF20" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="BG20" t="n">
-        <v>28</v>
+        <v>4.3</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Estoril Praia</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>3.35</v>
+        <v>2.52</v>
       </c>
       <c r="H21" t="n">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="I21" t="n">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M21" t="n">
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
         <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="U21" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="V21" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="W21" t="n">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="X21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY21" t="n">
         <v>11</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>12</v>
       </c>
       <c r="AZ21" t="n">
         <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="BC21" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BE21" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.6</v>
+        <v>17.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Estoril Praia</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.46</v>
+        <v>3.15</v>
       </c>
       <c r="G22" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="H22" t="n">
-        <v>3.15</v>
+        <v>2.38</v>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>2.44</v>
       </c>
       <c r="J22" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="P22" t="n">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="U22" t="n">
-        <v>1.66</v>
+        <v>2.18</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="W22" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="X22" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y22" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD22" t="n">
         <v>12</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AE22" t="n">
         <v>27</v>
       </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
       <c r="AF22" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AG22" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH22" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ22" t="n">
         <v>55</v>
       </c>
       <c r="AK22" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG22" t="n">
         <v>16</v>
       </c>
-      <c r="AS22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>29</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>50</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,184 +4817,184 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.94</v>
+        <v>2.46</v>
       </c>
       <c r="G23" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="H23" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="I23" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="K23" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
         <v>1.12</v>
       </c>
       <c r="N23" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="O23" t="n">
         <v>1.51</v>
       </c>
       <c r="P23" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="R23" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="U23" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="V23" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="X23" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z23" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AA23" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
         <v>55</v>
       </c>
       <c r="AK23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL23" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR23" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AV23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G24" t="n">
         <v>3.15</v>
       </c>
-      <c r="G24" t="n">
-        <v>3.45</v>
-      </c>
       <c r="H24" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I24" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J24" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="M24" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.14</v>
+        <v>2.78</v>
       </c>
       <c r="O24" t="n">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="P24" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="R24" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="S24" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X24" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>240</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT24" t="n">
         <v>8.4</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>380</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>6.8</v>
       </c>
       <c r="AU24" t="n">
         <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="AX24" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.1</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.4</v>
+        <v>50</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.4</v>
+        <v>28</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.3</v>
+        <v>25</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.4</v>
+        <v>34</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.5</v>
+        <v>46</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.4</v>
+        <v>27</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.3</v>
+        <v>34</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Caracas</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="G25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.44</v>
       </c>
-      <c r="H25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.84</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="X25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>380</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR25" t="n">
         <v>12</v>
       </c>
-      <c r="Y25" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AS25" t="n">
-        <v>60</v>
+        <v>4.4</v>
       </c>
       <c r="AT25" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY25" t="n">
         <v>12</v>
       </c>
-      <c r="AW25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA25" t="n">
-        <v>55</v>
+        <v>4.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="BD25" t="n">
-        <v>38</v>
+        <v>4.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>110</v>
+        <v>4.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>55</v>
+        <v>4.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,78 +5399,78 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:15:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Zamora FC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Caracas</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="O26" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.42</v>
+        <v>2.14</v>
       </c>
       <c r="T26" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="U26" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z26" t="n">
         <v>1000</v>
@@ -5479,25 +5479,25 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
@@ -5521,37 +5521,37 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AS26" t="n">
         <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW26" t="n">
         <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA26" t="n">
         <v>1.01</v>
@@ -5560,7 +5560,7 @@
         <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD26" t="n">
         <v>1.01</v>
@@ -5569,21 +5569,21 @@
         <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG26" t="n">
         <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,60 +5593,60 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="P27" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.81</v>
+        <v>1.42</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="T27" t="n">
         <v>1.03</v>
@@ -5658,7 +5658,7 @@
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,120 +5787,120 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="G28" t="n">
-        <v>3.55</v>
+        <v>1.62</v>
       </c>
       <c r="H28" t="n">
-        <v>2.68</v>
+        <v>5.7</v>
       </c>
       <c r="I28" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.05</v>
+        <v>9</v>
       </c>
       <c r="L28" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="M28" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>2.24</v>
+        <v>1.72</v>
       </c>
       <c r="O28" t="n">
-        <v>1.7</v>
+        <v>1.31</v>
       </c>
       <c r="P28" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>1.81</v>
       </c>
       <c r="R28" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>6.8</v>
+        <v>1.87</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>1.03</v>
       </c>
       <c r="U28" t="n">
-        <v>1.65</v>
+        <v>1.03</v>
       </c>
       <c r="V28" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.39</v>
+        <v>2.6</v>
       </c>
       <c r="X28" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
         <v>1000</v>
@@ -5909,69 +5909,69 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="G29" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="H29" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="J29" t="n">
         <v>2.76</v>
       </c>
       <c r="K29" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="L29" t="n">
         <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="O29" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="P29" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="R29" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S29" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="U29" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="V29" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="W29" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="X29" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="Y29" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AF29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH29" t="n">
         <v>28</v>
       </c>
       <c r="AI29" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="AK29" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AL29" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN29" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
         <v>6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AR29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE29" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.65</v>
+        <v>2.56</v>
       </c>
       <c r="G30" t="n">
-        <v>1.86</v>
+        <v>2.86</v>
       </c>
       <c r="H30" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="I30" t="n">
-        <v>8.4</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="K30" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>3.05</v>
+        <v>1.37</v>
       </c>
       <c r="O30" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="P30" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>2.42</v>
       </c>
       <c r="R30" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S30" t="n">
-        <v>3.7</v>
+        <v>2.42</v>
       </c>
       <c r="T30" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="V30" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="W30" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB30" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF30" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AG30" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX30" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB30" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF30" t="n">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,186 +6374,186 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portuguesa FC</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G31" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H31" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="I31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY31" t="n">
         <v>7.6</v>
       </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ31" t="n">
+      <c r="AZ31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB31" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BC31" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
         <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BG31" t="n">
         <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,191 +6563,191 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Portuguesa FC</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="G32" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="H32" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
       </c>
       <c r="M32" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.7</v>
+        <v>1.68</v>
       </c>
       <c r="O32" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="P32" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="R32" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="T32" t="n">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="U32" t="n">
-        <v>1.82</v>
+        <v>1.03</v>
       </c>
       <c r="V32" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="W32" t="n">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="X32" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="O33" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.18</v>
       </c>
-      <c r="S33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,70 +6956,70 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="P34" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.94</v>
+        <v>1.51</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>3.45</v>
+        <v>1.51</v>
       </c>
       <c r="T34" t="n">
-        <v>2.08</v>
+        <v>1.03</v>
       </c>
       <c r="U34" t="n">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="V34" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
         <v>1000</v>
@@ -7031,10 +7031,10 @@
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
         <v>1000</v>
@@ -7043,10 +7043,10 @@
         <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
         <v>1000</v>
@@ -7055,10 +7055,10 @@
         <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
         <v>1000</v>
@@ -7067,75 +7067,75 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
         <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>180</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>140</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>180</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
         <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,191 +7145,191 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="G35" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="H35" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="I35" t="n">
+        <v>14</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
         <v>8</v>
       </c>
-      <c r="J35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N35" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X35" t="n">
+      <c r="AC35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK35" t="n">
         <v>21</v>
       </c>
-      <c r="Y35" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG35" t="n">
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH35" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
+      <c r="AQ35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU35" t="n">
         <v>8.4</v>
       </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ35" t="n">
+      <c r="AV35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF35" t="n">
         <v>6</v>
       </c>
-      <c r="AR35" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG35" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,191 +7339,191 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:45:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="G36" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="H36" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="O36" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="P36" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.45</v>
+        <v>1.65</v>
       </c>
       <c r="R36" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X36" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX36" t="n">
         <v>8</v>
       </c>
-      <c r="T36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X36" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="AY36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD36" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC36" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>430</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV36" t="n">
+      <c r="BE36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF36" t="n">
         <v>6.2</v>
       </c>
-      <c r="AW36" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>38</v>
-      </c>
       <c r="BG36" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-19 05:36:31</t>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,184 +7533,378 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:45:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>CA Huracan</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="G37" t="n">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="H37" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="I37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
         <v>6.6</v>
       </c>
-      <c r="J37" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X37" t="n">
+      <c r="AC37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG37" t="n">
         <v>16</v>
       </c>
-      <c r="Y37" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AH37" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AI37" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AJ37" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
-        <v>160</v>
+        <v>430</v>
       </c>
       <c r="AN37" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>11.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ37" t="n">
-        <v>15.5</v>
+        <v>8.6</v>
       </c>
       <c r="AR37" t="n">
         <v>6.8</v>
       </c>
       <c r="AS37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-19 07:59:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X38" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS38" t="n">
         <v>7.6</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AT38" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AU38" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AV38" t="n">
         <v>19</v>
       </c>
-      <c r="AW37" t="n">
+      <c r="AW38" t="n">
         <v>7.4</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="AX38" t="n">
         <v>8.4</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="AY38" t="n">
         <v>8.6</v>
       </c>
-      <c r="AZ37" t="n">
+      <c r="AZ38" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA37" t="n">
+      <c r="BA38" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BB38" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC37" t="n">
+      <c r="BC38" t="n">
         <v>16</v>
       </c>
-      <c r="BD37" t="n">
+      <c r="BD38" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE37" t="n">
+      <c r="BE38" t="n">
         <v>7.6</v>
       </c>
-      <c r="BF37" t="n">
+      <c r="BF38" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BG37" t="n">
+      <c r="BG38" t="n">
         <v>7.4</v>
       </c>
-      <c r="BH37" t="inlineStr">
-        <is>
-          <t>2026-04-19 05:36:31</t>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-19 07:59:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
         <v>2.38</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
         <v>1.45</v>
@@ -1163,7 +1163,7 @@
         <v>5.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1175,13 +1175,13 @@
         <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
         <v>1.73</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
         <v>2.8</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -1354,31 +1354,31 @@
         <v>4.8</v>
       </c>
       <c r="K5" t="n">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="O5" t="n">
         <v>1.19</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R5" t="n">
         <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
@@ -1936,7 +1936,7 @@
         <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,22 +1945,22 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="O8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1972,7 +1972,7 @@
         <v>1.1</v>
       </c>
       <c r="W8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H9" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
@@ -2145,10 +2145,10 @@
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
@@ -2157,16 +2157,16 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U9" t="n">
         <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
         <v>17.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -2309,58 +2309,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="G10" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="J10" t="n">
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>1.98</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
         <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2414,7 +2414,7 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP10" t="n">
         <v>1.03</v>
@@ -2468,11 +2468,11 @@
         <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -2524,25 +2524,25 @@
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.39</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>1.39</v>
+        <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="T11" t="n">
         <v>1.75</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J12" t="n">
         <v>3.55</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.5</v>
       </c>
       <c r="K12" t="n">
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="X12" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
         <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI12" t="n">
         <v>55</v>
       </c>
-      <c r="AF12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH12" t="n">
+      <c r="AJ12" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC12" t="n">
         <v>20</v>
       </c>
-      <c r="AI12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BD12" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G13" t="n">
         <v>1.85</v>
@@ -2900,7 +2900,7 @@
         <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J13" t="n">
         <v>4.1</v>
@@ -2921,16 +2921,16 @@
         <v>1.18</v>
       </c>
       <c r="P13" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T13" t="n">
         <v>1.61</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>2.08</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="H14" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="I14" t="n">
         <v>3.8</v>
@@ -3100,7 +3100,7 @@
         <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,7 +3109,7 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.22</v>
@@ -3133,16 +3133,16 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
@@ -3151,25 +3151,25 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3187,68 +3187,68 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="G15" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H15" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="J15" t="n">
-        <v>1.09</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3351,13 +3351,13 @@
         <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE15" t="n">
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
         <v>1000</v>
@@ -3390,37 +3390,37 @@
         <v>4.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR15" t="n">
         <v>4.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT15" t="n">
         <v>9.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AV15" t="n">
         <v>4.1</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="n">
         <v>4.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AZ15" t="n">
         <v>4.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB15" t="n">
         <v>5.1</v>
@@ -3429,20 +3429,20 @@
         <v>4.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE15" t="n">
         <v>5.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BG15" t="n">
         <v>4.7</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -3473,28 +3473,28 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
         <v>4</v>
@@ -3503,10 +3503,10 @@
         <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
@@ -3521,10 +3521,10 @@
         <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
@@ -3533,13 +3533,13 @@
         <v>15.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA16" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AC16" t="n">
         <v>8.199999999999999</v>
@@ -3551,7 +3551,7 @@
         <v>40</v>
       </c>
       <c r="AF16" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AG16" t="n">
         <v>11.5</v>
@@ -3560,37 +3560,37 @@
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ16" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AT16" t="n">
         <v>9.4</v>
@@ -3602,7 +3602,7 @@
         <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>13</v>
@@ -3611,32 +3611,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BE16" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF16" t="n">
         <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="G17" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="I17" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
         <v>3.7</v>
@@ -3691,13 +3691,13 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
         <v>1.88</v>
@@ -3715,19 +3715,19 @@
         <v>2.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA17" t="n">
         <v>46</v>
@@ -3739,7 +3739,7 @@
         <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE17" t="n">
         <v>34</v>
@@ -3751,10 +3751,10 @@
         <v>14.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ17" t="n">
         <v>48</v>
@@ -3784,10 +3784,10 @@
         <v>14.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AU17" t="n">
         <v>6.4</v>
@@ -3796,41 +3796,41 @@
         <v>9.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF17" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>18</v>
       </c>
       <c r="BG17" t="n">
         <v>18</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>5.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="I18" t="n">
         <v>1.85</v>
@@ -3891,10 +3891,10 @@
         <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R18" t="n">
         <v>1.42</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -4055,91 +4055,91 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="G19" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H19" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>3.05</v>
       </c>
       <c r="K19" t="n">
-        <v>5.8</v>
+        <v>3.65</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>1.84</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P19" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="R19" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9</v>
+        <v>3.65</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
@@ -4157,68 +4157,68 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -4270,13 +4270,13 @@
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
         <v>1.92</v>
       </c>
       <c r="O20" t="n">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="P20" t="n">
         <v>1.92</v>
@@ -4285,7 +4285,7 @@
         <v>1.57</v>
       </c>
       <c r="R20" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
         <v>2.38</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -4446,22 +4446,22 @@
         <v>1.86</v>
       </c>
       <c r="G21" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H21" t="n">
         <v>3.7</v>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M21" t="n">
         <v>1.03</v>
@@ -4473,28 +4473,28 @@
         <v>1.17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="Q21" t="n">
         <v>1.53</v>
       </c>
       <c r="R21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S21" t="n">
         <v>2.26</v>
       </c>
       <c r="T21" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>2.86</v>
       </c>
       <c r="V21" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>34</v>
@@ -4545,7 +4545,7 @@
         <v>70</v>
       </c>
       <c r="AN21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO21" t="n">
         <v>34</v>
@@ -4554,10 +4554,10 @@
         <v>19.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS21" t="n">
         <v>4.1</v>
@@ -4566,28 +4566,28 @@
         <v>10.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AV21" t="n">
         <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX21" t="n">
         <v>11</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
         <v>11.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BC21" t="n">
         <v>12.5</v>
@@ -4596,7 +4596,7 @@
         <v>18.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF21" t="n">
         <v>6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -4640,25 +4640,25 @@
         <v>3.65</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H22" t="n">
         <v>2.34</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J22" t="n">
         <v>2.98</v>
       </c>
       <c r="K22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="N22" t="n">
         <v>2.46</v>
@@ -4673,19 +4673,19 @@
         <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S22" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="V22" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W22" t="n">
         <v>1.34</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -4834,10 +4834,10 @@
         <v>1.53</v>
       </c>
       <c r="G23" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I23" t="n">
         <v>8</v>
@@ -4846,7 +4846,7 @@
         <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
         <v>1.36</v>
@@ -4861,10 +4861,10 @@
         <v>1.34</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R23" t="n">
         <v>1.35</v>
@@ -4873,7 +4873,7 @@
         <v>3.55</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
         <v>1.84</v>
@@ -4882,7 +4882,7 @@
         <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X23" t="n">
         <v>15.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -5025,55 +5025,55 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="G24" t="n">
         <v>2.12</v>
       </c>
       <c r="H24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
         <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>1.31</v>
+        <v>3.6</v>
       </c>
       <c r="O24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
-        <v>1.3</v>
+        <v>1.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.32</v>
+        <v>1.92</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="T24" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="U24" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W24" t="n">
         <v>1.89</v>
@@ -5127,7 +5127,7 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
@@ -5145,7 +5145,7 @@
         <v>4.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
         <v>7</v>
@@ -5166,7 +5166,7 @@
         <v>3.85</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB24" t="n">
         <v>4</v>
@@ -5178,7 +5178,7 @@
         <v>4.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF24" t="n">
         <v>12</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -5231,10 +5231,10 @@
         <v>2.36</v>
       </c>
       <c r="J25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.4</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.45</v>
       </c>
       <c r="L25" t="n">
         <v>1.49</v>
@@ -5243,7 +5243,7 @@
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
         <v>1.42</v>
@@ -5252,7 +5252,7 @@
         <v>1.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R25" t="n">
         <v>1.28</v>
@@ -5360,7 +5360,7 @@
         <v>18.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BB25" t="n">
         <v>32</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
         <v>2.52</v>
       </c>
       <c r="H26" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I26" t="n">
         <v>3.2</v>
@@ -5449,13 +5449,13 @@
         <v>1.95</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T26" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U26" t="n">
         <v>2.26</v>
@@ -5464,7 +5464,7 @@
         <v>1.45</v>
       </c>
       <c r="W26" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X26" t="n">
         <v>14</v>
@@ -5482,7 +5482,7 @@
         <v>11.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD26" t="n">
         <v>13.5</v>
@@ -5491,7 +5491,7 @@
         <v>32</v>
       </c>
       <c r="AF26" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
         <v>11.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
         <v>1.76</v>
       </c>
       <c r="U27" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V27" t="n">
         <v>1.69</v>
@@ -5673,7 +5673,7 @@
         <v>34</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC27" t="n">
         <v>8</v>
@@ -5700,13 +5700,13 @@
         <v>55</v>
       </c>
       <c r="AK27" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL27" t="n">
         <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN27" t="n">
         <v>34</v>
@@ -5724,7 +5724,7 @@
         <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT27" t="n">
         <v>11</v>
@@ -5748,29 +5748,29 @@
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG27" t="n">
         <v>16</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G28" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="H28" t="n">
         <v>3.25</v>
       </c>
       <c r="I28" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
         <v>2.92</v>
       </c>
       <c r="K28" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="L28" t="n">
         <v>1.47</v>
@@ -5831,7 +5831,7 @@
         <v>1.52</v>
       </c>
       <c r="P28" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q28" t="n">
         <v>2.52</v>
@@ -5849,10 +5849,10 @@
         <v>1.79</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W28" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X28" t="n">
         <v>10.5</v>
@@ -5918,7 +5918,7 @@
         <v>16</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT28" t="n">
         <v>6</v>
@@ -5930,7 +5930,7 @@
         <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX28" t="n">
         <v>11</v>
@@ -5942,29 +5942,29 @@
         <v>16</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -6207,19 +6207,19 @@
         <v>2.92</v>
       </c>
       <c r="L30" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="N30" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="O30" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="P30" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Q30" t="n">
         <v>3.3</v>
@@ -6228,7 +6228,7 @@
         <v>1.12</v>
       </c>
       <c r="S30" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="T30" t="n">
         <v>2.44</v>
@@ -6243,7 +6243,7 @@
         <v>1.4</v>
       </c>
       <c r="X30" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y30" t="n">
         <v>8.4</v>
@@ -6306,7 +6306,7 @@
         <v>12</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT30" t="n">
         <v>6.8</v>
@@ -6318,7 +6318,7 @@
         <v>13</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX30" t="n">
         <v>15</v>
@@ -6330,29 +6330,29 @@
         <v>4.1</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB30" t="n">
         <v>4.4</v>
       </c>
       <c r="BC30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD30" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BE30" t="n">
         <v>4.5</v>
       </c>
-      <c r="BE30" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -6383,46 +6383,46 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="G31" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.45</v>
-      </c>
-      <c r="I31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K31" t="n">
-        <v>110</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O31" t="n">
         <v>1.47</v>
       </c>
-      <c r="O31" t="n">
-        <v>1.1</v>
-      </c>
       <c r="P31" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>2.14</v>
+        <v>4.8</v>
       </c>
       <c r="T31" t="n">
         <v>2</v>
@@ -6431,7 +6431,7 @@
         <v>1.7</v>
       </c>
       <c r="V31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
         <v>1.7</v>
@@ -6500,7 +6500,7 @@
         <v>19.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT31" t="n">
         <v>5.8</v>
@@ -6512,7 +6512,7 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX31" t="n">
         <v>9.800000000000001</v>
@@ -6524,29 +6524,29 @@
         <v>15.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC31" t="n">
         <v>21</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF31" t="n">
         <v>21</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -6879,52 +6879,52 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF33" t="n">
         <v>1.01</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -6965,46 +6965,46 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="H34" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I34" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="J34" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="K34" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="L34" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N34" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="O34" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="T34" t="n">
         <v>2.32</v>
@@ -7013,10 +7013,10 @@
         <v>1.65</v>
       </c>
       <c r="V34" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="X34" t="n">
         <v>7</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -7162,19 +7162,19 @@
         <v>2.56</v>
       </c>
       <c r="G35" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="H35" t="n">
         <v>3.25</v>
       </c>
       <c r="I35" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
-        <v>1.93</v>
+        <v>2.52</v>
       </c>
       <c r="K35" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7183,34 +7183,34 @@
         <v>1.12</v>
       </c>
       <c r="N35" t="n">
-        <v>1.37</v>
+        <v>2.46</v>
       </c>
       <c r="O35" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="P35" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="R35" t="n">
         <v>1.17</v>
       </c>
       <c r="S35" t="n">
-        <v>2.42</v>
+        <v>4.8</v>
       </c>
       <c r="T35" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="U35" t="n">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="V35" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="W35" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="X35" t="n">
         <v>8.6</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>1.65</v>
       </c>
       <c r="G36" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="H36" t="n">
         <v>5.2</v>
@@ -7380,7 +7380,7 @@
         <v>3.1</v>
       </c>
       <c r="O36" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P36" t="n">
         <v>1.72</v>
@@ -7404,7 +7404,7 @@
         <v>1.13</v>
       </c>
       <c r="W36" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7464,13 +7464,13 @@
         <v>8.6</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT36" t="n">
         <v>5.2</v>
@@ -7479,10 +7479,10 @@
         <v>6.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX36" t="n">
         <v>6.8</v>
@@ -7491,32 +7491,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB36" t="n">
         <v>12.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF36" t="n">
         <v>10</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G38" t="n">
         <v>1.91</v>
@@ -7759,7 +7759,7 @@
         <v>4.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M38" t="n">
         <v>1.07</v>
@@ -7783,13 +7783,13 @@
         <v>3.3</v>
       </c>
       <c r="T38" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U38" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V38" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W38" t="n">
         <v>2.1</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <v>1.39</v>
       </c>
       <c r="G40" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H40" t="n">
         <v>8.800000000000001</v>
@@ -8144,10 +8144,10 @@
         <v>4.4</v>
       </c>
       <c r="K40" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L40" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M40" t="n">
         <v>1.07</v>
@@ -8180,7 +8180,7 @@
         <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="X40" t="n">
         <v>17.5</v>
@@ -8243,10 +8243,10 @@
         <v>21</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT40" t="n">
         <v>5.2</v>
@@ -8255,10 +8255,10 @@
         <v>8.4</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX40" t="n">
         <v>5.7</v>
@@ -8267,10 +8267,10 @@
         <v>8</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB40" t="n">
         <v>8.4</v>
@@ -8279,20 +8279,20 @@
         <v>12.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF40" t="n">
         <v>6</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
         <v>1.6</v>
       </c>
       <c r="H41" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I41" t="n">
         <v>8.199999999999999</v>
@@ -8356,7 +8356,7 @@
         <v>2.08</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="R41" t="n">
         <v>1.41</v>
@@ -8461,7 +8461,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ41" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="BA41" t="n">
         <v>7.4</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
         <v>2.8</v>
       </c>
       <c r="K42" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -8541,10 +8541,10 @@
         <v>1.18</v>
       </c>
       <c r="N42" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O42" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="P42" t="n">
         <v>1.36</v>
@@ -8556,10 +8556,10 @@
         <v>1.12</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="T42" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U42" t="n">
         <v>1.55</v>
@@ -8568,13 +8568,13 @@
         <v>1.27</v>
       </c>
       <c r="W42" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X42" t="n">
         <v>6.4</v>
       </c>
       <c r="Y42" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z42" t="n">
         <v>1000</v>
@@ -8583,25 +8583,25 @@
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC42" t="n">
         <v>7.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE42" t="n">
         <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG42" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI42" t="n">
         <v>180</v>
@@ -8631,56 +8631,56 @@
         <v>8.6</v>
       </c>
       <c r="AR42" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU42" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS42" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AV42" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AW42" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="AX42" t="n">
         <v>10.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BA42" t="n">
-        <v>8.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BB42" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BC42" t="n">
         <v>36</v>
       </c>
       <c r="BD42" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BE42" t="n">
-        <v>8.4</v>
+        <v>95</v>
       </c>
       <c r="BF42" t="n">
         <v>38</v>
       </c>
       <c r="BG42" t="n">
-        <v>8.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G43" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="H43" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I43" t="n">
         <v>6.6</v>
       </c>
       <c r="J43" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K43" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L43" t="n">
         <v>1.36</v>
@@ -8744,16 +8744,16 @@
         <v>1.87</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R43" t="n">
         <v>1.32</v>
       </c>
       <c r="S43" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T43" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="U43" t="n">
         <v>1.93</v>
@@ -8762,7 +8762,7 @@
         <v>1.17</v>
       </c>
       <c r="W43" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X43" t="n">
         <v>16</v>
@@ -8780,7 +8780,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD43" t="n">
         <v>24</v>
@@ -8792,7 +8792,7 @@
         <v>10.5</v>
       </c>
       <c r="AG43" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH43" t="n">
         <v>23</v>
@@ -8825,10 +8825,10 @@
         <v>15.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>6.8</v>
+        <v>38</v>
       </c>
       <c r="AS43" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT43" t="n">
         <v>6.8</v>
@@ -8840,7 +8840,7 @@
         <v>19</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX43" t="n">
         <v>8.4</v>
@@ -8852,7 +8852,7 @@
         <v>18.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB43" t="n">
         <v>14.5</v>
@@ -8861,20 +8861,20 @@
         <v>16</v>
       </c>
       <c r="BD43" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BE43" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF43" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG43" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-19 10:23:02</t>
+          <t>2026-04-19 12:41:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH43"/>
+  <dimension ref="A1:BH45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,7 +802,7 @@
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V2" t="n">
         <v>1.51</v>
@@ -874,19 +874,19 @@
         <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
         <v>6.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -901,26 +901,26 @@
         <v>4.8</v>
       </c>
       <c r="BB2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC2" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
         <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG2" t="n">
         <v>4.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="H3" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="K3" t="n">
-        <v>34</v>
+        <v>8.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>2.38</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.13</v>
       </c>
       <c r="P3" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
         <v>1.37</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="S3" t="n">
         <v>1.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1029,10 +1029,10 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH3" t="n">
         <v>1000</v>
@@ -1041,10 +1041,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1053,7 +1053,7 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
@@ -1071,10 +1071,10 @@
         <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AV3" t="n">
         <v>1.03</v>
@@ -1083,10 +1083,10 @@
         <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>1.03</v>
@@ -1095,10 +1095,10 @@
         <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
         <v>1.03</v>
@@ -1107,14 +1107,14 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>220</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G4" t="n">
         <v>1.45</v>
@@ -1154,7 +1154,7 @@
         <v>8.4</v>
       </c>
       <c r="I4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
         <v>4.7</v>
@@ -1169,7 +1169,7 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.25</v>
@@ -1193,7 +1193,7 @@
         <v>1.85</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
         <v>3.2</v>
@@ -1202,7 +1202,7 @@
         <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z4" t="n">
         <v>100</v>
@@ -1211,25 +1211,25 @@
         <v>390</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4" t="n">
         <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE4" t="n">
         <v>180</v>
       </c>
       <c r="AF4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
         <v>150</v>
@@ -1247,7 +1247,7 @@
         <v>180</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AO4" t="n">
         <v>240</v>
@@ -1256,13 +1256,13 @@
         <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
         <v>7.4</v>
@@ -1271,10 +1271,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
         <v>7.4</v>
@@ -1283,10 +1283,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
@@ -1295,20 +1295,20 @@
         <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
         <v>3.15</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.49</v>
@@ -1754,7 +1754,7 @@
         <v>2.96</v>
       </c>
       <c r="O7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
         <v>1.67</v>
@@ -1772,7 +1772,7 @@
         <v>1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V7" t="n">
         <v>1.24</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G8" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="H8" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,34 +1945,34 @@
         <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>2.34</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="S8" t="n">
-        <v>1.14</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2023,68 +2023,68 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -2118,28 +2118,28 @@
         <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="H9" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="I9" t="n">
         <v>3.65</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
@@ -2154,7 +2154,7 @@
         <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
         <v>1.69</v>
@@ -2166,7 +2166,7 @@
         <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X9" t="n">
         <v>17.5</v>
@@ -2223,10 +2223,10 @@
         <v>36</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
         <v>1.03</v>
@@ -2235,25 +2235,25 @@
         <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW9" t="n">
         <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
         <v>1.03</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G10" t="n">
         <v>6.2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="I10" t="n">
         <v>1.83</v>
@@ -2327,19 +2327,19 @@
         <v>4.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
         <v>1.66</v>
@@ -2348,13 +2348,13 @@
         <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="T10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
         <v>2.2</v>
@@ -2417,37 +2417,37 @@
         <v>10.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AX10" t="n">
         <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>1.03</v>
@@ -2465,14 +2465,14 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -2521,25 +2521,25 @@
         <v>4.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P11" t="n">
         <v>2.22</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S11" t="n">
         <v>2.76</v>
@@ -2557,7 +2557,7 @@
         <v>2.34</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
         <v>26</v>
@@ -2620,7 +2620,7 @@
         <v>4.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
         <v>8</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
         <v>3.9</v>
@@ -2715,25 +2715,25 @@
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
         <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
         <v>1.94</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
         <v>3.4</v>
@@ -2742,13 +2742,13 @@
         <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
         <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X12" t="n">
         <v>14</v>
@@ -2772,10 +2772,10 @@
         <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG12" t="n">
         <v>11</v>
@@ -2814,19 +2814,19 @@
         <v>24</v>
       </c>
       <c r="AS12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU12" t="n">
         <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX12" t="n">
         <v>12.5</v>
@@ -2841,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="BC12" t="n">
         <v>20</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G13" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
         <v>5.4</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
@@ -2915,7 +2915,7 @@
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O13" t="n">
         <v>1.18</v>
@@ -2942,7 +2942,7 @@
         <v>1.22</v>
       </c>
       <c r="W13" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
         <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,34 +3109,34 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="S14" t="n">
-        <v>1.69</v>
+        <v>2.86</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X14" t="n">
         <v>22</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -3315,7 +3315,7 @@
         <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
         <v>3.05</v>
@@ -3327,10 +3327,10 @@
         <v>2.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3357,7 +3357,7 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT15" t="n">
         <v>9.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW15" t="n">
         <v>5</v>
       </c>
       <c r="AX15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>4.5</v>
       </c>
-      <c r="AY15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BA15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF15" t="n">
         <v>14.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -3476,22 +3476,22 @@
         <v>2.36</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I16" t="n">
         <v>3.45</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
@@ -3503,34 +3503,34 @@
         <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
         <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X16" t="n">
         <v>16</v>
       </c>
       <c r="Y16" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
         <v>30</v>
@@ -3539,13 +3539,13 @@
         <v>60</v>
       </c>
       <c r="AB16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
         <v>40</v>
@@ -3557,25 +3557,25 @@
         <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI16" t="n">
         <v>46</v>
       </c>
       <c r="AJ16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
         <v>42</v>
@@ -3590,7 +3590,7 @@
         <v>20</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT16" t="n">
         <v>9.4</v>
@@ -3599,13 +3599,13 @@
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY16" t="n">
         <v>9.800000000000001</v>
@@ -3614,29 +3614,29 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD16" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BE16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BF16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H17" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="I17" t="n">
         <v>2.72</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
         <v>3.7</v>
@@ -3700,58 +3700,58 @@
         <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
         <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH17" t="n">
         <v>17.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
         <v>44</v>
@@ -3760,7 +3760,7 @@
         <v>48</v>
       </c>
       <c r="AK17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL17" t="n">
         <v>46</v>
@@ -3772,65 +3772,65 @@
         <v>28</v>
       </c>
       <c r="AO17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>14.5</v>
       </c>
-      <c r="AS17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BA17" t="n">
-        <v>5.3</v>
+        <v>30</v>
       </c>
       <c r="BB17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.6</v>
+        <v>36</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.9</v>
+        <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>4.6</v>
       </c>
       <c r="G18" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H18" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="I18" t="n">
         <v>1.85</v>
@@ -3888,7 +3888,7 @@
         <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P18" t="n">
         <v>2.1</v>
@@ -3900,7 +3900,7 @@
         <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
         <v>1.75</v>
@@ -3927,7 +3927,7 @@
         <v>23</v>
       </c>
       <c r="AB18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC18" t="n">
         <v>11.5</v>
@@ -3993,7 +3993,7 @@
         <v>15</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AY18" t="n">
         <v>14</v>
@@ -4002,7 +4002,7 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB18" t="n">
         <v>4.1</v>
@@ -4014,17 +4014,17 @@
         <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF18" t="n">
         <v>4</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>2.66</v>
       </c>
       <c r="G19" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="H19" t="n">
         <v>2.7</v>
@@ -4067,31 +4067,31 @@
         <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.34</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
         <v>3.65</v>
@@ -4100,19 +4100,19 @@
         <v>1.78</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V19" t="n">
         <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
         <v>22</v>
@@ -4124,7 +4124,7 @@
         <v>12.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD19" t="n">
         <v>15</v>
@@ -4157,7 +4157,7 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
@@ -4172,7 +4172,7 @@
         <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
@@ -4184,48 +4184,48 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX19" t="n">
         <v>14</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC19" t="n">
         <v>4.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Saudi 1st Division</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,55 +4240,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Al-Ula FC</t>
+          <t>Sporting Lisbon B</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Jabalain</t>
+          <t>Felgueiras</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>2.64</v>
       </c>
       <c r="G20" t="n">
-        <v>1.84</v>
+        <v>3.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>2.52</v>
       </c>
       <c r="I20" t="n">
-        <v>7.8</v>
+        <v>3.25</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="K20" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4297,10 +4297,10 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>2.18</v>
+        <v>1.42</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Saudi 1st Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al-Ula FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Al Jabalain</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="G21" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="H21" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K21" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>2.78</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="R21" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="U21" t="n">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="X21" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="Y21" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z21" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AA21" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC21" t="n">
         <v>13</v>
       </c>
-      <c r="AD21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE21" t="n">
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG21" t="n">
         <v>48</v>
       </c>
-      <c r="AF21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.65</v>
+        <v>1.85</v>
       </c>
       <c r="G22" t="n">
-        <v>3.95</v>
+        <v>1.96</v>
       </c>
       <c r="H22" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>2.48</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>2.46</v>
+        <v>6.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="P22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T22" t="n">
         <v>1.48</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X22" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF22" t="n">
         <v>6</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG22" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mirandes</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.53</v>
+        <v>3.65</v>
       </c>
       <c r="G23" t="n">
-        <v>1.57</v>
+        <v>3.95</v>
       </c>
       <c r="H23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y23" t="n">
         <v>7.2</v>
       </c>
-      <c r="I23" t="n">
+      <c r="Z23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX23" t="n">
         <v>8</v>
       </c>
-      <c r="J23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="X23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AY23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG23" t="n">
+      <c r="BC23" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN23" t="n">
+      <c r="BE23" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF23" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>8.6</v>
       </c>
       <c r="BG23" t="n">
         <v>9.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>French Ligue 2</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.96</v>
+        <v>1.54</v>
       </c>
       <c r="G24" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="I24" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="V24" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="W24" t="n">
-        <v>1.89</v>
+        <v>2.74</v>
       </c>
       <c r="X24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG24" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AH24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN24" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AO24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>21</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ24" t="n">
+      <c r="BA24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB24" t="n">
         <v>12</v>
       </c>
-      <c r="AR24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX24" t="n">
+      <c r="BC24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE24" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BF24" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>French Ligue 2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.55</v>
+        <v>1.97</v>
       </c>
       <c r="G25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J25" t="n">
         <v>3.6</v>
       </c>
-      <c r="H25" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S25" t="n">
         <v>3.35</v>
       </c>
-      <c r="K25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.28</v>
       </c>
-      <c r="S25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.73</v>
-      </c>
       <c r="W25" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="X25" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
         <v>11</v>
       </c>
-      <c r="Y25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>10</v>
-      </c>
       <c r="AQ25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT25" t="n">
         <v>8</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>11</v>
       </c>
       <c r="AU25" t="n">
         <v>7</v>
       </c>
       <c r="AV25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX25" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>22</v>
-      </c>
       <c r="AY25" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC25" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA25" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>42</v>
-      </c>
       <c r="BD25" t="n">
-        <v>32</v>
+        <v>4.3</v>
       </c>
       <c r="BE25" t="n">
-        <v>42</v>
+        <v>4.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="BG25" t="n">
-        <v>22</v>
+        <v>4.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52</v>
+        <v>3.6</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1</v>
+        <v>2.34</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>2.36</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O26" t="n">
         <v>1.42</v>
       </c>
-      <c r="M26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.31</v>
-      </c>
       <c r="P26" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="Q26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T26" t="n">
         <v>1.95</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.74</v>
-      </c>
       <c r="U26" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="V26" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="W26" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AB26" t="n">
         <v>11.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB26" t="n">
         <v>32</v>
       </c>
-      <c r="AF26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>30</v>
-      </c>
       <c r="BC26" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="BD26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE26" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="BF26" t="n">
-        <v>17.5</v>
+        <v>46</v>
       </c>
       <c r="BG26" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Estoril Praia</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I27" t="n">
         <v>3.15</v>
       </c>
-      <c r="G27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.44</v>
-      </c>
       <c r="J27" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U27" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V27" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="W27" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="X27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN27" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="AO27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP27" t="n">
         <v>14</v>
       </c>
-      <c r="AC27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="AT27" t="n">
         <v>11</v>
       </c>
       <c r="AU27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AX27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AY27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ27" t="n">
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="BB27" t="n">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="BC27" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.6</v>
+        <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>10.5</v>
+        <v>60</v>
       </c>
       <c r="BF27" t="n">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Moreirense</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Estoril Praia</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H28" t="n">
         <v>2.4</v>
       </c>
-      <c r="G28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H28" t="n">
-        <v>3.25</v>
-      </c>
       <c r="I28" t="n">
-        <v>3.9</v>
+        <v>2.44</v>
       </c>
       <c r="J28" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="P28" t="n">
-        <v>1.54</v>
+        <v>1.94</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.52</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="U28" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.34</v>
+        <v>1.69</v>
       </c>
       <c r="W28" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="X28" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y28" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD28" t="n">
         <v>12</v>
       </c>
-      <c r="Z28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF28" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AG28" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH28" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ28" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK28" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL28" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN28" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP28" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG28" t="n">
         <v>16</v>
       </c>
-      <c r="AS28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,36 +5981,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.98</v>
+        <v>2.44</v>
       </c>
       <c r="G29" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="H29" t="n">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="I29" t="n">
-        <v>2.94</v>
+        <v>3.85</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K29" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L29" t="n">
         <v>1.47</v>
@@ -6019,19 +6019,19 @@
         <v>1.12</v>
       </c>
       <c r="N29" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P29" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="Q29" t="n">
         <v>2.52</v>
       </c>
       <c r="R29" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S29" t="n">
         <v>5.1</v>
@@ -6040,125 +6040,125 @@
         <v>2.04</v>
       </c>
       <c r="U29" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="V29" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="W29" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="X29" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="Z29" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AA29" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL29" t="n">
         <v>80</v>
       </c>
-      <c r="AF29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>65</v>
-      </c>
       <c r="AM29" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AS29" t="n">
-        <v>24</v>
+        <v>4.3</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV29" t="n">
         <v>11</v>
       </c>
       <c r="AW29" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="AX29" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AY29" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA29" t="n">
         <v>50</v>
       </c>
       <c r="BB29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC29" t="n">
-        <v>25</v>
+        <v>4.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>34</v>
+        <v>4.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>46</v>
+        <v>4.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>27</v>
+        <v>4.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>34</v>
+        <v>4.3</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G30" t="n">
         <v>3.15</v>
       </c>
-      <c r="G30" t="n">
-        <v>3.5</v>
-      </c>
       <c r="H30" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="I30" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J30" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="L30" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="M30" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.14</v>
+        <v>2.78</v>
       </c>
       <c r="O30" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="P30" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="R30" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="S30" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.44</v>
+        <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="V30" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W30" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X30" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT30" t="n">
         <v>8.4</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>380</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>6.8</v>
       </c>
       <c r="AU30" t="n">
         <v>6.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="AX30" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.1</v>
+        <v>19</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.4</v>
+        <v>50</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.4</v>
+        <v>28</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.3</v>
+        <v>25</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.4</v>
+        <v>34</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.5</v>
+        <v>46</v>
       </c>
       <c r="BF30" t="n">
-        <v>4.4</v>
+        <v>27</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.3</v>
+        <v>34</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Caracas</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>2.42</v>
+        <v>3.5</v>
       </c>
       <c r="H31" t="n">
-        <v>3.65</v>
+        <v>2.78</v>
       </c>
       <c r="I31" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>380</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS31" t="n">
         <v>4.3</v>
       </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X31" t="n">
+      <c r="AT31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY31" t="n">
         <v>12</v>
       </c>
-      <c r="Y31" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS31" t="n">
+      <c r="AZ31" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BA31" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB31" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>21</v>
+        <v>4.3</v>
       </c>
       <c r="BD31" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,78 +6563,78 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18:15:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Zamora FC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Caracas</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N32" t="n">
-        <v>1.25</v>
+        <v>2.76</v>
       </c>
       <c r="O32" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.42</v>
+        <v>2.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>1.42</v>
+        <v>4.8</v>
       </c>
       <c r="T32" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z32" t="n">
         <v>1000</v>
@@ -6643,25 +6643,25 @@
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI32" t="n">
         <v>1000</v>
@@ -6685,69 +6685,69 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,72 +6757,72 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="G33" t="n">
-        <v>1.62</v>
+        <v>3.55</v>
       </c>
       <c r="H33" t="n">
-        <v>5.7</v>
+        <v>2.74</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="K33" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="L33" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.72</v>
+        <v>2.52</v>
       </c>
       <c r="O33" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="P33" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S33" t="n">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="T33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W33" t="n">
-        <v>2.6</v>
+        <v>1.46</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,105 +6951,105 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:15:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="O34" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="P34" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="R34" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>6.8</v>
+        <v>1.98</v>
       </c>
       <c r="T34" t="n">
-        <v>2.32</v>
+        <v>1.03</v>
       </c>
       <c r="U34" t="n">
-        <v>1.65</v>
+        <v>1.03</v>
       </c>
       <c r="V34" t="n">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="W34" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
@@ -7058,13 +7058,13 @@
         <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
         <v>1000</v>
@@ -7073,69 +7073,69 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,191 +7145,191 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.56</v>
+        <v>1.46</v>
       </c>
       <c r="G35" t="n">
-        <v>2.9</v>
+        <v>1.58</v>
       </c>
       <c r="H35" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I35" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="K35" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF35" t="n">
         <v>1.01</v>
       </c>
-      <c r="M35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG35" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,191 +7339,191 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U36" t="n">
         <v>1.65</v>
       </c>
-      <c r="G36" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="H36" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I36" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J36" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K36" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L36" t="n">
+      <c r="V36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W36" t="n">
         <v>1.38</v>
       </c>
-      <c r="M36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.08</v>
-      </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB36" t="n">
         <v>8.4</v>
       </c>
       <c r="AC36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB36" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
+      <c r="BC36" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE36" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG36" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF36" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG36" t="n">
         <v>10</v>
       </c>
-      <c r="BG36" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7538,186 +7538,186 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Portuguesa FC</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.58</v>
+        <v>2.56</v>
       </c>
       <c r="G37" t="n">
-        <v>2.04</v>
+        <v>2.88</v>
       </c>
       <c r="H37" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="I37" t="n">
-        <v>8.4</v>
+        <v>3.85</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="K37" t="n">
-        <v>7.2</v>
+        <v>3.25</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="N37" t="n">
-        <v>1.68</v>
+        <v>2.46</v>
       </c>
       <c r="O37" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="P37" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.08</v>
+        <v>2.62</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S37" t="n">
-        <v>2.08</v>
+        <v>4.8</v>
       </c>
       <c r="T37" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="U37" t="n">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="V37" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="W37" t="n">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD37" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE37" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK37" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AR37" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS37" t="n">
         <v>4.8</v>
       </c>
-      <c r="AS37" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AT37" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AX37" t="n">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.65</v>
+        <v>9.6</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BD37" t="n">
         <v>4.8</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF37" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7727,191 +7727,191 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P38" t="n">
         <v>1.72</v>
       </c>
-      <c r="G38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I38" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.88</v>
-      </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R38" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T38" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="U38" t="n">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="V38" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="W38" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X38" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z38" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA38" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC38" t="n">
         <v>10.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE38" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG38" t="n">
         <v>12.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AQ38" t="n">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="AR38" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AS38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW38" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT38" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW38" t="n">
+      <c r="AX38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD38" t="n">
         <v>4</v>
       </c>
-      <c r="AX38" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE38" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG38" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7921,36 +7921,36 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Portuguesa FC</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,22 +7959,22 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="O39" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P39" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="R39" t="n">
         <v>1.18</v>
       </c>
       <c r="S39" t="n">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="T39" t="n">
         <v>1.03</v>
@@ -7983,10 +7983,10 @@
         <v>1.03</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8043,69 +8043,69 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8115,36 +8115,36 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="G40" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="H40" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="I40" t="n">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="J40" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="K40" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="L40" t="n">
         <v>1.33</v>
@@ -8153,153 +8153,153 @@
         <v>1.07</v>
       </c>
       <c r="N40" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P40" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S40" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T40" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="U40" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="W40" t="n">
-        <v>3.1</v>
+        <v>2.16</v>
       </c>
       <c r="X40" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y40" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB40" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF40" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AG40" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI40" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ40" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="AK40" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM40" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN40" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP40" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AT40" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU40" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AX40" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY40" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4.2</v>
+        <v>17</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BB40" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="BC40" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BF40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8309,78 +8309,78 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>4.1</v>
+        <v>1.84</v>
       </c>
       <c r="O41" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="P41" t="n">
-        <v>2.08</v>
+        <v>1.39</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="R41" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="T41" t="n">
-        <v>1.9</v>
+        <v>1.03</v>
       </c>
       <c r="U41" t="n">
-        <v>1.93</v>
+        <v>1.03</v>
       </c>
       <c r="V41" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="W41" t="n">
-        <v>2.66</v>
+        <v>1.47</v>
       </c>
       <c r="X41" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z41" t="n">
         <v>1000</v>
@@ -8389,22 +8389,22 @@
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC41" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD41" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE41" t="n">
         <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG41" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH41" t="n">
         <v>1000</v>
@@ -8425,75 +8425,75 @@
         <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR41" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS41" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU41" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV41" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW41" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX41" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY41" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BA41" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB41" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC41" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD41" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE41" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF41" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG41" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8503,191 +8503,191 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>21:45:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="G42" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="H42" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I42" t="n">
+        <v>14</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X42" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ42" t="n">
         <v>4.2</v>
       </c>
-      <c r="I42" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S42" t="n">
+      <c r="BA42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB42" t="n">
         <v>8.4</v>
       </c>
-      <c r="T42" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X42" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>430</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>21</v>
-      </c>
       <c r="BC42" t="n">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>40</v>
+        <v>4.3</v>
       </c>
       <c r="BE42" t="n">
-        <v>95</v>
+        <v>4.6</v>
       </c>
       <c r="BF42" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="BG42" t="n">
-        <v>46</v>
+        <v>4.6</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-19 12:41:44</t>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8697,184 +8697,572 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="G43" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="H43" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="I43" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="K43" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L43" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M43" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N43" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="P43" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="R43" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S43" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U43" t="n">
         <v>1.93</v>
       </c>
       <c r="V43" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W43" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="X43" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Z43" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA43" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD43" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AE43" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG43" t="n">
         <v>10.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ43" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL43" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM43" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AO43" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR43" t="n">
-        <v>38</v>
+        <v>7.2</v>
       </c>
       <c r="AS43" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AT43" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU43" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW43" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV43" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW43" t="n">
+      <c r="AX43" t="n">
         <v>8</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>8.4</v>
       </c>
       <c r="AY43" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ43" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:57:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>21:45:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S44" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X44" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>38</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:57:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H45" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I45" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X45" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ45" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA43" t="n">
+      <c r="AK45" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW45" t="n">
         <v>8</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="AX45" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB45" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC43" t="n">
+      <c r="BC45" t="n">
         <v>16</v>
       </c>
-      <c r="BD43" t="n">
+      <c r="BD45" t="n">
         <v>32</v>
       </c>
-      <c r="BE43" t="n">
+      <c r="BE45" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF43" t="n">
+      <c r="BF45" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BG43" t="n">
+      <c r="BG45" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BH43" t="inlineStr">
-        <is>
-          <t>2026-04-19 12:41:44</t>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>2026-04-19 14:57:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH45"/>
+  <dimension ref="A1:BH47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I2" t="n">
         <v>2.94</v>
@@ -775,7 +775,7 @@
         <v>3.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
@@ -808,7 +808,7 @@
         <v>1.51</v>
       </c>
       <c r="W2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
@@ -853,7 +853,7 @@
         <v>48</v>
       </c>
       <c r="AL2" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
         <v>200</v>
@@ -862,7 +862,7 @@
         <v>60</v>
       </c>
       <c r="AO2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP2" t="n">
         <v>6.6</v>
@@ -886,7 +886,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -898,10 +898,10 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC2" t="n">
         <v>4.7</v>
@@ -910,7 +910,7 @@
         <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF2" t="n">
         <v>4.8</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="H3" t="n">
         <v>12</v>
@@ -963,10 +963,10 @@
         <v>21</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="K3" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>1.21</v>
@@ -981,19 +981,19 @@
         <v>1.13</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
         <v>1.75</v>
@@ -1002,7 +1002,7 @@
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1053,68 +1053,68 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR3" t="n">
         <v>4.4</v>
       </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
       </c>
       <c r="AU3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX3" t="n">
         <v>6.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB3" t="n">
         <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>220</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H4" t="n">
         <v>8.4</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
         <v>5.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="V4" t="n">
         <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X4" t="n">
         <v>24</v>
@@ -1208,85 +1208,85 @@
         <v>100</v>
       </c>
       <c r="AA4" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
         <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AE4" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AP4" t="n">
         <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
@@ -1295,20 +1295,20 @@
         <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="I5" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V5" t="n">
         <v>2.96</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.34</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="G6" t="n">
         <v>2.12</v>
@@ -1653,7 +1653,7 @@
         <v>5.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
         <v>6.2</v>
@@ -1671,7 +1671,7 @@
         <v>4.1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>4.9</v>
       </c>
       <c r="BA6" t="n">
         <v>5.7</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G7" t="n">
         <v>2.12</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>3.6</v>
@@ -1751,13 +1751,13 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O7" t="n">
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
         <v>2.26</v>
@@ -1775,10 +1775,10 @@
         <v>1.86</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X7" t="n">
         <v>12.5</v>
@@ -1796,7 +1796,7 @@
         <v>8.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>22</v>
@@ -1835,16 +1835,16 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.4</v>
+        <v>3.8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AT7" t="n">
         <v>5.9</v>
@@ -1856,19 +1856,19 @@
         <v>14.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ7" t="n">
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB7" t="n">
         <v>19</v>
@@ -1877,20 +1877,20 @@
         <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE7" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF7" t="n">
         <v>15.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -1921,43 +1921,43 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G8" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K8" t="n">
         <v>6.8</v>
       </c>
-      <c r="J8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>950</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="R8" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S8" t="n">
         <v>2.1</v>
@@ -1972,7 +1972,7 @@
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2023,34 +2023,34 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ8" t="n">
         <v>5.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8" t="n">
         <v>5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX8" t="n">
         <v>4.3</v>
@@ -2059,32 +2059,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD8" t="n">
         <v>5.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
         <v>4.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="I9" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>1.39</v>
@@ -2139,37 +2139,37 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
         <v>1.69</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
         <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y9" t="n">
         <v>15</v>
@@ -2193,7 +2193,7 @@
         <v>42</v>
       </c>
       <c r="AF9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
         <v>13.5</v>
@@ -2223,28 +2223,28 @@
         <v>36</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AX9" t="n">
         <v>12.5</v>
@@ -2256,29 +2256,29 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>15.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>4.4</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="I10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="J10" t="n">
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.29</v>
@@ -2336,40 +2336,40 @@
         <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2378,10 +2378,10 @@
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2414,65 +2414,65 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="AX10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY10" t="n">
         <v>13.5</v>
       </c>
-      <c r="AT10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU10" t="n">
+      <c r="AZ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG10" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>46</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>7</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G11" t="n">
         <v>1.74</v>
@@ -2512,7 +2512,7 @@
         <v>5.2</v>
       </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
         <v>4.1</v>
@@ -2548,7 +2548,7 @@
         <v>1.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
         <v>1.2</v>
@@ -2560,7 +2560,7 @@
         <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z11" t="n">
         <v>55</v>
@@ -2617,7 +2617,7 @@
         <v>16.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS11" t="n">
         <v>5</v>
@@ -2632,7 +2632,7 @@
         <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX11" t="n">
         <v>8.6</v>
@@ -2644,7 +2644,7 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB11" t="n">
         <v>13</v>
@@ -2656,24 +2656,24 @@
         <v>4.5</v>
       </c>
       <c r="BE11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG11" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="G12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P12" t="n">
         <v>2.18</v>
       </c>
-      <c r="H12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.96</v>
-      </c>
       <c r="Q12" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="U12" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
         <v>30</v>
       </c>
       <c r="AA12" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH12" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AI12" t="n">
         <v>46</v>
       </c>
-      <c r="AF12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>55</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP12" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AU12" t="n">
         <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>24</v>
+        <v>5.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.68</v>
+        <v>2.54</v>
       </c>
       <c r="G13" t="n">
-        <v>1.79</v>
+        <v>2.78</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>2.94</v>
       </c>
       <c r="J13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY13" t="n">
         <v>4.3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
         <v>13</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>14</v>
+        <v>5.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="G14" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="H14" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="T14" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="U14" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="X14" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV14" t="n">
         <v>14</v>
       </c>
-      <c r="AC14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AW14" t="n">
-        <v>4.5</v>
+        <v>9.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.4</v>
+        <v>24</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.5</v>
+        <v>32</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,67 +3270,67 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.52</v>
+        <v>1.68</v>
       </c>
       <c r="G15" t="n">
-        <v>2.76</v>
+        <v>1.78</v>
       </c>
       <c r="H15" t="n">
-        <v>2.72</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2.98</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>1.58</v>
+        <v>2.28</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3345,22 +3345,22 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
         <v>1000</v>
@@ -3372,7 +3372,7 @@
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
@@ -3381,75 +3381,75 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
         <v>4.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.3</v>
+        <v>14</v>
       </c>
       <c r="BC15" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF15" t="n">
         <v>5.6</v>
       </c>
-      <c r="BF15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BG15" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G16" t="n">
         <v>2.36</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.46</v>
-      </c>
       <c r="H16" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
         <v>3.45</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
         <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="X16" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="Z16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>13.5</v>
+        <v>4.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AR16" t="n">
-        <v>20</v>
+        <v>4.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.4</v>
+        <v>3.75</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>14.5</v>
+        <v>4</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="BA16" t="n">
-        <v>10</v>
+        <v>4.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>9.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF16" t="n">
         <v>11</v>
       </c>
-      <c r="BF16" t="n">
-        <v>16</v>
-      </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G17" t="n">
         <v>2.96</v>
       </c>
       <c r="H17" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I17" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
         <v>3.7</v>
@@ -3691,7 +3691,7 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
         <v>1.3</v>
@@ -3715,7 +3715,7 @@
         <v>2.26</v>
       </c>
       <c r="V17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W17" t="n">
         <v>1.51</v>
@@ -3724,13 +3724,13 @@
         <v>16.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="n">
         <v>13.5</v>
@@ -3739,40 +3739,40 @@
         <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF17" t="n">
         <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
         <v>17.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ17" t="n">
         <v>48</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL17" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN17" t="n">
         <v>28</v>
       </c>
       <c r="AO17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP17" t="n">
         <v>14</v>
@@ -3787,7 +3787,7 @@
         <v>23</v>
       </c>
       <c r="AT17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU17" t="n">
         <v>7</v>
@@ -3820,7 +3820,7 @@
         <v>25</v>
       </c>
       <c r="BE17" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BF17" t="n">
         <v>17.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G18" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I18" t="n">
         <v>1.85</v>
@@ -3876,7 +3876,7 @@
         <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3906,7 +3906,7 @@
         <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
         <v>2.16</v>
@@ -3918,10 +3918,10 @@
         <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AA18" t="n">
         <v>23</v>
@@ -3930,34 +3930,34 @@
         <v>23</v>
       </c>
       <c r="AC18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH18" t="n">
         <v>22</v>
       </c>
-      <c r="AF18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>23</v>
-      </c>
       <c r="AI18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ18" t="n">
         <v>140</v>
       </c>
       <c r="AK18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM18" t="n">
         <v>120</v>
@@ -3966,7 +3966,7 @@
         <v>80</v>
       </c>
       <c r="AO18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AP18" t="n">
         <v>15</v>
@@ -3993,7 +3993,7 @@
         <v>15</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AY18" t="n">
         <v>14</v>
@@ -4002,29 +4002,29 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BG18" t="n">
         <v>7.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G19" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H19" t="n">
         <v>2.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L19" t="n">
         <v>1.43</v>
@@ -4082,13 +4082,13 @@
         <v>3.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R19" t="n">
         <v>1.32</v>
@@ -4103,16 +4103,16 @@
         <v>2.08</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z19" t="n">
         <v>22</v>
@@ -4124,16 +4124,16 @@
         <v>12.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
         <v>14.5</v>
@@ -4172,7 +4172,7 @@
         <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT19" t="n">
         <v>8.4</v>
@@ -4184,7 +4184,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX19" t="n">
         <v>14</v>
@@ -4196,29 +4196,29 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -4249,43 +4249,43 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H20" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="I20" t="n">
         <v>3.25</v>
       </c>
       <c r="J20" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O20" t="n">
         <v>1.38</v>
       </c>
       <c r="P20" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q20" t="n">
         <v>2.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
         <v>2.06</v>
@@ -4297,10 +4297,10 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -4443,58 +4443,58 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="G21" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I21" t="n">
         <v>6.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K21" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="T21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V21" t="n">
         <v>1.19</v>
       </c>
       <c r="W21" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
@@ -4503,7 +4503,7 @@
         <v>24</v>
       </c>
       <c r="Z21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
@@ -4521,7 +4521,7 @@
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG21" t="n">
         <v>12</v>
@@ -4533,10 +4533,10 @@
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL21" t="n">
         <v>36</v>
@@ -4545,75 +4545,75 @@
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AY21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BC21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BF21" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>48</v>
+        <v>5.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Belgrano</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.85</v>
+        <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1.96</v>
+        <v>3.95</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="K22" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="N22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S22" t="n">
+        <v>6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>6.2</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X22" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>27</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL22" t="n">
+      <c r="AR22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS22" t="n">
         <v>30</v>
       </c>
-      <c r="AM22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN22" t="n">
+      <c r="AT22" t="n">
         <v>8.6</v>
       </c>
-      <c r="AO22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AU22" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.4</v>
+        <v>30</v>
       </c>
       <c r="AX22" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AZ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB22" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>19</v>
-      </c>
       <c r="BC22" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="BF22" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,179 +4822,179 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.65</v>
+        <v>1.85</v>
       </c>
       <c r="G23" t="n">
-        <v>3.95</v>
+        <v>1.96</v>
       </c>
       <c r="H23" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>2.48</v>
+        <v>4.3</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M23" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>2.52</v>
+        <v>6.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="P23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.84</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="S23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF23" t="n">
         <v>6</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG23" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I24" t="n">
         <v>8</v>
@@ -5043,22 +5043,22 @@
         <v>4.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R24" t="n">
         <v>1.35</v>
@@ -5070,13 +5070,13 @@
         <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V24" t="n">
         <v>1.14</v>
       </c>
       <c r="W24" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X24" t="n">
         <v>15.5</v>
@@ -5091,7 +5091,7 @@
         <v>280</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC24" t="n">
         <v>9.800000000000001</v>
@@ -5106,7 +5106,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AG24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH24" t="n">
         <v>27</v>
@@ -5121,7 +5121,7 @@
         <v>18.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM24" t="n">
         <v>180</v>
@@ -5139,10 +5139,10 @@
         <v>18.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="AS24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT24" t="n">
         <v>6.6</v>
@@ -5160,13 +5160,13 @@
         <v>7.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
         <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB24" t="n">
         <v>12</v>
@@ -5175,20 +5175,20 @@
         <v>14.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF24" t="n">
         <v>8.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G25" t="n">
         <v>2.12</v>
@@ -5228,10 +5228,10 @@
         <v>3.95</v>
       </c>
       <c r="I25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K25" t="n">
         <v>3.8</v>
@@ -5243,13 +5243,13 @@
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O25" t="n">
         <v>1.32</v>
       </c>
       <c r="P25" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="n">
         <v>1.92</v>
@@ -5258,13 +5258,13 @@
         <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
         <v>1.79</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V25" t="n">
         <v>1.28</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -5425,40 +5425,40 @@
         <v>2.36</v>
       </c>
       <c r="J26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.4</v>
       </c>
-      <c r="K26" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L26" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
         <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U26" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V26" t="n">
         <v>1.73</v>
@@ -5488,7 +5488,7 @@
         <v>11.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF26" t="n">
         <v>23</v>
@@ -5497,7 +5497,7 @@
         <v>15</v>
       </c>
       <c r="AH26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
         <v>46</v>
@@ -5506,7 +5506,7 @@
         <v>70</v>
       </c>
       <c r="AK26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL26" t="n">
         <v>60</v>
@@ -5533,7 +5533,7 @@
         <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU26" t="n">
         <v>7</v>
@@ -5545,13 +5545,13 @@
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
         <v>14</v>
       </c>
       <c r="AZ26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA26" t="n">
         <v>27</v>
@@ -5566,17 +5566,17 @@
         <v>32</v>
       </c>
       <c r="BE26" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BF26" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BG26" t="n">
         <v>22</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
         <v>3.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3.15</v>
       </c>
       <c r="J27" t="n">
         <v>3.5</v>
@@ -5625,7 +5625,7 @@
         <v>3.55</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -5640,10 +5640,10 @@
         <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
         <v>3.25</v>
@@ -5652,13 +5652,13 @@
         <v>1.74</v>
       </c>
       <c r="U27" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X27" t="n">
         <v>15</v>
@@ -5667,10 +5667,10 @@
         <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB27" t="n">
         <v>12</v>
@@ -5685,19 +5685,19 @@
         <v>32</v>
       </c>
       <c r="AF27" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH27" t="n">
         <v>15.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK27" t="n">
         <v>25</v>
@@ -5709,10 +5709,10 @@
         <v>70</v>
       </c>
       <c r="AN27" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP27" t="n">
         <v>14</v>
@@ -5721,10 +5721,10 @@
         <v>12.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS27" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AT27" t="n">
         <v>11</v>
@@ -5736,16 +5736,16 @@
         <v>12.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY27" t="n">
         <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA27" t="n">
         <v>38</v>
@@ -5766,11 +5766,11 @@
         <v>17.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G28" t="n">
         <v>3.3</v>
       </c>
       <c r="H28" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="I28" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.41</v>
@@ -5825,16 +5825,16 @@
         <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>1.32</v>
       </c>
       <c r="P28" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R28" t="n">
         <v>1.37</v>
@@ -5843,19 +5843,19 @@
         <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U28" t="n">
         <v>2.2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X28" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y28" t="n">
         <v>11</v>
@@ -5864,16 +5864,16 @@
         <v>18.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB28" t="n">
         <v>14.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE28" t="n">
         <v>26</v>
@@ -5891,13 +5891,13 @@
         <v>38</v>
       </c>
       <c r="AJ28" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AK28" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL28" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM28" t="n">
         <v>95</v>
@@ -5906,7 +5906,7 @@
         <v>36</v>
       </c>
       <c r="AO28" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AP28" t="n">
         <v>12.5</v>
@@ -5918,7 +5918,7 @@
         <v>14</v>
       </c>
       <c r="AS28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
@@ -5933,45 +5933,45 @@
         <v>19</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.6</v>
+        <v>19</v>
       </c>
       <c r="AY28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ28" t="n">
         <v>15</v>
       </c>
       <c r="BA28" t="n">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="BB28" t="n">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="BC28" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="BE28" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Chilean Segunda Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Deportes Rengo Unido</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="G29" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>2.92</v>
+        <v>1.03</v>
       </c>
       <c r="K29" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>1.24</v>
       </c>
       <c r="O29" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="P29" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.52</v>
+        <v>1.19</v>
       </c>
       <c r="R29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S29" t="n">
         <v>1.19</v>
       </c>
-      <c r="S29" t="n">
-        <v>5.1</v>
-      </c>
       <c r="T29" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Peruvian Segunda Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Binacional</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>CD Estudiantil CNI</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>2.94</v>
+        <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>1.03</v>
       </c>
       <c r="K30" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.78</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.51</v>
+        <v>1.13</v>
       </c>
       <c r="P30" t="n">
-        <v>1.59</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.52</v>
+        <v>1.13</v>
       </c>
       <c r="R30" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="S30" t="n">
-        <v>5.1</v>
+        <v>1.13</v>
       </c>
       <c r="T30" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="F31" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H31" t="n">
         <v>3.3</v>
       </c>
-      <c r="G31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2.78</v>
-      </c>
       <c r="I31" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="J31" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="K31" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="L31" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="M31" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="N31" t="n">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="O31" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="P31" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="R31" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="S31" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="U31" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="V31" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="X31" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA31" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC31" t="n">
         <v>8.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AG31" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AL31" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AM31" t="n">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>4.3</v>
+        <v>50</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.3</v>
+        <v>38</v>
       </c>
       <c r="AX31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.4</v>
+        <v>50</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.4</v>
+        <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.3</v>
+        <v>50</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,120 +6563,120 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Caracas</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.22</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="H32" t="n">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="I32" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="L32" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O32" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="P32" t="n">
         <v>1.59</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S32" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="V32" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="W32" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="X32" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Y32" t="n">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB32" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AD32" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF32" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AG32" t="n">
         <v>14</v>
       </c>
       <c r="AH32" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN32" t="n">
         <v>1000</v>
@@ -6685,69 +6685,69 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT32" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AU32" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="AX32" t="n">
-        <v>9.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="BB32" t="n">
-        <v>3.85</v>
+        <v>27</v>
       </c>
       <c r="BC32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BD32" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.2</v>
+        <v>46</v>
       </c>
       <c r="BF32" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.1</v>
+        <v>24</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Central Cordoba (SdE)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Club Oriental de La Paz</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="G33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H33" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I33" t="n">
-        <v>3.85</v>
+        <v>2.94</v>
       </c>
       <c r="J33" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="K33" t="n">
-        <v>4.7</v>
+        <v>2.92</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="N33" t="n">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="O33" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="P33" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.32</v>
+        <v>3.35</v>
       </c>
       <c r="R33" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>2.32</v>
+        <v>7.6</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V33" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="W33" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,184 +6951,184 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18:15:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Club Oriental de La Paz</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N34" t="n">
-        <v>1.82</v>
+        <v>3.1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="P34" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S34" t="n">
-        <v>1.98</v>
+        <v>3.9</v>
       </c>
       <c r="T34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X34" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS34" t="n">
         <v>1.03</v>
       </c>
-      <c r="U34" t="n">
+      <c r="AT34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW34" t="n">
         <v>1.03</v>
       </c>
-      <c r="V34" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
@@ -7145,78 +7145,78 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Zamora FC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Academia Anzoategui FC</t>
+          <t>Caracas</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.46</v>
+        <v>2.22</v>
       </c>
       <c r="G35" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="H35" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="I35" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J35" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L35" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="M35" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="N35" t="n">
-        <v>1.86</v>
+        <v>2.76</v>
       </c>
       <c r="O35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V35" t="n">
         <v>1.31</v>
       </c>
-      <c r="P35" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.1</v>
-      </c>
       <c r="W35" t="n">
-        <v>2.6</v>
+        <v>1.71</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z35" t="n">
         <v>1000</v>
@@ -7225,25 +7225,25 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC35" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE35" t="n">
         <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
@@ -7267,69 +7267,69 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,105 +7339,105 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:15:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="O36" t="n">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="P36" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>1.98</v>
       </c>
       <c r="R36" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>6.8</v>
+        <v>1.98</v>
       </c>
       <c r="T36" t="n">
-        <v>2.32</v>
+        <v>1.03</v>
       </c>
       <c r="U36" t="n">
-        <v>1.65</v>
+        <v>1.03</v>
       </c>
       <c r="V36" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
@@ -7446,13 +7446,13 @@
         <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
         <v>1000</v>
@@ -7461,69 +7461,69 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,191 +7533,191 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Floresta EC</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ferroviaria</t>
+          <t>Academia Anzoategui FC</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.56</v>
+        <v>1.46</v>
       </c>
       <c r="G37" t="n">
-        <v>2.88</v>
+        <v>1.58</v>
       </c>
       <c r="H37" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
+        <v>11</v>
+      </c>
+      <c r="J37" t="n">
         <v>3.85</v>
       </c>
-      <c r="J37" t="n">
-        <v>2.76</v>
-      </c>
       <c r="K37" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M37" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="N37" t="n">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="P37" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.62</v>
+        <v>1.92</v>
       </c>
       <c r="R37" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="T37" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="U37" t="n">
-        <v>1.74</v>
+        <v>1.03</v>
       </c>
       <c r="V37" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="X37" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ37" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AR37" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU37" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV37" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX37" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY37" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ37" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE37" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7727,191 +7727,191 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Maringa</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brusque FC</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="F38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U38" t="n">
         <v>1.65</v>
       </c>
-      <c r="G38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="H38" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I38" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K38" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="V38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W38" t="n">
         <v>1.38</v>
       </c>
-      <c r="M38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W38" t="n">
-        <v>2.08</v>
-      </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB38" t="n">
         <v>8.4</v>
       </c>
       <c r="AC38" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB38" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF38" t="n">
+      <c r="BC38" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE38" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG38" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF38" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG38" t="n">
         <v>10</v>
       </c>
-      <c r="BG38" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7926,186 +7926,186 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Floresta EC</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Portuguesa FC</t>
+          <t>Ferroviaria</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.67</v>
+        <v>2.56</v>
       </c>
       <c r="G39" t="n">
-        <v>2.14</v>
+        <v>2.94</v>
       </c>
       <c r="H39" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="K39" t="n">
-        <v>7.8</v>
+        <v>3.25</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N39" t="n">
-        <v>1.58</v>
+        <v>2.44</v>
       </c>
       <c r="O39" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="P39" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="Q39" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T39" t="n">
         <v>2.08</v>
       </c>
-      <c r="R39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.03</v>
-      </c>
       <c r="U39" t="n">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="V39" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="W39" t="n">
-        <v>1.87</v>
+        <v>1.52</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE39" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI39" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO39" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP39" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="AQ39" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.6</v>
+        <v>15.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="AV39" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX39" t="n">
-        <v>3.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.65</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ39" t="n">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="BA39" t="n">
         <v>4.9</v>
       </c>
       <c r="BB39" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE39" t="n">
         <v>5</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BG39" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8115,191 +8115,191 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Maringa</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Brusque FC</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="G40" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="H40" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="K40" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="L40" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M40" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="O40" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="P40" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R40" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="S40" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="U40" t="n">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="V40" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W40" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="X40" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y40" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z40" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA40" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>13</v>
       </c>
       <c r="AG40" t="n">
         <v>12.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI40" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK40" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL40" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM40" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO40" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AQ40" t="n">
-        <v>14.5</v>
+        <v>3.7</v>
       </c>
       <c r="AR40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV40" t="n">
         <v>3.9</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AW40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD40" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT40" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE40" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF40" t="n">
         <v>9</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8309,72 +8309,72 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Deportivo La Guaira</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Portuguesa FC</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M41" t="n">
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="O41" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P41" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="R41" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S41" t="n">
-        <v>1.95</v>
+        <v>3.55</v>
       </c>
       <c r="T41" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="U41" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="V41" t="n">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="W41" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8431,69 +8431,69 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8503,36 +8503,36 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="G42" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="H42" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="I42" t="n">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="J42" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="K42" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="L42" t="n">
         <v>1.33</v>
@@ -8541,153 +8541,153 @@
         <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P42" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q42" t="n">
+        <v>2</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U42" t="n">
         <v>1.98</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.54</v>
-      </c>
       <c r="V42" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="W42" t="n">
-        <v>3.3</v>
+        <v>2.16</v>
       </c>
       <c r="X42" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC42" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF42" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AG42" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ42" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="AK42" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN42" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP42" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ42" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AT42" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU42" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV42" t="n">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AX42" t="n">
-        <v>5.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY42" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ42" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE42" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8697,78 +8697,78 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Univ Catolica (Chile)</t>
+          <t>Club Sportivo Ameliano</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>4.1</v>
+        <v>1.88</v>
       </c>
       <c r="O43" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="P43" t="n">
-        <v>2.08</v>
+        <v>1.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="R43" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="T43" t="n">
-        <v>1.9</v>
+        <v>1.03</v>
       </c>
       <c r="U43" t="n">
-        <v>1.93</v>
+        <v>1.03</v>
       </c>
       <c r="V43" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="W43" t="n">
-        <v>2.78</v>
+        <v>1.47</v>
       </c>
       <c r="X43" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z43" t="n">
         <v>1000</v>
@@ -8777,22 +8777,22 @@
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC43" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD43" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE43" t="n">
         <v>1000</v>
       </c>
       <c r="AF43" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH43" t="n">
         <v>1000</v>
@@ -8813,75 +8813,75 @@
         <v>1000</v>
       </c>
       <c r="AN43" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AO43" t="n">
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY43" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BA43" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC43" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD43" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8891,191 +8891,191 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>21:45:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CA Huracan</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="G44" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="H44" t="n">
-        <v>4.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>4.7</v>
+        <v>14</v>
       </c>
       <c r="J44" t="n">
-        <v>2.82</v>
+        <v>4.4</v>
       </c>
       <c r="K44" t="n">
-        <v>2.96</v>
+        <v>5.4</v>
       </c>
       <c r="L44" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="M44" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="N44" t="n">
-        <v>2.18</v>
+        <v>3.5</v>
       </c>
       <c r="O44" t="n">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="P44" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.45</v>
+        <v>2.02</v>
       </c>
       <c r="R44" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="S44" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W44" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X44" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU44" t="n">
         <v>8.4</v>
       </c>
-      <c r="T44" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X44" t="n">
+      <c r="AV44" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX44" t="n">
         <v>6.4</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AY44" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB44" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Z44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB44" t="n">
+      <c r="BC44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE44" t="n">
         <v>5.9</v>
       </c>
-      <c r="AC44" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>430</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU44" t="n">
+      <c r="BF44" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV44" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>38</v>
-      </c>
       <c r="BG44" t="n">
-        <v>46</v>
+        <v>5.9</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-19 14:57:30</t>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9085,184 +9085,572 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Univ Catolica (Chile)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="G45" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="H45" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="I45" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="K45" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M45" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N45" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="O45" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="P45" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="R45" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S45" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U45" t="n">
         <v>1.93</v>
       </c>
       <c r="V45" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W45" t="n">
-        <v>2.32</v>
+        <v>2.78</v>
       </c>
       <c r="X45" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Y45" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z45" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA45" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD45" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE45" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF45" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG45" t="n">
         <v>10.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI45" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL45" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM45" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO45" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR45" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="AS45" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT45" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV45" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU45" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>19</v>
-      </c>
       <c r="AW45" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX45" t="n">
         <v>8</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>8.4</v>
       </c>
       <c r="AY45" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ45" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>2026-04-19 17:11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>21:45:00</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CA Huracan</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S46" t="n">
+        <v>8</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X46" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>46</v>
+      </c>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>2026-04-19 17:11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H47" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X47" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ47" t="n">
         <v>18.5</v>
       </c>
-      <c r="BA45" t="n">
+      <c r="AK47" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW47" t="n">
         <v>8</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="AX47" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB47" t="n">
         <v>14.5</v>
       </c>
-      <c r="BC45" t="n">
+      <c r="BC47" t="n">
         <v>16</v>
       </c>
-      <c r="BD45" t="n">
+      <c r="BD47" t="n">
         <v>32</v>
       </c>
-      <c r="BE45" t="n">
+      <c r="BE47" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF45" t="n">
+      <c r="BF47" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BG45" t="n">
+      <c r="BG47" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BH45" t="inlineStr">
-        <is>
-          <t>2026-04-19 14:57:30</t>
+      <c r="BH47" t="inlineStr">
+        <is>
+          <t>2026-04-19 17:11:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -760,16 +760,16 @@
         <v>2.98</v>
       </c>
       <c r="G2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="n">
         <v>2.72</v>
       </c>
       <c r="I2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="K2" t="n">
         <v>3.2</v>
@@ -781,7 +781,7 @@
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O2" t="n">
         <v>1.51</v>
@@ -790,13 +790,13 @@
         <v>1.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R2" t="n">
         <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T2" t="n">
         <v>2.02</v>
@@ -805,16 +805,16 @@
         <v>1.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
         <v>20</v>
@@ -823,7 +823,7 @@
         <v>60</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8.4</v>
@@ -832,7 +832,7 @@
         <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AF2" t="n">
         <v>21</v>
@@ -844,25 +844,25 @@
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AJ2" t="n">
         <v>70</v>
       </c>
       <c r="AK2" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>370</v>
       </c>
       <c r="AM2" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AP2" t="n">
         <v>6.6</v>
@@ -874,7 +874,7 @@
         <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT2" t="n">
         <v>6.8</v>
@@ -886,41 +886,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.9</v>
+        <v>40</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.8</v>
+        <v>38</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
         <v>6.4</v>
@@ -981,7 +981,7 @@
         <v>1.13</v>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="Q3" t="n">
         <v>1.39</v>
@@ -1002,7 +1002,7 @@
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,7 +1059,7 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.3</v>
@@ -1080,22 +1080,22 @@
         <v>4.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA3" t="n">
         <v>4.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
         <v>11.5</v>
@@ -1104,17 +1104,17 @@
         <v>4.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF3" t="n">
         <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G4" t="n">
         <v>1.44</v>
@@ -1169,13 +1169,13 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q4" t="n">
         <v>1.63</v>
@@ -1187,10 +1187,10 @@
         <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V4" t="n">
         <v>1.1</v>
@@ -1202,16 +1202,16 @@
         <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z4" t="n">
-        <v>100</v>
+        <v>540</v>
       </c>
       <c r="AA4" t="n">
         <v>360</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>12.5</v>
@@ -1232,7 +1232,7 @@
         <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="AJ4" t="n">
         <v>12.5</v>
@@ -1244,25 +1244,25 @@
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>160</v>
+        <v>390</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
         <v>8</v>
@@ -1271,10 +1271,10 @@
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
@@ -1283,10 +1283,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
@@ -1295,20 +1295,20 @@
         <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -1342,19 +1342,19 @@
         <v>7.4</v>
       </c>
       <c r="G5" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>1.28</v>
@@ -1363,7 +1363,7 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
         <v>1.25</v>
@@ -1372,46 +1372,46 @@
         <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="R5" t="n">
         <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="T5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
         <v>2.96</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB5" t="n">
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1444,65 +1444,65 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.56</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AR5" t="n">
         <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.35</v>
+        <v>5.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.33</v>
+        <v>4.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.29</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.31</v>
+        <v>2.48</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.34</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.34</v>
+        <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.33</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.34</v>
+        <v>2.58</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.34</v>
+        <v>7.8</v>
       </c>
       <c r="BG5" t="n">
         <v>5.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.92</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
         <v>4.2</v>
@@ -1545,10 +1545,10 @@
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
@@ -1557,28 +1557,28 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
         <v>1.26</v>
@@ -1611,22 +1611,22 @@
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1644,46 +1644,46 @@
         <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE6" t="n">
         <v>6</v>
@@ -1692,11 +1692,11 @@
         <v>12.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G7" t="n">
         <v>2.12</v>
@@ -1736,7 +1736,7 @@
         <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
@@ -1757,13 +1757,13 @@
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
         <v>2.26</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
         <v>4.2</v>
@@ -1775,25 +1775,25 @@
         <v>1.86</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC7" t="n">
         <v>8.199999999999999</v>
@@ -1808,19 +1808,19 @@
         <v>13.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK7" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1829,22 +1829,22 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="AT7" t="n">
         <v>5.9</v>
@@ -1856,7 +1856,7 @@
         <v>14.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -1868,7 +1868,7 @@
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
         <v>19</v>
@@ -1877,20 +1877,20 @@
         <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BF7" t="n">
         <v>15.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G8" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
         <v>6.8</v>
@@ -1963,7 +1963,7 @@
         <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
         <v>2.32</v>
@@ -1972,10 +1972,10 @@
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -1999,10 +1999,10 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.2</v>
+        <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS8" t="n">
         <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AW8" t="n">
         <v>5.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="AY8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="BA8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD8" t="n">
         <v>5.7</v>
       </c>
-      <c r="BB8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF8" t="n">
         <v>4.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="H9" t="n">
         <v>2.94</v>
@@ -2142,7 +2142,7 @@
         <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P9" t="n">
         <v>1.93</v>
@@ -2160,7 +2160,7 @@
         <v>1.69</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
         <v>1.41</v>
@@ -2169,70 +2169,70 @@
         <v>1.58</v>
       </c>
       <c r="X9" t="n">
-        <v>18.5</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>500</v>
       </c>
       <c r="Z9" t="n">
-        <v>26</v>
+        <v>500</v>
       </c>
       <c r="AA9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH9" t="n">
         <v>60</v>
       </c>
-      <c r="AB9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AO9" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AQ9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT9" t="n">
         <v>8.4</v>
@@ -2244,7 +2244,7 @@
         <v>10.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX9" t="n">
         <v>12.5</v>
@@ -2256,29 +2256,29 @@
         <v>12.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="G10" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="I10" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="J10" t="n">
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -2345,46 +2345,46 @@
         <v>1.72</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB10" t="n">
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
         <v>1000</v>
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2408,71 +2408,71 @@
         <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="AP10" t="n">
-        <v>13</v>
+        <v>5.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AU10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE10" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA10" t="n">
+      <c r="BF10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H11" t="n">
         <v>5.2</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J11" t="n">
         <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.33</v>
@@ -2527,28 +2527,28 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
         <v>2.76</v>
       </c>
       <c r="T11" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
         <v>1.2</v>
@@ -2566,7 +2566,7 @@
         <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
         <v>12</v>
@@ -2575,16 +2575,16 @@
         <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AF11" t="n">
         <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
@@ -2596,10 +2596,10 @@
         <v>19.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
         <v>110</v>
@@ -2608,7 +2608,7 @@
         <v>9.6</v>
       </c>
       <c r="AO11" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
         <v>15</v>
@@ -2617,13 +2617,13 @@
         <v>16.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU11" t="n">
         <v>7.8</v>
@@ -2632,10 +2632,10 @@
         <v>16</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY11" t="n">
         <v>7.8</v>
@@ -2644,7 +2644,7 @@
         <v>14.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB11" t="n">
         <v>13</v>
@@ -2653,20 +2653,20 @@
         <v>12.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="BE11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF11" t="n">
         <v>6.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -2697,25 +2697,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2727,94 +2727,94 @@
         <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V12" t="n">
         <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y12" t="n">
         <v>19</v>
       </c>
       <c r="Z12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA12" t="n">
         <v>60</v>
       </c>
       <c r="AB12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
         <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ12" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
         <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AN12" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AT12" t="n">
         <v>11.5</v>
@@ -2823,44 +2823,44 @@
         <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="AX12" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.9</v>
+        <v>26</v>
       </c>
       <c r="BC12" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.6</v>
+        <v>36</v>
       </c>
       <c r="BF12" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG12" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H13" t="n">
         <v>2.7</v>
@@ -2903,10 +2903,10 @@
         <v>2.94</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>1.32</v>
@@ -2915,10 +2915,10 @@
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
         <v>2.02</v>
@@ -2927,134 +2927,134 @@
         <v>1.83</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U13" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X13" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG13" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>5</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
         <v>1.41</v>
@@ -3109,146 +3109,146 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
         <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="X14" t="n">
         <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Z14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA14" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AB14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP14" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>24</v>
       </c>
       <c r="AS14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
         <v>14</v>
       </c>
       <c r="AW14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY14" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
         <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G15" t="n">
         <v>1.78</v>
@@ -3294,7 +3294,7 @@
         <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.24</v>
@@ -3312,7 +3312,7 @@
         <v>2.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R15" t="n">
         <v>1.62</v>
@@ -3345,10 +3345,10 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AC15" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3357,13 +3357,13 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="AG15" t="n">
         <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
@@ -3372,7 +3372,7 @@
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="AL15" t="n">
         <v>1000</v>
@@ -3381,22 +3381,22 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="AQ15" t="n">
         <v>18</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AT15" t="n">
         <v>9.800000000000001</v>
@@ -3408,19 +3408,19 @@
         <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ15" t="n">
         <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB15" t="n">
         <v>14</v>
@@ -3429,20 +3429,20 @@
         <v>12.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G16" t="n">
         <v>2.2</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.36</v>
-      </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>1.3</v>
@@ -3503,7 +3503,7 @@
         <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
         <v>1.73</v>
@@ -3512,19 +3512,19 @@
         <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U16" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
         <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="X16" t="n">
         <v>22</v>
@@ -3533,7 +3533,7 @@
         <v>18</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
@@ -3551,92 +3551,92 @@
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
         <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="AU16" t="n">
         <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC16" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC16" t="n">
+      <c r="BD16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF16" t="n">
         <v>4.2</v>
       </c>
-      <c r="BD16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE16" t="n">
+      <c r="BG16" t="n">
         <v>4.8</v>
       </c>
-      <c r="BF16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="G17" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3694,13 +3694,13 @@
         <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R17" t="n">
         <v>1.39</v>
@@ -3718,55 +3718,55 @@
         <v>1.59</v>
       </c>
       <c r="W17" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="X17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y17" t="n">
         <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
         <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AK17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM17" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
         <v>28</v>
@@ -3784,53 +3784,53 @@
         <v>15.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
         <v>18</v>
       </c>
       <c r="AX17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BB17" t="n">
         <v>25</v>
       </c>
       <c r="BC17" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
         <v>25</v>
       </c>
       <c r="BE17" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="BF17" t="n">
         <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -3864,22 +3864,22 @@
         <v>4.7</v>
       </c>
       <c r="G18" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H18" t="n">
         <v>1.76</v>
       </c>
       <c r="I18" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -3909,10 +3909,10 @@
         <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
@@ -3921,25 +3921,25 @@
         <v>10.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA18" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AF18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG18" t="n">
         <v>21</v>
@@ -3948,10 +3948,10 @@
         <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ18" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AK18" t="n">
         <v>70</v>
@@ -3960,13 +3960,13 @@
         <v>70</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AO18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP18" t="n">
         <v>15</v>
@@ -3993,7 +3993,7 @@
         <v>15</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="AY18" t="n">
         <v>14</v>
@@ -4002,29 +4002,29 @@
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG18" t="n">
         <v>7.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>2.7</v>
       </c>
       <c r="I19" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J19" t="n">
         <v>3.35</v>
@@ -4073,13 +4073,13 @@
         <v>3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
         <v>1.35</v>
@@ -4088,7 +4088,7 @@
         <v>1.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
         <v>1.32</v>
@@ -4097,7 +4097,7 @@
         <v>3.65</v>
       </c>
       <c r="T19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U19" t="n">
         <v>2.08</v>
@@ -4106,25 +4106,25 @@
         <v>1.53</v>
       </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y19" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z19" t="n">
         <v>22</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
         <v>14.5</v>
@@ -4136,28 +4136,28 @@
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
@@ -4172,19 +4172,19 @@
         <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="AV19" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX19" t="n">
         <v>14</v>
@@ -4196,29 +4196,29 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>2.66</v>
       </c>
       <c r="G20" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="H20" t="n">
         <v>2.58</v>
       </c>
       <c r="I20" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
         <v>2.78</v>
@@ -4273,34 +4273,34 @@
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="O20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="Q20" t="n">
         <v>2.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>2.06</v>
+        <v>3.65</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U20" t="n">
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4318,7 +4318,7 @@
         <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD20" t="n">
         <v>1000</v>
@@ -4357,7 +4357,7 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.03</v>
@@ -4372,7 +4372,7 @@
         <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV20" t="n">
         <v>1.03</v>
@@ -4405,14 +4405,14 @@
         <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
         <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
@@ -4485,7 +4485,7 @@
         <v>2.66</v>
       </c>
       <c r="T21" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U21" t="n">
         <v>2.08</v>
@@ -4503,13 +4503,13 @@
         <v>24</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
         <v>11.5</v>
@@ -4521,31 +4521,31 @@
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
         <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
@@ -4557,10 +4557,10 @@
         <v>17.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AT21" t="n">
         <v>8</v>
@@ -4572,7 +4572,7 @@
         <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX21" t="n">
         <v>8</v>
@@ -4584,7 +4584,7 @@
         <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BB21" t="n">
         <v>12</v>
@@ -4593,20 +4593,20 @@
         <v>12</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
         <v>6.2</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H22" t="n">
         <v>2.36</v>
       </c>
       <c r="I22" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J22" t="n">
         <v>3.1</v>
@@ -4667,31 +4667,31 @@
         <v>1.61</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R22" t="n">
         <v>1.17</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U22" t="n">
         <v>1.72</v>
       </c>
       <c r="V22" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y22" t="n">
         <v>7</v>
@@ -4703,10 +4703,10 @@
         <v>44</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD22" t="n">
         <v>12.5</v>
@@ -4715,7 +4715,7 @@
         <v>36</v>
       </c>
       <c r="AF22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG22" t="n">
         <v>17</v>
@@ -4724,19 +4724,19 @@
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ22" t="n">
         <v>110</v>
       </c>
       <c r="AK22" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AL22" t="n">
         <v>110</v>
       </c>
       <c r="AM22" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN22" t="n">
         <v>130</v>
@@ -4760,47 +4760,47 @@
         <v>8.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW22" t="n">
         <v>30</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA22" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BB22" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="BC22" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BD22" t="n">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BE22" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="BF22" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BG22" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>1.85</v>
       </c>
       <c r="G23" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H23" t="n">
         <v>4</v>
@@ -4873,7 +4873,7 @@
         <v>2.24</v>
       </c>
       <c r="T23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U23" t="n">
         <v>2.72</v>
@@ -4894,64 +4894,64 @@
         <v>36</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB23" t="n">
         <v>17.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD23" t="n">
         <v>20</v>
       </c>
       <c r="AE23" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AF23" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH23" t="n">
         <v>18.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK23" t="n">
         <v>18</v>
       </c>
       <c r="AL23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM23" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AN23" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AO23" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.7</v>
+        <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AT23" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU23" t="n">
         <v>9</v>
@@ -4960,7 +4960,7 @@
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="AX23" t="n">
         <v>11</v>
@@ -4972,7 +4972,7 @@
         <v>11.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="BB23" t="n">
         <v>19</v>
@@ -4984,7 +4984,7 @@
         <v>18.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="BF23" t="n">
         <v>6</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G24" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H24" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J24" t="n">
         <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.35</v>
@@ -5049,16 +5049,16 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R24" t="n">
         <v>1.35</v>
@@ -5067,58 +5067,58 @@
         <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U24" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
         <v>1.14</v>
       </c>
       <c r="W24" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X24" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z24" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA24" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AB24" t="n">
         <v>7.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE24" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF24" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AG24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI24" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL24" t="n">
         <v>42</v>
@@ -5127,68 +5127,68 @@
         <v>180</v>
       </c>
       <c r="AN24" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AO24" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR24" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV24" t="n">
         <v>24</v>
       </c>
       <c r="AW24" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AX24" t="n">
         <v>7.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
         <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="G25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H25" t="n">
         <v>3.95</v>
       </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
         <v>3.5</v>
@@ -5237,7 +5237,7 @@
         <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
@@ -5252,16 +5252,16 @@
         <v>1.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R25" t="n">
         <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T25" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="U25" t="n">
         <v>2.08</v>
@@ -5270,7 +5270,7 @@
         <v>1.28</v>
       </c>
       <c r="W25" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X25" t="n">
         <v>16</v>
@@ -5279,7 +5279,7 @@
         <v>17.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
@@ -5294,7 +5294,7 @@
         <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -5306,10 +5306,10 @@
         <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ25" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AK25" t="n">
         <v>27</v>
@@ -5318,13 +5318,13 @@
         <v>46</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
         <v>18.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AP25" t="n">
         <v>11</v>
@@ -5333,10 +5333,10 @@
         <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -5345,10 +5345,10 @@
         <v>7</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.85</v>
+        <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
@@ -5357,32 +5357,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BC25" t="n">
         <v>18.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.5</v>
+        <v>26</v>
       </c>
       <c r="BF25" t="n">
         <v>13</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -5437,16 +5437,16 @@
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.43</v>
       </c>
       <c r="P26" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R26" t="n">
         <v>1.28</v>
@@ -5455,10 +5455,10 @@
         <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U26" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V26" t="n">
         <v>1.73</v>
@@ -5515,7 +5515,7 @@
         <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO26" t="n">
         <v>25</v>
@@ -5554,16 +5554,16 @@
         <v>18</v>
       </c>
       <c r="BA26" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BB26" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BC26" t="n">
         <v>42</v>
       </c>
       <c r="BD26" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BE26" t="n">
         <v>70</v>
@@ -5572,11 +5572,11 @@
         <v>48</v>
       </c>
       <c r="BG26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -5607,13 +5607,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G27" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I27" t="n">
         <v>3.1</v>
@@ -5646,28 +5646,28 @@
         <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="U27" t="n">
         <v>2.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W27" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X27" t="n">
         <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="n">
         <v>48</v>
@@ -5685,7 +5685,7 @@
         <v>32</v>
       </c>
       <c r="AF27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG27" t="n">
         <v>12</v>
@@ -5697,10 +5697,10 @@
         <v>40</v>
       </c>
       <c r="AJ27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
         <v>36</v>
@@ -5709,25 +5709,25 @@
         <v>70</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP27" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>12.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS27" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU27" t="n">
         <v>7.4</v>
@@ -5742,7 +5742,7 @@
         <v>16</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ27" t="n">
         <v>14.5</v>
@@ -5751,7 +5751,7 @@
         <v>38</v>
       </c>
       <c r="BB27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC27" t="n">
         <v>23</v>
@@ -5763,14 +5763,14 @@
         <v>60</v>
       </c>
       <c r="BF27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H28" t="n">
         <v>2.34</v>
@@ -5819,22 +5819,22 @@
         <v>3.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
         <v>1.32</v>
       </c>
       <c r="P28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q28" t="n">
         <v>1.97</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.98</v>
       </c>
       <c r="R28" t="n">
         <v>1.37</v>
@@ -5843,19 +5843,19 @@
         <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U28" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V28" t="n">
         <v>1.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X28" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y28" t="n">
         <v>11</v>
@@ -5867,7 +5867,7 @@
         <v>32</v>
       </c>
       <c r="AB28" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC28" t="n">
         <v>8.199999999999999</v>
@@ -5912,31 +5912,31 @@
         <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR28" t="n">
         <v>14</v>
       </c>
       <c r="AS28" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX28" t="n">
         <v>19</v>
       </c>
       <c r="AY28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
         <v>15</v>
@@ -5948,23 +5948,23 @@
         <v>48</v>
       </c>
       <c r="BC28" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="BD28" t="n">
         <v>40</v>
       </c>
       <c r="BE28" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BG28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -5995,58 +5995,58 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>1.75</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M29" t="n">
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.24</v>
+        <v>3.9</v>
       </c>
       <c r="O29" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="R29" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>1.19</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U29" t="n">
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -6213,22 +6213,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O30" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="R30" t="n">
         <v>1.16</v>
       </c>
       <c r="S30" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.54</v>
       </c>
       <c r="G31" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H31" t="n">
         <v>3.3</v>
@@ -6401,7 +6401,7 @@
         <v>3.25</v>
       </c>
       <c r="L31" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="M31" t="n">
         <v>1.12</v>
@@ -6413,10 +6413,10 @@
         <v>1.52</v>
       </c>
       <c r="P31" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R31" t="n">
         <v>1.19</v>
@@ -6434,10 +6434,10 @@
         <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X31" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y31" t="n">
         <v>12</v>
@@ -6458,7 +6458,7 @@
         <v>18</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AF31" t="n">
         <v>18</v>
@@ -6470,10 +6470,10 @@
         <v>24</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK31" t="n">
         <v>44</v>
@@ -6506,7 +6506,7 @@
         <v>6.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AV31" t="n">
         <v>11</v>
@@ -6530,23 +6530,23 @@
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF31" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
         <v>3.15</v>
       </c>
       <c r="L32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M32" t="n">
         <v>1.12</v>
@@ -6610,7 +6610,7 @@
         <v>1.59</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R32" t="n">
         <v>1.21</v>
@@ -6631,19 +6631,19 @@
         <v>1.46</v>
       </c>
       <c r="X32" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y32" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z32" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AA32" t="n">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC32" t="n">
         <v>7</v>
@@ -6652,58 +6652,58 @@
         <v>13.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AF32" t="n">
-        <v>970</v>
+        <v>46</v>
       </c>
       <c r="AG32" t="n">
         <v>14</v>
       </c>
       <c r="AH32" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AI32" t="n">
-        <v>65</v>
+        <v>380</v>
       </c>
       <c r="AJ32" t="n">
-        <v>55</v>
+        <v>340</v>
       </c>
       <c r="AK32" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="AL32" t="n">
-        <v>65</v>
+        <v>380</v>
       </c>
       <c r="AM32" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ32" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR32" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AS32" t="n">
         <v>25</v>
       </c>
       <c r="AT32" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU32" t="n">
         <v>6.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW32" t="n">
         <v>23</v>
@@ -6715,7 +6715,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA32" t="n">
         <v>32</v>
@@ -6730,7 +6730,7 @@
         <v>34</v>
       </c>
       <c r="BE32" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF32" t="n">
         <v>27</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -6771,25 +6771,25 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G33" t="n">
         <v>3.5</v>
       </c>
       <c r="H33" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="I33" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="J33" t="n">
         <v>2.72</v>
       </c>
       <c r="K33" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="L33" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="M33" t="n">
         <v>1.18</v>
@@ -6798,10 +6798,10 @@
         <v>2.16</v>
       </c>
       <c r="O33" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P33" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q33" t="n">
         <v>3.35</v>
@@ -6810,40 +6810,40 @@
         <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="T33" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
         <v>1.6</v>
       </c>
       <c r="V33" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W33" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X33" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="Y33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB33" t="n">
         <v>8.4</v>
       </c>
-      <c r="Z33" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AC33" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE33" t="n">
         <v>65</v>
@@ -6852,43 +6852,43 @@
         <v>25</v>
       </c>
       <c r="AG33" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH33" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="AI33" t="n">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AJ33" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK33" t="n">
         <v>85</v>
       </c>
       <c r="AL33" t="n">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="AM33" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AN33" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AO33" t="n">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="AP33" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ33" t="n">
         <v>6.2</v>
       </c>
       <c r="AR33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.3</v>
+        <v>40</v>
       </c>
       <c r="AT33" t="n">
         <v>6.8</v>
@@ -6897,44 +6897,44 @@
         <v>6.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.3</v>
+        <v>27</v>
       </c>
       <c r="AX33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY33" t="n">
         <v>15</v>
       </c>
-      <c r="AY33" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AZ33" t="n">
-        <v>4.1</v>
+        <v>27</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.4</v>
+        <v>40</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.4</v>
+        <v>32</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.3</v>
+        <v>32</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.4</v>
+        <v>42</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.5</v>
+        <v>110</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.4</v>
+        <v>38</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.3</v>
+        <v>55</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G34" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H34" t="n">
         <v>2.8</v>
@@ -6977,10 +6977,10 @@
         <v>3.15</v>
       </c>
       <c r="J34" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="K34" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6992,52 +6992,52 @@
         <v>3.1</v>
       </c>
       <c r="O34" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P34" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R34" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S34" t="n">
         <v>3.9</v>
       </c>
       <c r="T34" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U34" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="V34" t="n">
         <v>1.46</v>
       </c>
       <c r="W34" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X34" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z34" t="n">
         <v>22</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB34" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC34" t="n">
         <v>8.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE34" t="n">
         <v>42</v>
@@ -7049,16 +7049,16 @@
         <v>14.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ34" t="n">
-        <v>50</v>
+        <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AL34" t="n">
         <v>55</v>
@@ -7067,37 +7067,37 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP34" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AQ34" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR34" t="n">
         <v>14.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT34" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV34" t="n">
         <v>10</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AX34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY34" t="n">
         <v>9.800000000000001</v>
@@ -7106,29 +7106,29 @@
         <v>14</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>26</v>
+        <v>5.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>28</v>
+        <v>5.9</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
         <v>4.3</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K35" t="n">
         <v>3.45</v>
@@ -7219,7 +7219,7 @@
         <v>14</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA35" t="n">
         <v>1000</v>
@@ -7249,10 +7249,10 @@
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL35" t="n">
         <v>1000</v>
@@ -7261,68 +7261,68 @@
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="AR35" t="n">
-        <v>19.5</v>
+        <v>4</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT35" t="n">
         <v>6.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>12</v>
+        <v>3.85</v>
       </c>
       <c r="AW35" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX35" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY35" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>15.5</v>
+        <v>3.8</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB35" t="n">
-        <v>3.85</v>
+        <v>11.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>21</v>
+        <v>3.95</v>
       </c>
       <c r="BD35" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF35" t="n">
         <v>21</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -7353,28 +7353,28 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N36" t="n">
         <v>1.82</v>
@@ -7386,58 +7386,58 @@
         <v>1.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S36" t="n">
-        <v>1.98</v>
+        <v>3.85</v>
       </c>
       <c r="T36" t="n">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="U36" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="V36" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF36" t="n">
         <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
@@ -7461,62 +7461,62 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -7550,13 +7550,13 @@
         <v>1.46</v>
       </c>
       <c r="G37" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I37" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J37" t="n">
         <v>3.85</v>
@@ -7565,7 +7565,7 @@
         <v>5.4</v>
       </c>
       <c r="L37" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M37" t="n">
         <v>1.04</v>
@@ -7595,10 +7595,10 @@
         <v>1.03</v>
       </c>
       <c r="V37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W37" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -7637,7 +7637,7 @@
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK37" t="n">
         <v>1000</v>
@@ -7649,68 +7649,68 @@
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.03</v>
+        <v>1.73</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7759,7 @@
         <v>3</v>
       </c>
       <c r="L38" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M38" t="n">
         <v>1.17</v>
@@ -7780,10 +7780,10 @@
         <v>1.14</v>
       </c>
       <c r="S38" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="T38" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U38" t="n">
         <v>1.65</v>
@@ -7804,7 +7804,7 @@
         <v>16.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>55</v>
+        <v>400</v>
       </c>
       <c r="AB38" t="n">
         <v>8.4</v>
@@ -7816,7 +7816,7 @@
         <v>14.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF38" t="n">
         <v>22</v>
@@ -7825,19 +7825,19 @@
         <v>17</v>
       </c>
       <c r="AH38" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ38" t="n">
         <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL38" t="n">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AM38" t="n">
         <v>320</v>
@@ -7858,7 +7858,7 @@
         <v>14</v>
       </c>
       <c r="AS38" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT38" t="n">
         <v>7.4</v>
@@ -7870,7 +7870,7 @@
         <v>12.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>9.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="AX38" t="n">
         <v>18.5</v>
@@ -7879,32 +7879,32 @@
         <v>14.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB38" t="n">
         <v>11</v>
       </c>
-      <c r="BB38" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BC38" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BD38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG38" t="n">
         <v>11</v>
       </c>
-      <c r="BE38" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>10</v>
-      </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -7938,28 +7938,28 @@
         <v>2.56</v>
       </c>
       <c r="G39" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H39" t="n">
         <v>3.25</v>
       </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="J39" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="K39" t="n">
         <v>3.25</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
         <v>1.13</v>
       </c>
       <c r="N39" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O39" t="n">
         <v>1.55</v>
@@ -7977,16 +7977,16 @@
         <v>5.5</v>
       </c>
       <c r="T39" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U39" t="n">
         <v>1.72</v>
       </c>
       <c r="V39" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W39" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X39" t="n">
         <v>8.6</v>
@@ -8013,7 +8013,7 @@
         <v>70</v>
       </c>
       <c r="AF39" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG39" t="n">
         <v>16</v>
@@ -8028,7 +8028,7 @@
         <v>55</v>
       </c>
       <c r="AK39" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL39" t="n">
         <v>85</v>
@@ -8043,7 +8043,7 @@
         <v>90</v>
       </c>
       <c r="AP39" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ39" t="n">
         <v>6.8</v>
@@ -8052,19 +8052,19 @@
         <v>15.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT39" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU39" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AV39" t="n">
         <v>11.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AX39" t="n">
         <v>11.5</v>
@@ -8076,29 +8076,29 @@
         <v>17</v>
       </c>
       <c r="BA39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC39" t="n">
         <v>4.9</v>
       </c>
-      <c r="BB39" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BD39" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE39" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -8132,10 +8132,10 @@
         <v>1.59</v>
       </c>
       <c r="G40" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="H40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I40" t="n">
         <v>9</v>
@@ -8159,7 +8159,7 @@
         <v>1.41</v>
       </c>
       <c r="P40" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q40" t="n">
         <v>2.02</v>
@@ -8168,7 +8168,7 @@
         <v>1.27</v>
       </c>
       <c r="S40" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T40" t="n">
         <v>1.92</v>
@@ -8180,7 +8180,7 @@
         <v>1.12</v>
       </c>
       <c r="W40" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8195,7 +8195,7 @@
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC40" t="n">
         <v>11</v>
@@ -8240,13 +8240,13 @@
         <v>9</v>
       </c>
       <c r="AQ40" t="n">
-        <v>3.7</v>
+        <v>13.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT40" t="n">
         <v>5.2</v>
@@ -8255,10 +8255,10 @@
         <v>6.8</v>
       </c>
       <c r="AV40" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX40" t="n">
         <v>6.6</v>
@@ -8267,32 +8267,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB40" t="n">
         <v>11.5</v>
       </c>
       <c r="BC40" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF40" t="n">
         <v>9</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -8323,34 +8323,34 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G41" t="n">
         <v>2.04</v>
       </c>
       <c r="H41" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I41" t="n">
         <v>6.4</v>
       </c>
       <c r="J41" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K41" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L41" t="n">
         <v>1.42</v>
       </c>
       <c r="M41" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>1.67</v>
+        <v>2.78</v>
       </c>
       <c r="O41" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P41" t="n">
         <v>1.67</v>
@@ -8359,10 +8359,10 @@
         <v>2.18</v>
       </c>
       <c r="R41" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S41" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T41" t="n">
         <v>1.98</v>
@@ -8371,7 +8371,7 @@
         <v>1.8</v>
       </c>
       <c r="V41" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W41" t="n">
         <v>1.97</v>
@@ -8443,10 +8443,10 @@
         <v>5</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.25</v>
+        <v>5.8</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AV41" t="n">
         <v>4.3</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
         <v>4.8</v>
       </c>
       <c r="I42" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
         <v>3.75</v>
@@ -8541,13 +8541,13 @@
         <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O42" t="n">
         <v>1.32</v>
       </c>
       <c r="P42" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
@@ -8556,7 +8556,7 @@
         <v>1.34</v>
       </c>
       <c r="S42" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T42" t="n">
         <v>1.85</v>
@@ -8607,7 +8607,7 @@
         <v>90</v>
       </c>
       <c r="AJ42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK42" t="n">
         <v>24</v>
@@ -8619,7 +8619,7 @@
         <v>140</v>
       </c>
       <c r="AN42" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO42" t="n">
         <v>110</v>
@@ -8631,10 +8631,10 @@
         <v>14.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT42" t="n">
         <v>7.2</v>
@@ -8646,7 +8646,7 @@
         <v>17</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX42" t="n">
         <v>9.199999999999999</v>
@@ -8658,7 +8658,7 @@
         <v>17</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB42" t="n">
         <v>14</v>
@@ -8667,20 +8667,20 @@
         <v>16</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF42" t="n">
         <v>10</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G44" t="n">
         <v>1.46</v>
@@ -8962,7 +8962,7 @@
         <v>17.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z44" t="n">
         <v>1000</v>
@@ -9016,59 +9016,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AR44" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS44" t="n">
         <v>5.7</v>
       </c>
-      <c r="AS44" t="n">
+      <c r="AT44" t="n">
         <v>6</v>
       </c>
-      <c r="AT44" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AU44" t="n">
-        <v>8.4</v>
+        <v>3.95</v>
       </c>
       <c r="AV44" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AX44" t="n">
         <v>6.4</v>
       </c>
       <c r="AY44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AZ44" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD44" t="n">
         <v>5.2</v>
       </c>
-      <c r="BA44" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BE44" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BF44" t="n">
         <v>6.8</v>
       </c>
       <c r="BG44" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -9105,10 +9105,10 @@
         <v>1.56</v>
       </c>
       <c r="H45" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J45" t="n">
         <v>4.3</v>
@@ -9117,7 +9117,7 @@
         <v>5</v>
       </c>
       <c r="L45" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M45" t="n">
         <v>1.05</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
         <v>2.26</v>
       </c>
       <c r="G46" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H46" t="n">
         <v>4.3</v>
@@ -9311,7 +9311,7 @@
         <v>2.96</v>
       </c>
       <c r="L46" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="M46" t="n">
         <v>1.18</v>
@@ -9326,16 +9326,16 @@
         <v>1.37</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R46" t="n">
         <v>1.12</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T46" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="U46" t="n">
         <v>1.56</v>
@@ -9347,13 +9347,13 @@
         <v>1.73</v>
       </c>
       <c r="X46" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Y46" t="n">
         <v>9.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA46" t="n">
         <v>1000</v>
@@ -9371,10 +9371,10 @@
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH46" t="n">
         <v>1000</v>
@@ -9407,7 +9407,7 @@
         <v>8.6</v>
       </c>
       <c r="AR46" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AS46" t="n">
         <v>40</v>
@@ -9437,7 +9437,7 @@
         <v>46</v>
       </c>
       <c r="BB46" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC46" t="n">
         <v>25</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
         <v>4.3</v>
       </c>
       <c r="L47" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M47" t="n">
         <v>1.07</v>
@@ -9529,10 +9529,10 @@
         <v>3.65</v>
       </c>
       <c r="T47" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="U47" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V47" t="n">
         <v>1.19</v>
@@ -9601,7 +9601,7 @@
         <v>15.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AS47" t="n">
         <v>8.199999999999999</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-19 17:11:30</t>
+          <t>2026-04-19 19:23:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -766,7 +766,7 @@
         <v>2.72</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="J2" t="n">
         <v>2.92</v>
@@ -784,7 +784,7 @@
         <v>2.64</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P2" t="n">
         <v>1.56</v>
@@ -802,10 +802,10 @@
         <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W2" t="n">
         <v>1.45</v>
@@ -865,52 +865,52 @@
         <v>75</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
         <v>16.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.3</v>
+        <v>50</v>
       </c>
       <c r="BB2" t="n">
         <v>40</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
         <v>38</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="G3" t="n">
         <v>1.29</v>
       </c>
       <c r="H3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="J3" t="n">
         <v>6.4</v>
@@ -975,31 +975,31 @@
         <v>1.02</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="P3" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
         <v>2.18</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
         <v>4.4</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1029,22 +1029,22 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1053,68 +1053,68 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
         <v>13.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
         <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G4" t="n">
         <v>1.44</v>
       </c>
       <c r="H4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>10.5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.27</v>
@@ -1193,7 +1193,7 @@
         <v>1.92</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W4" t="n">
         <v>3.25</v>
@@ -1202,7 +1202,7 @@
         <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z4" t="n">
         <v>540</v>
@@ -1283,16 +1283,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD4" t="n">
         <v>18</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>1.43</v>
       </c>
       <c r="I5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="J5" t="n">
         <v>4.6</v>
@@ -1366,13 +1366,13 @@
         <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
         <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
         <v>1.44</v>
@@ -1399,7 +1399,7 @@
         <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>180</v>
@@ -1468,19 +1468,19 @@
         <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="AX5" t="n">
         <v>4.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="AZ5" t="n">
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.48</v>
+        <v>3.9</v>
       </c>
       <c r="BB5" t="n">
         <v>4.2</v>
@@ -1492,17 +1492,17 @@
         <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5" t="n">
         <v>5.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -1542,13 +1542,13 @@
         <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
@@ -1566,7 +1566,7 @@
         <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R6" t="n">
         <v>1.32</v>
@@ -1626,7 +1626,7 @@
         <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
         <v>1000</v>
@@ -1644,13 +1644,13 @@
         <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AT6" t="n">
         <v>6.6</v>
@@ -1659,10 +1659,10 @@
         <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
         <v>9.199999999999999</v>
@@ -1674,29 +1674,29 @@
         <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC6" t="n">
         <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF6" t="n">
         <v>12.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
         <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>1.49</v>
@@ -1787,7 +1787,7 @@
         <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
@@ -1805,7 +1805,7 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG7" t="n">
         <v>11.5</v>
@@ -1817,7 +1817,7 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AK7" t="n">
         <v>48</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1841,22 +1841,22 @@
         <v>10</v>
       </c>
       <c r="AR7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU7" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6</v>
       </c>
       <c r="AV7" t="n">
         <v>14.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -1868,7 +1868,7 @@
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB7" t="n">
         <v>19</v>
@@ -1877,20 +1877,20 @@
         <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
         <v>15.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -1924,19 +1924,19 @@
         <v>1.49</v>
       </c>
       <c r="G8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.22</v>
@@ -1957,7 +1957,7 @@
         <v>1.47</v>
       </c>
       <c r="R8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S8" t="n">
         <v>2.1</v>
@@ -1972,7 +1972,7 @@
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="X8" t="n">
         <v>90</v>
@@ -1999,7 +1999,7 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
         <v>15</v>
@@ -2029,16 +2029,16 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
         <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2050,7 +2050,7 @@
         <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX8" t="n">
         <v>9.4</v>
@@ -2062,7 +2062,7 @@
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB8" t="n">
         <v>8.4</v>
@@ -2071,10 +2071,10 @@
         <v>11.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF8" t="n">
         <v>4.7</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
         <v>2.94</v>
@@ -2154,7 +2154,7 @@
         <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
         <v>1.69</v>
@@ -2169,10 +2169,10 @@
         <v>1.58</v>
       </c>
       <c r="X9" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
@@ -2181,22 +2181,22 @@
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
         <v>14</v>
       </c>
       <c r="AD9" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG9" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
         <v>60</v>
@@ -2265,7 +2265,7 @@
         <v>5.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE9" t="n">
         <v>6</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>4.8</v>
@@ -2342,7 +2342,7 @@
         <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
         <v>1.45</v>
@@ -2351,7 +2351,7 @@
         <v>2.78</v>
       </c>
       <c r="T10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U10" t="n">
         <v>2.2</v>
@@ -2366,7 +2366,7 @@
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
         <v>40</v>
@@ -2417,16 +2417,16 @@
         <v>29</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AR10" t="n">
         <v>11</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
         <v>10.5</v>
@@ -2438,41 +2438,41 @@
         <v>6.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY10" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC10" t="n">
         <v>7</v>
       </c>
-      <c r="BC10" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>4.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>2.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
         <v>3.45</v>
@@ -2712,7 +2712,7 @@
         <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
         <v>1.37</v>
@@ -2721,7 +2721,7 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.25</v>
@@ -2730,34 +2730,34 @@
         <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
         <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T12" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V12" t="n">
         <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X12" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Z12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA12" t="n">
         <v>60</v>
@@ -2766,7 +2766,7 @@
         <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD12" t="n">
         <v>14</v>
@@ -2790,7 +2790,7 @@
         <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>34</v>
@@ -2805,22 +2805,22 @@
         <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="n">
         <v>11.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
         <v>13</v>
@@ -2832,13 +2832,13 @@
         <v>15.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BB12" t="n">
         <v>26</v>
@@ -2847,20 +2847,20 @@
         <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE12" t="n">
         <v>36</v>
       </c>
       <c r="BF12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG12" t="n">
         <v>22</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -2915,10 +2915,10 @@
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>2.02</v>
@@ -2939,7 +2939,7 @@
         <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W13" t="n">
         <v>1.57</v>
@@ -2984,7 +2984,7 @@
         <v>130</v>
       </c>
       <c r="AK13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="n">
         <v>95</v>
@@ -3020,7 +3020,7 @@
         <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
         <v>15.5</v>
@@ -3032,10 +3032,10 @@
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC13" t="n">
         <v>13</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="G14" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
         <v>3.7</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.75</v>
       </c>
       <c r="L14" t="n">
         <v>1.41</v>
@@ -3109,34 +3109,34 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
         <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
         <v>1.75</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="X14" t="n">
         <v>14.5</v>
@@ -3148,13 +3148,13 @@
         <v>32</v>
       </c>
       <c r="AA14" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AB14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
         <v>18</v>
@@ -3163,7 +3163,7 @@
         <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
@@ -3172,13 +3172,13 @@
         <v>18.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AJ14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
         <v>36</v>
@@ -3190,43 +3190,43 @@
         <v>17</v>
       </c>
       <c r="AO14" t="n">
-        <v>240</v>
+        <v>46</v>
       </c>
       <c r="AP14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>14</v>
-      </c>
       <c r="AR14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT14" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
         <v>14</v>
       </c>
       <c r="AW14" t="n">
-        <v>38</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX14" t="n">
         <v>11.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
         <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB14" t="n">
         <v>22</v>
@@ -3238,17 +3238,17 @@
         <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF14" t="n">
         <v>13</v>
       </c>
       <c r="BG14" t="n">
-        <v>38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3476,13 @@
         <v>2.14</v>
       </c>
       <c r="G16" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J16" t="n">
         <v>3.85</v>
@@ -3509,22 +3509,22 @@
         <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
         <v>2.86</v>
       </c>
       <c r="T16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
         <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="X16" t="n">
         <v>22</v>
@@ -3593,7 +3593,7 @@
         <v>5.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
         <v>7.6</v>
@@ -3611,7 +3611,7 @@
         <v>6.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
         <v>5.1</v>
@@ -3620,7 +3620,7 @@
         <v>4.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BD16" t="n">
         <v>5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G17" t="n">
         <v>3.05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I17" t="n">
         <v>2.68</v>
@@ -3685,7 +3685,7 @@
         <v>3.65</v>
       </c>
       <c r="L17" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3694,13 +3694,13 @@
         <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R17" t="n">
         <v>1.39</v>
@@ -3715,7 +3715,7 @@
         <v>2.26</v>
       </c>
       <c r="V17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W17" t="n">
         <v>1.49</v>
@@ -3736,13 +3736,13 @@
         <v>13</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
         <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="AF17" t="n">
         <v>22</v>
@@ -3757,7 +3757,7 @@
         <v>38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>110</v>
+        <v>900</v>
       </c>
       <c r="AK17" t="n">
         <v>34</v>
@@ -3775,7 +3775,7 @@
         <v>22</v>
       </c>
       <c r="AP17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>10.5</v>
@@ -3793,7 +3793,7 @@
         <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW17" t="n">
         <v>18</v>
@@ -3802,13 +3802,13 @@
         <v>19</v>
       </c>
       <c r="AY17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB17" t="n">
         <v>25</v>
@@ -3817,20 +3817,20 @@
         <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE17" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BF17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG17" t="n">
         <v>18.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -3870,13 +3870,13 @@
         <v>1.76</v>
       </c>
       <c r="I18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.11</v>
@@ -3885,19 +3885,19 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -3906,10 +3906,10 @@
         <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W18" t="n">
         <v>1.23</v>
@@ -3924,7 +3924,7 @@
         <v>12</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AB18" t="n">
         <v>19.5</v>
@@ -3936,7 +3936,7 @@
         <v>10.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF18" t="n">
         <v>40</v>
@@ -3963,7 +3963,7 @@
         <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AO18" t="n">
         <v>10.5</v>
@@ -3987,7 +3987,7 @@
         <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW18" t="n">
         <v>15</v>
@@ -4005,16 +4005,16 @@
         <v>16</v>
       </c>
       <c r="BB18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC18" t="n">
         <v>7.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF18" t="n">
         <v>10.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4082,7 @@
         <v>3.45</v>
       </c>
       <c r="O19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P19" t="n">
         <v>1.84</v>
@@ -4097,10 +4097,10 @@
         <v>3.65</v>
       </c>
       <c r="T19" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="U19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V19" t="n">
         <v>1.53</v>
@@ -4109,7 +4109,7 @@
         <v>1.53</v>
       </c>
       <c r="X19" t="n">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="Y19" t="n">
         <v>11.5</v>
@@ -4124,7 +4124,7 @@
         <v>11.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
         <v>14.5</v>
@@ -4157,13 +4157,13 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>8.4</v>
@@ -4172,13 +4172,13 @@
         <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
         <v>9.800000000000001</v>
@@ -4193,32 +4193,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC19" t="n">
         <v>14.5</v>
       </c>
       <c r="BD19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF19" t="n">
         <v>6.8</v>
       </c>
-      <c r="BE19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H20" t="n">
         <v>2.58</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J20" t="n">
         <v>2.78</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.37</v>
@@ -4273,22 +4273,22 @@
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O20" t="n">
         <v>1.37</v>
       </c>
       <c r="P20" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
         <v>1.05</v>
@@ -4300,7 +4300,7 @@
         <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4312,7 +4312,7 @@
         <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB20" t="n">
         <v>1000</v>
@@ -4339,7 +4339,7 @@
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
         <v>1000</v>
@@ -4360,59 +4360,59 @@
         <v>5.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU20" t="n">
         <v>4.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.72</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -4551,10 +4551,10 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR21" t="n">
         <v>7</v>
@@ -4563,34 +4563,34 @@
         <v>7.8</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU21" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
         <v>7.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
         <v>7.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD21" t="n">
         <v>16</v>
@@ -4599,14 +4599,14 @@
         <v>7.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG21" t="n">
         <v>7.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H22" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I22" t="n">
         <v>2.44</v>
@@ -4661,16 +4661,16 @@
         <v>1.14</v>
       </c>
       <c r="N22" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O22" t="n">
         <v>1.61</v>
       </c>
       <c r="P22" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R22" t="n">
         <v>1.17</v>
@@ -4697,13 +4697,13 @@
         <v>7</v>
       </c>
       <c r="Z22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA22" t="n">
         <v>44</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC22" t="n">
         <v>7.2</v>
@@ -4769,13 +4769,13 @@
         <v>30</v>
       </c>
       <c r="AX22" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY22" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA22" t="n">
         <v>34</v>
@@ -4796,11 +4796,11 @@
         <v>36</v>
       </c>
       <c r="BG22" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         <v>4.3</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K23" t="n">
         <v>4.7</v>
@@ -4855,7 +4855,7 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O23" t="n">
         <v>1.15</v>
@@ -4873,10 +4873,10 @@
         <v>2.24</v>
       </c>
       <c r="T23" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="U23" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="V23" t="n">
         <v>1.3</v>
@@ -4906,7 +4906,7 @@
         <v>20</v>
       </c>
       <c r="AE23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF23" t="n">
         <v>15.5</v>
@@ -4915,10 +4915,10 @@
         <v>11.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ23" t="n">
         <v>23</v>
@@ -4936,10 +4936,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AO23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP23" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AQ23" t="n">
         <v>11.5</v>
@@ -4948,7 +4948,7 @@
         <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT23" t="n">
         <v>14</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -5049,13 +5049,13 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O24" t="n">
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q24" t="n">
         <v>1.98</v>
@@ -5070,10 +5070,10 @@
         <v>2.06</v>
       </c>
       <c r="U24" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V24" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W24" t="n">
         <v>2.68</v>
@@ -5085,10 +5085,10 @@
         <v>23</v>
       </c>
       <c r="Z24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA24" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AB24" t="n">
         <v>7.6</v>
@@ -5100,10 +5100,10 @@
         <v>28</v>
       </c>
       <c r="AE24" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG24" t="n">
         <v>9.800000000000001</v>
@@ -5130,7 +5130,7 @@
         <v>10</v>
       </c>
       <c r="AO24" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AP24" t="n">
         <v>13</v>
@@ -5142,7 +5142,7 @@
         <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT24" t="n">
         <v>6.8</v>
@@ -5151,10 +5151,10 @@
         <v>8.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX24" t="n">
         <v>7.8</v>
@@ -5169,13 +5169,13 @@
         <v>14</v>
       </c>
       <c r="BB24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC24" t="n">
         <v>15.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="BE24" t="n">
         <v>28</v>
@@ -5184,11 +5184,11 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -5225,10 +5225,10 @@
         <v>2.1</v>
       </c>
       <c r="H25" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
         <v>3.5</v>
@@ -5237,40 +5237,40 @@
         <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P25" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q25" t="n">
         <v>1.94</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="U25" t="n">
         <v>2.08</v>
       </c>
       <c r="V25" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="X25" t="n">
         <v>16</v>
@@ -5279,7 +5279,7 @@
         <v>17.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
@@ -5291,25 +5291,25 @@
         <v>9.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AG25" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
         <v>22</v>
       </c>
       <c r="AI25" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
         <v>27</v>
@@ -5333,10 +5333,10 @@
         <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -5348,7 +5348,7 @@
         <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
@@ -5357,10 +5357,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BA25" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BB25" t="n">
         <v>11.5</v>
@@ -5369,7 +5369,7 @@
         <v>18.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BE25" t="n">
         <v>26</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
         <v>1.43</v>
@@ -5515,7 +5515,7 @@
         <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO26" t="n">
         <v>25</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
         <v>3.05</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>3.5</v>
@@ -5637,10 +5637,10 @@
         <v>1.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R27" t="n">
         <v>1.43</v>
@@ -5649,25 +5649,25 @@
         <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V27" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W27" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X27" t="n">
         <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA27" t="n">
         <v>48</v>
@@ -5679,28 +5679,28 @@
         <v>7.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>32</v>
       </c>
       <c r="AF27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG27" t="n">
         <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI27" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
         <v>36</v>
@@ -5709,22 +5709,22 @@
         <v>70</v>
       </c>
       <c r="AN27" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO27" t="n">
         <v>27</v>
       </c>
       <c r="AP27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ27" t="n">
         <v>12.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT27" t="n">
         <v>11.5</v>
@@ -5736,7 +5736,7 @@
         <v>12.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX27" t="n">
         <v>16</v>
@@ -5745,16 +5745,16 @@
         <v>11.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB27" t="n">
         <v>32</v>
       </c>
       <c r="BC27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD27" t="n">
         <v>32</v>
@@ -5763,14 +5763,14 @@
         <v>60</v>
       </c>
       <c r="BF27" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -5816,40 +5816,40 @@
         <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
         <v>1.32</v>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q28" t="n">
         <v>1.97</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U28" t="n">
         <v>2.22</v>
       </c>
       <c r="V28" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W28" t="n">
         <v>1.42</v>
@@ -5867,7 +5867,7 @@
         <v>32</v>
       </c>
       <c r="AB28" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC28" t="n">
         <v>8.199999999999999</v>
@@ -5903,7 +5903,7 @@
         <v>95</v>
       </c>
       <c r="AN28" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AO28" t="n">
         <v>19.5</v>
@@ -5921,7 +5921,7 @@
         <v>14.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU28" t="n">
         <v>7.4</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
         <v>1.47</v>
       </c>
       <c r="I29" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>3.7</v>
@@ -6016,16 +6016,16 @@
         <v>1.28</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N29" t="n">
-        <v>3.9</v>
+        <v>1.34</v>
       </c>
       <c r="O29" t="n">
         <v>1.25</v>
       </c>
       <c r="P29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Q29" t="n">
         <v>1.64</v>
@@ -6043,7 +6043,7 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="W29" t="n">
         <v>1.08</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BF29" t="n">
         <v>1.55</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -6213,22 +6213,22 @@
         <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
         <v>1.57</v>
       </c>
       <c r="R30" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
         <v>2.72</v>
       </c>
       <c r="H31" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I31" t="n">
         <v>3.6</v>
@@ -6428,7 +6428,7 @@
         <v>2.06</v>
       </c>
       <c r="U31" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V31" t="n">
         <v>1.4</v>
@@ -6458,7 +6458,7 @@
         <v>18</v>
       </c>
       <c r="AE31" t="n">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AF31" t="n">
         <v>18</v>
@@ -6536,17 +6536,17 @@
         <v>5.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF31" t="n">
         <v>7.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
         <v>5.1</v>
       </c>
       <c r="T32" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U32" t="n">
         <v>1.87</v>
@@ -6631,7 +6631,7 @@
         <v>1.46</v>
       </c>
       <c r="X32" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y32" t="n">
         <v>8.800000000000001</v>
@@ -6685,10 +6685,10 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ32" t="n">
         <v>8</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>7.8</v>
       </c>
       <c r="AR32" t="n">
         <v>15</v>
@@ -6697,13 +6697,13 @@
         <v>25</v>
       </c>
       <c r="AT32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU32" t="n">
         <v>6.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW32" t="n">
         <v>23</v>
@@ -6715,7 +6715,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA32" t="n">
         <v>32</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -6777,16 +6777,16 @@
         <v>3.5</v>
       </c>
       <c r="H33" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="I33" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K33" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="L33" t="n">
         <v>1.74</v>
@@ -6801,16 +6801,16 @@
         <v>1.77</v>
       </c>
       <c r="P33" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
         <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T33" t="n">
         <v>2.5</v>
@@ -6822,16 +6822,16 @@
         <v>1.53</v>
       </c>
       <c r="W33" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X33" t="n">
         <v>6.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z33" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA33" t="n">
         <v>120</v>
@@ -6846,22 +6846,22 @@
         <v>17</v>
       </c>
       <c r="AE33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH33" t="n">
         <v>65</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>110</v>
       </c>
       <c r="AI33" t="n">
         <v>540</v>
       </c>
       <c r="AJ33" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AK33" t="n">
         <v>85</v>
@@ -6891,7 +6891,7 @@
         <v>40</v>
       </c>
       <c r="AT33" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU33" t="n">
         <v>6.2</v>
@@ -6909,7 +6909,7 @@
         <v>15</v>
       </c>
       <c r="AZ33" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BA33" t="n">
         <v>40</v>
@@ -6930,11 +6930,11 @@
         <v>38</v>
       </c>
       <c r="BG33" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -7374,34 +7374,34 @@
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O36" t="n">
         <v>1.42</v>
       </c>
       <c r="P36" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q36" t="n">
         <v>2.12</v>
       </c>
       <c r="R36" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>1.73</v>
       </c>
       <c r="U36" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V36" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="W36" t="n">
         <v>1.22</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -7553,40 +7553,40 @@
         <v>1.55</v>
       </c>
       <c r="H37" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I37" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="J37" t="n">
         <v>3.85</v>
       </c>
       <c r="K37" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L37" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
         <v>1.04</v>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>1.55</v>
       </c>
       <c r="O37" t="n">
         <v>1.31</v>
       </c>
       <c r="P37" t="n">
-        <v>1.86</v>
+        <v>1.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>3.15</v>
+        <v>1.85</v>
       </c>
       <c r="T37" t="n">
         <v>1.03</v>
@@ -7655,7 +7655,7 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.73</v>
+        <v>6.2</v>
       </c>
       <c r="AQ37" t="n">
         <v>4.2</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -7744,16 +7744,16 @@
         <v>3.3</v>
       </c>
       <c r="G38" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H38" t="n">
         <v>2.68</v>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="J38" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="K38" t="n">
         <v>3</v>
@@ -7762,19 +7762,19 @@
         <v>1.7</v>
       </c>
       <c r="M38" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N38" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="O38" t="n">
         <v>1.7</v>
       </c>
       <c r="P38" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R38" t="n">
         <v>1.14</v>
@@ -7783,16 +7783,16 @@
         <v>6.8</v>
       </c>
       <c r="T38" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U38" t="n">
         <v>1.65</v>
       </c>
       <c r="V38" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W38" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X38" t="n">
         <v>7</v>
@@ -7801,7 +7801,7 @@
         <v>7.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA38" t="n">
         <v>400</v>
@@ -7819,16 +7819,16 @@
         <v>48</v>
       </c>
       <c r="AF38" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AG38" t="n">
         <v>17</v>
       </c>
       <c r="AH38" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI38" t="n">
         <v>110</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>240</v>
       </c>
       <c r="AJ38" t="n">
         <v>1000</v>
@@ -7846,25 +7846,25 @@
         <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP38" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR38" t="n">
         <v>14</v>
       </c>
       <c r="AS38" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="AT38" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV38" t="n">
         <v>12.5</v>
@@ -7879,32 +7879,32 @@
         <v>14.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BA38" t="n">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BB38" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="BC38" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BD38" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="BE38" t="n">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="BF38" t="n">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BG38" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>1.5</v>
@@ -7983,10 +7983,10 @@
         <v>1.72</v>
       </c>
       <c r="V39" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W39" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X39" t="n">
         <v>8.6</v>
@@ -7995,7 +7995,7 @@
         <v>11</v>
       </c>
       <c r="Z39" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AA39" t="n">
         <v>85</v>
@@ -8004,13 +8004,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC39" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD39" t="n">
         <v>19</v>
       </c>
       <c r="AE39" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF39" t="n">
         <v>17</v>
@@ -8037,7 +8037,7 @@
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO39" t="n">
         <v>90</v>
@@ -8046,13 +8046,13 @@
         <v>6.8</v>
       </c>
       <c r="AQ39" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR39" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AS39" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT39" t="n">
         <v>6.6</v>
@@ -8061,44 +8061,44 @@
         <v>6</v>
       </c>
       <c r="AV39" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW39" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AX39" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ39" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB39" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BC39" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BF39" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G40" t="n">
         <v>1.74</v>
@@ -8138,7 +8138,7 @@
         <v>6.4</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J40" t="n">
         <v>3.3</v>
@@ -8150,13 +8150,13 @@
         <v>1.37</v>
       </c>
       <c r="M40" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N40" t="n">
         <v>3.15</v>
       </c>
       <c r="O40" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P40" t="n">
         <v>1.73</v>
@@ -8168,7 +8168,7 @@
         <v>1.27</v>
       </c>
       <c r="S40" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T40" t="n">
         <v>1.92</v>
@@ -8255,7 +8255,7 @@
         <v>6.8</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AW40" t="n">
         <v>4.4</v>
@@ -8282,7 +8282,7 @@
         <v>4.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF40" t="n">
         <v>9</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -8323,16 +8323,16 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="G41" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="H41" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I41" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J41" t="n">
         <v>3.25</v>
@@ -8356,25 +8356,25 @@
         <v>1.67</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R41" t="n">
         <v>1.25</v>
       </c>
       <c r="S41" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T41" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V41" t="n">
         <v>1.18</v>
       </c>
       <c r="W41" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8389,7 +8389,7 @@
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC41" t="n">
         <v>1000</v>
@@ -8431,62 +8431,62 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AX41" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AY41" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AZ41" t="n">
         <v>4.3</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BC41" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="BE41" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG41" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -8517,37 +8517,37 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G42" t="n">
         <v>1.85</v>
       </c>
       <c r="H42" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
         <v>6</v>
       </c>
       <c r="J42" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K42" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L42" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M42" t="n">
         <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O42" t="n">
         <v>1.32</v>
       </c>
       <c r="P42" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
@@ -8559,7 +8559,7 @@
         <v>3.35</v>
       </c>
       <c r="T42" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U42" t="n">
         <v>1.98</v>
@@ -8571,7 +8571,7 @@
         <v>2.16</v>
       </c>
       <c r="X42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y42" t="n">
         <v>22</v>
@@ -8631,7 +8631,7 @@
         <v>14.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS42" t="n">
         <v>4.3</v>
@@ -8646,7 +8646,7 @@
         <v>17</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX42" t="n">
         <v>9.199999999999999</v>
@@ -8658,7 +8658,7 @@
         <v>17</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB42" t="n">
         <v>14</v>
@@ -8676,11 +8676,11 @@
         <v>10</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -8711,46 +8711,46 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M43" t="n">
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="O43" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="P43" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.91</v>
+        <v>2.44</v>
       </c>
       <c r="R43" t="n">
         <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>1.91</v>
+        <v>4.7</v>
       </c>
       <c r="T43" t="n">
         <v>1.03</v>
@@ -8765,7 +8765,7 @@
         <v>1.47</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y43" t="n">
         <v>1000</v>
@@ -8822,59 +8822,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -8911,16 +8911,16 @@
         <v>1.46</v>
       </c>
       <c r="H44" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I44" t="n">
         <v>14</v>
       </c>
       <c r="J44" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K44" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L44" t="n">
         <v>1.33</v>
@@ -8935,7 +8935,7 @@
         <v>1.33</v>
       </c>
       <c r="P44" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q44" t="n">
         <v>2.02</v>
@@ -9013,7 +9013,7 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ44" t="n">
         <v>4.9</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G46" t="n">
         <v>2.36</v>
@@ -9308,7 +9308,7 @@
         <v>2.84</v>
       </c>
       <c r="K46" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="L46" t="n">
         <v>1.64</v>
@@ -9335,7 +9335,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="T46" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U46" t="n">
         <v>1.56</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
         <v>4.3</v>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M47" t="n">
         <v>1.07</v>
@@ -9532,7 +9532,7 @@
         <v>1.9</v>
       </c>
       <c r="U47" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V47" t="n">
         <v>1.19</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-19 19:23:40</t>
+          <t>2026-04-19 21:36:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -757,37 +757,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G2" t="n">
         <v>3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="I2" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.56</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q2" t="n">
         <v>2.52</v>
@@ -796,79 +796,79 @@
         <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W2" t="n">
         <v>1.45</v>
       </c>
       <c r="X2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB2" t="n">
         <v>11</v>
       </c>
-      <c r="Y2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF2" t="n">
         <v>20</v>
       </c>
-      <c r="AA2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>21</v>
       </c>
-      <c r="AG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>23</v>
-      </c>
       <c r="AI2" t="n">
-        <v>290</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AL2" t="n">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN2" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AP2" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR2" t="n">
         <v>15</v>
@@ -877,13 +877,13 @@
         <v>18.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>16.5</v>
@@ -892,35 +892,35 @@
         <v>16.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>140</v>
       </c>
       <c r="BF2" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>13.5</v>
       </c>
       <c r="I3" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="J3" t="n">
         <v>6.4</v>
@@ -984,16 +984,16 @@
         <v>2.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R3" t="n">
         <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
         <v>1.76</v>
@@ -1044,7 +1044,7 @@
         <v>10.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1074,7 +1074,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AV3" t="n">
         <v>6.6</v>
@@ -1089,7 +1089,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BA3" t="n">
         <v>7.2</v>
@@ -1098,10 +1098,10 @@
         <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
         <v>7.2</v>
@@ -1110,11 +1110,11 @@
         <v>3.3</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>5.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1184,7 +1184,7 @@
         <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T4" t="n">
         <v>1.91</v>
@@ -1223,7 +1223,7 @@
         <v>160</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
@@ -1256,13 +1256,13 @@
         <v>18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT4" t="n">
         <v>8</v>
@@ -1271,10 +1271,10 @@
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
@@ -1286,7 +1286,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
         <v>10</v>
@@ -1295,20 +1295,20 @@
         <v>12</v>
       </c>
       <c r="BD4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
         <v>3.75</v>
@@ -1375,10 +1375,10 @@
         <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
@@ -1468,7 +1468,7 @@
         <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AX5" t="n">
         <v>4.2</v>
@@ -1492,17 +1492,17 @@
         <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG5" t="n">
         <v>5.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
         <v>3.3</v>
@@ -1686,7 +1686,7 @@
         <v>5.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF6" t="n">
         <v>12.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
         <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.49</v>
@@ -1754,7 +1754,7 @@
         <v>2.98</v>
       </c>
       <c r="O7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P7" t="n">
         <v>1.74</v>
@@ -1799,7 +1799,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
@@ -1835,7 +1835,7 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
         <v>7</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
@@ -1856,7 +1856,7 @@
         <v>14.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX7" t="n">
         <v>9</v>
@@ -1868,7 +1868,7 @@
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
         <v>19</v>
@@ -1877,20 +1877,20 @@
         <v>19</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF7" t="n">
         <v>15.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v>1.58</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
@@ -1936,13 +1936,13 @@
         <v>4.4</v>
       </c>
       <c r="K8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.22</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
         <v>6</v>
@@ -1951,28 +1951,28 @@
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="R8" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X8" t="n">
         <v>90</v>
@@ -2002,7 +2002,7 @@
         <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
@@ -2029,16 +2029,16 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ8" t="n">
         <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2050,7 +2050,7 @@
         <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX8" t="n">
         <v>9.4</v>
@@ -2062,7 +2062,7 @@
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BB8" t="n">
         <v>8.4</v>
@@ -2071,10 +2071,10 @@
         <v>11.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF8" t="n">
         <v>4.7</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.32</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="H9" t="n">
         <v>2.94</v>
@@ -2166,7 +2166,7 @@
         <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X9" t="n">
         <v>970</v>
@@ -2265,7 +2265,7 @@
         <v>5.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE9" t="n">
         <v>6</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -2318,25 +2318,25 @@
         <v>1.83</v>
       </c>
       <c r="I10" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
         <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.24</v>
       </c>
       <c r="P10" t="n">
         <v>2.1</v>
@@ -2345,10 +2345,10 @@
         <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="T10" t="n">
         <v>1.66</v>
@@ -2357,7 +2357,7 @@
         <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="W10" t="n">
         <v>1.26</v>
@@ -2417,7 +2417,7 @@
         <v>29</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
         <v>5.8</v>
@@ -2435,10 +2435,10 @@
         <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AX10" t="n">
         <v>6.6</v>
@@ -2465,14 +2465,14 @@
         <v>7.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>1.65</v>
       </c>
       <c r="G11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H11" t="n">
         <v>5.2</v>
       </c>
       <c r="I11" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J11" t="n">
         <v>4.1</v>
@@ -2533,7 +2533,7 @@
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
         <v>1.69</v>
@@ -2566,37 +2566,37 @@
         <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
         <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
+        <v>400</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
         <v>160</v>
       </c>
-      <c r="AF11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>75</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK11" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL11" t="n">
         <v>32</v>
@@ -2605,68 +2605,68 @@
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
         <v>16.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC11" t="n">
         <v>14.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>12.5</v>
       </c>
       <c r="BD11" t="n">
         <v>16</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
         <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
         <v>1.48</v>
@@ -2766,7 +2766,7 @@
         <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>14</v>
@@ -2790,25 +2790,25 @@
         <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
         <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
         <v>11.5</v>
@@ -2820,7 +2820,7 @@
         <v>11.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
         <v>13</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I13" t="n">
         <v>2.94</v>
@@ -2906,7 +2906,7 @@
         <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.32</v>
@@ -2915,10 +2915,10 @@
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
         <v>2.02</v>
@@ -2933,16 +2933,16 @@
         <v>3.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U13" t="n">
         <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X13" t="n">
         <v>19</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G14" t="n">
         <v>2.16</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I14" t="n">
         <v>3.95</v>
@@ -3100,7 +3100,7 @@
         <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
         <v>1.41</v>
@@ -3133,22 +3133,22 @@
         <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X14" t="n">
         <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Z14" t="n">
         <v>32</v>
       </c>
       <c r="AA14" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="AB14" t="n">
         <v>10.5</v>
@@ -3172,7 +3172,7 @@
         <v>18.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
         <v>26</v>
@@ -3196,16 +3196,16 @@
         <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
         <v>25</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.6</v>
+        <v>60</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU14" t="n">
         <v>7</v>
@@ -3214,19 +3214,19 @@
         <v>14</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX14" t="n">
         <v>11.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
         <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB14" t="n">
         <v>22</v>
@@ -3238,17 +3238,17 @@
         <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF14" t="n">
         <v>13</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         <v>1.55</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S15" t="n">
         <v>2.34</v>
@@ -3324,7 +3324,7 @@
         <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
         <v>1.22</v>
@@ -3360,7 +3360,7 @@
         <v>25</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
         <v>36</v>
@@ -3393,10 +3393,10 @@
         <v>18</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
         <v>9.800000000000001</v>
@@ -3408,7 +3408,7 @@
         <v>15</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -3420,7 +3420,7 @@
         <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB15" t="n">
         <v>14</v>
@@ -3432,17 +3432,17 @@
         <v>13</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF15" t="n">
         <v>6</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -3473,31 +3473,31 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G16" t="n">
         <v>2.24</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I16" t="n">
         <v>3.55</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.25</v>
@@ -3506,16 +3506,16 @@
         <v>2.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
         <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U16" t="n">
         <v>2.3</v>
@@ -3533,16 +3533,16 @@
         <v>18</v>
       </c>
       <c r="Z16" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
         <v>16.5</v>
@@ -3554,22 +3554,22 @@
         <v>18</v>
       </c>
       <c r="AG16" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
         <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ16" t="n">
         <v>34</v>
       </c>
       <c r="AK16" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
         <v>580</v>
@@ -3581,16 +3581,16 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AQ16" t="n">
         <v>8.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
         <v>7.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
@@ -3611,32 +3611,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF16" t="n">
         <v>4.7</v>
       </c>
-      <c r="BD16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG16" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G17" t="n">
         <v>3.05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
         <v>1.39</v>
@@ -3691,10 +3691,10 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -3715,7 +3715,7 @@
         <v>2.26</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W17" t="n">
         <v>1.49</v>
@@ -3730,7 +3730,7 @@
         <v>17.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="n">
         <v>13</v>
@@ -3742,7 +3742,7 @@
         <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF17" t="n">
         <v>22</v>
@@ -3751,7 +3751,7 @@
         <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI17" t="n">
         <v>38</v>
@@ -3784,7 +3784,7 @@
         <v>15.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
@@ -3796,7 +3796,7 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX17" t="n">
         <v>19</v>
@@ -3805,7 +3805,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
         <v>24</v>
@@ -3820,17 +3820,17 @@
         <v>26</v>
       </c>
       <c r="BE17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF17" t="n">
         <v>18</v>
       </c>
       <c r="BG17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G18" t="n">
         <v>5.2</v>
@@ -3942,7 +3942,7 @@
         <v>40</v>
       </c>
       <c r="AG18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH18" t="n">
         <v>22</v>
@@ -3954,10 +3954,10 @@
         <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM18" t="n">
         <v>200</v>
@@ -4005,26 +4005,26 @@
         <v>16</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF18" t="n">
         <v>10.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         <v>2.68</v>
       </c>
       <c r="G19" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I19" t="n">
         <v>2.98</v>
@@ -4073,13 +4073,13 @@
         <v>3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O19" t="n">
         <v>1.34</v>
@@ -4103,7 +4103,7 @@
         <v>2.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
         <v>1.53</v>
@@ -4121,7 +4121,7 @@
         <v>120</v>
       </c>
       <c r="AB19" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC19" t="n">
         <v>7.8</v>
@@ -4145,10 +4145,10 @@
         <v>150</v>
       </c>
       <c r="AJ19" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
         <v>120</v>
@@ -4172,7 +4172,7 @@
         <v>14.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -4184,41 +4184,41 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX19" t="n">
         <v>14</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC19" t="n">
         <v>14.5</v>
       </c>
       <c r="BD19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE19" t="n">
         <v>7.6</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BF19" t="n">
         <v>7.2</v>
       </c>
-      <c r="BF19" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="G20" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H20" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="I20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="J20" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>1.37</v>
@@ -4297,10 +4297,10 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4312,13 +4312,13 @@
         <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
         <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
         <v>1000</v>
@@ -4363,10 +4363,10 @@
         <v>5.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.86</v>
+        <v>1.37</v>
       </c>
       <c r="AT20" t="n">
         <v>5.6</v>
@@ -4375,44 +4375,44 @@
         <v>4.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.74</v>
+        <v>1.3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.86</v>
+        <v>1.37</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.86</v>
+        <v>1.37</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
         <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.04</v>
@@ -4485,7 +4485,7 @@
         <v>2.66</v>
       </c>
       <c r="T21" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U21" t="n">
         <v>2.08</v>
@@ -4518,7 +4518,7 @@
         <v>24</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF21" t="n">
         <v>11</v>
@@ -4530,25 +4530,25 @@
         <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL21" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AM21" t="n">
         <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP21" t="n">
         <v>17.5</v>
@@ -4557,10 +4557,10 @@
         <v>19.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
         <v>8.800000000000001</v>
@@ -4572,7 +4572,7 @@
         <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
         <v>8.800000000000001</v>
@@ -4584,7 +4584,7 @@
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB21" t="n">
         <v>13.5</v>
@@ -4596,17 +4596,17 @@
         <v>16</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
         <v>6.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -4640,19 +4640,19 @@
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H22" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I22" t="n">
         <v>2.44</v>
       </c>
       <c r="J22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.2</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4670,7 +4670,7 @@
         <v>1.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="R22" t="n">
         <v>1.17</v>
@@ -4682,7 +4682,7 @@
         <v>2.26</v>
       </c>
       <c r="U22" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V22" t="n">
         <v>1.69</v>
@@ -4691,7 +4691,7 @@
         <v>1.34</v>
       </c>
       <c r="X22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y22" t="n">
         <v>7</v>
@@ -4703,7 +4703,7 @@
         <v>44</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC22" t="n">
         <v>7.2</v>
@@ -4739,7 +4739,7 @@
         <v>500</v>
       </c>
       <c r="AN22" t="n">
-        <v>130</v>
+        <v>360</v>
       </c>
       <c r="AO22" t="n">
         <v>46</v>
@@ -4748,16 +4748,16 @@
         <v>7.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR22" t="n">
         <v>11.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
@@ -4778,10 +4778,10 @@
         <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB22" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BC22" t="n">
         <v>30</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
         <v>4.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
@@ -4870,7 +4870,7 @@
         <v>1.7</v>
       </c>
       <c r="S23" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T23" t="n">
         <v>1.52</v>
@@ -4903,7 +4903,7 @@
         <v>11</v>
       </c>
       <c r="AD23" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE23" t="n">
         <v>40</v>
@@ -4921,13 +4921,13 @@
         <v>40</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
         <v>18</v>
       </c>
       <c r="AL23" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AM23" t="n">
         <v>60</v>
@@ -4948,7 +4948,7 @@
         <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT23" t="n">
         <v>14</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>1.56</v>
       </c>
       <c r="G24" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H24" t="n">
         <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
         <v>4.4</v>
@@ -5049,13 +5049,13 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
         <v>1.98</v>
@@ -5067,22 +5067,22 @@
         <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
         <v>1.15</v>
       </c>
       <c r="W24" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z24" t="n">
         <v>60</v>
@@ -5118,7 +5118,7 @@
         <v>14.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
         <v>42</v>
@@ -5142,7 +5142,7 @@
         <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT24" t="n">
         <v>6.8</v>
@@ -5154,7 +5154,7 @@
         <v>23</v>
       </c>
       <c r="AW24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX24" t="n">
         <v>7.8</v>
@@ -5184,11 +5184,11 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BG24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G25" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J25" t="n">
         <v>3.5</v>
       </c>
       <c r="K25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L25" t="n">
         <v>1.15</v>
@@ -5243,7 +5243,7 @@
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O25" t="n">
         <v>1.31</v>
@@ -5255,64 +5255,64 @@
         <v>1.94</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S25" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="U25" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X25" t="n">
         <v>16</v>
       </c>
       <c r="Y25" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="AG25" t="n">
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL25" t="n">
         <v>46</v>
@@ -5333,10 +5333,10 @@
         <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -5348,19 +5348,19 @@
         <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
         <v>12</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB25" t="n">
         <v>11.5</v>
@@ -5369,20 +5369,20 @@
         <v>18.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE25" t="n">
         <v>26</v>
       </c>
       <c r="BF25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H26" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I26" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="J26" t="n">
         <v>3.35</v>
@@ -5455,22 +5455,22 @@
         <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U26" t="n">
         <v>1.99</v>
       </c>
       <c r="V26" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W26" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
         <v>11</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z26" t="n">
         <v>13.5</v>
@@ -5509,16 +5509,16 @@
         <v>48</v>
       </c>
       <c r="AL26" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM26" t="n">
         <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP26" t="n">
         <v>10</v>
@@ -5554,7 +5554,7 @@
         <v>18</v>
       </c>
       <c r="BA26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB26" t="n">
         <v>55</v>
@@ -5563,20 +5563,20 @@
         <v>42</v>
       </c>
       <c r="BD26" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BE26" t="n">
         <v>70</v>
       </c>
       <c r="BF26" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BG26" t="n">
         <v>23</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G27" t="n">
         <v>2.6</v>
       </c>
-      <c r="G27" t="n">
-        <v>2.62</v>
-      </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I27" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>3.5</v>
@@ -5634,19 +5634,19 @@
         <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
         <v>1.71</v>
@@ -5655,13 +5655,13 @@
         <v>2.32</v>
       </c>
       <c r="V27" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
         <v>1.62</v>
       </c>
       <c r="X27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y27" t="n">
         <v>13</v>
@@ -5691,7 +5691,7 @@
         <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI27" t="n">
         <v>38</v>
@@ -5709,10 +5709,10 @@
         <v>70</v>
       </c>
       <c r="AN27" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP27" t="n">
         <v>14</v>
@@ -5721,7 +5721,7 @@
         <v>12.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS27" t="n">
         <v>44</v>
@@ -5733,7 +5733,7 @@
         <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW27" t="n">
         <v>29</v>
@@ -5763,14 +5763,14 @@
         <v>60</v>
       </c>
       <c r="BF27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG27" t="n">
         <v>25</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -5816,10 +5816,10 @@
         <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
@@ -5834,7 +5834,7 @@
         <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R28" t="n">
         <v>1.38</v>
@@ -5846,10 +5846,10 @@
         <v>1.77</v>
       </c>
       <c r="U28" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="W28" t="n">
         <v>1.42</v>
@@ -5870,7 +5870,7 @@
         <v>14.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
         <v>11.5</v>
@@ -5891,7 +5891,7 @@
         <v>38</v>
       </c>
       <c r="AJ28" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK28" t="n">
         <v>42</v>
@@ -5900,16 +5900,16 @@
         <v>50</v>
       </c>
       <c r="AM28" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN28" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO28" t="n">
         <v>19.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ28" t="n">
         <v>9.6</v>
@@ -5921,7 +5921,7 @@
         <v>14.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
         <v>7.4</v>
@@ -5930,7 +5930,7 @@
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AX28" t="n">
         <v>19</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -5995,94 +5995,94 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="G29" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="J29" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>11</v>
+        <v>4.9</v>
       </c>
       <c r="L29" t="n">
         <v>1.28</v>
       </c>
       <c r="M29" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>1.34</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
         <v>1.25</v>
       </c>
       <c r="P29" t="n">
-        <v>1.33</v>
+        <v>2.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="V29" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ29" t="n">
         <v>1000</v>
@@ -6091,7 +6091,7 @@
         <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
@@ -6100,65 +6100,65 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.05</v>
+        <v>13</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.06</v>
+        <v>6.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.06</v>
+        <v>7.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.06</v>
+        <v>11</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.06</v>
+        <v>16.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.06</v>
+        <v>7.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.06</v>
+        <v>12</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.06</v>
+        <v>4.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.06</v>
+        <v>17.5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.06</v>
+        <v>15</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.06</v>
+        <v>4.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.06</v>
+        <v>5.1</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.06</v>
+        <v>5</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.06</v>
+        <v>5</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.06</v>
+        <v>5</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.06</v>
+        <v>6.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
@@ -6201,7 +6201,7 @@
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="K30" t="n">
         <v>1000</v>
@@ -6216,7 +6216,7 @@
         <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P30" t="n">
         <v>1.24</v>
@@ -6225,10 +6225,10 @@
         <v>1.57</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -6237,7 +6237,7 @@
         <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W30" t="n">
         <v>1.01</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
         <v>2.72</v>
       </c>
       <c r="H31" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I31" t="n">
         <v>3.6</v>
@@ -6434,7 +6434,7 @@
         <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X31" t="n">
         <v>9.199999999999999</v>
@@ -6446,7 +6446,7 @@
         <v>25</v>
       </c>
       <c r="AA31" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AB31" t="n">
         <v>8.199999999999999</v>
@@ -6470,7 +6470,7 @@
         <v>24</v>
       </c>
       <c r="AI31" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
         <v>220</v>
@@ -6500,7 +6500,7 @@
         <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>50</v>
+        <v>5.6</v>
       </c>
       <c r="AT31" t="n">
         <v>6.6</v>
@@ -6542,11 +6542,11 @@
         <v>7.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>50</v>
+        <v>6.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G32" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H32" t="n">
         <v>2.8</v>
       </c>
       <c r="I32" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L32" t="n">
         <v>1.48</v>
@@ -6625,10 +6625,10 @@
         <v>1.87</v>
       </c>
       <c r="V32" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W32" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X32" t="n">
         <v>9</v>
@@ -6643,7 +6643,7 @@
         <v>280</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC32" t="n">
         <v>7</v>
@@ -6661,13 +6661,13 @@
         <v>14</v>
       </c>
       <c r="AH32" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AI32" t="n">
         <v>380</v>
       </c>
       <c r="AJ32" t="n">
-        <v>340</v>
+        <v>60</v>
       </c>
       <c r="AK32" t="n">
         <v>190</v>
@@ -6694,10 +6694,10 @@
         <v>15</v>
       </c>
       <c r="AS32" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT32" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU32" t="n">
         <v>6.2</v>
@@ -6715,16 +6715,16 @@
         <v>12.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BB32" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="BC32" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BD32" t="n">
         <v>34</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -6798,22 +6798,22 @@
         <v>2.16</v>
       </c>
       <c r="O33" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="P33" t="n">
         <v>1.37</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R33" t="n">
         <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="U33" t="n">
         <v>1.6</v>
@@ -6837,7 +6837,7 @@
         <v>120</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC33" t="n">
         <v>7.4</v>
@@ -6846,7 +6846,7 @@
         <v>17</v>
       </c>
       <c r="AE33" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF33" t="n">
         <v>26</v>
@@ -6855,13 +6855,13 @@
         <v>18.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AI33" t="n">
         <v>540</v>
       </c>
       <c r="AJ33" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AK33" t="n">
         <v>85</v>
@@ -6876,7 +6876,7 @@
         <v>500</v>
       </c>
       <c r="AO33" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AP33" t="n">
         <v>5.8</v>
@@ -6888,7 +6888,7 @@
         <v>14</v>
       </c>
       <c r="AS33" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AT33" t="n">
         <v>7.2</v>
@@ -6903,7 +6903,7 @@
         <v>27</v>
       </c>
       <c r="AX33" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY33" t="n">
         <v>15</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -7249,10 +7249,10 @@
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK35" t="n">
         <v>85</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>65</v>
       </c>
       <c r="AL35" t="n">
         <v>1000</v>
@@ -7276,7 +7276,7 @@
         <v>4</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT35" t="n">
         <v>6.6</v>
@@ -7288,7 +7288,7 @@
         <v>3.85</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX35" t="n">
         <v>9.800000000000001</v>
@@ -7297,32 +7297,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB35" t="n">
         <v>11.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF35" t="n">
         <v>21</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -7359,10 +7359,10 @@
         <v>5.8</v>
       </c>
       <c r="H36" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="I36" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="J36" t="n">
         <v>3.3</v>
@@ -7374,70 +7374,70 @@
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>1.83</v>
+        <v>2.92</v>
       </c>
       <c r="O36" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P36" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="U36" t="n">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="V36" t="n">
         <v>2.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y36" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AB36" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
         <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
@@ -7458,65 +7458,65 @@
         <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.18</v>
+        <v>5.1</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.78</v>
+        <v>6</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.04</v>
+        <v>6.2</v>
       </c>
       <c r="AT36" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.82</v>
+        <v>4.1</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.91</v>
+        <v>4.7</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.06</v>
+        <v>6.2</v>
       </c>
       <c r="AX36" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AY36" t="n">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.06</v>
+        <v>6.2</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.12</v>
+        <v>7.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.18</v>
+        <v>8</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.18</v>
+        <v>8</v>
       </c>
       <c r="BG36" t="n">
-        <v>2.18</v>
+        <v>13</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         <v>6.4</v>
       </c>
       <c r="I37" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="J37" t="n">
         <v>3.85</v>
@@ -7583,10 +7583,10 @@
         <v>1.85</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S37" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="T37" t="n">
         <v>1.03</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>3.3</v>
       </c>
       <c r="G38" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H38" t="n">
         <v>2.68</v>
@@ -7768,19 +7768,19 @@
         <v>2.32</v>
       </c>
       <c r="O38" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="P38" t="n">
         <v>1.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
         <v>1.14</v>
       </c>
       <c r="S38" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="T38" t="n">
         <v>2.36</v>
@@ -7804,7 +7804,7 @@
         <v>15.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="AB38" t="n">
         <v>8.4</v>
@@ -7828,7 +7828,7 @@
         <v>50</v>
       </c>
       <c r="AI38" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AJ38" t="n">
         <v>1000</v>
@@ -7840,7 +7840,7 @@
         <v>540</v>
       </c>
       <c r="AM38" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN38" t="n">
         <v>1000</v>
@@ -7864,13 +7864,13 @@
         <v>7.6</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV38" t="n">
         <v>12.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AX38" t="n">
         <v>18.5</v>
@@ -7888,7 +7888,7 @@
         <v>32</v>
       </c>
       <c r="BC38" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BD38" t="n">
         <v>40</v>
@@ -7900,11 +7900,11 @@
         <v>36</v>
       </c>
       <c r="BG38" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -7935,25 +7935,25 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="M39" t="n">
         <v>1.13</v>
@@ -8046,10 +8046,10 @@
         <v>6.8</v>
       </c>
       <c r="AQ39" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AR39" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AS39" t="n">
         <v>6</v>
@@ -8061,19 +8061,19 @@
         <v>6</v>
       </c>
       <c r="AV39" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AW39" t="n">
         <v>5.8</v>
       </c>
       <c r="AX39" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ39" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BA39" t="n">
         <v>6</v>
@@ -8091,14 +8091,14 @@
         <v>6</v>
       </c>
       <c r="BF39" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG39" t="n">
         <v>6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -8129,37 +8129,37 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G40" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="H40" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="I40" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>3.3</v>
       </c>
       <c r="K40" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L40" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M40" t="n">
         <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P40" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q40" t="n">
         <v>2.02</v>
@@ -8171,16 +8171,16 @@
         <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U40" t="n">
         <v>1.64</v>
       </c>
       <c r="V40" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W40" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8231,7 +8231,7 @@
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
@@ -8243,10 +8243,10 @@
         <v>13.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT40" t="n">
         <v>5.2</v>
@@ -8255,10 +8255,10 @@
         <v>6.8</v>
       </c>
       <c r="AV40" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX40" t="n">
         <v>6.6</v>
@@ -8267,32 +8267,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB40" t="n">
         <v>11.5</v>
       </c>
       <c r="BC40" t="n">
-        <v>4.3</v>
+        <v>14.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF40" t="n">
         <v>9</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="G41" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I41" t="n">
         <v>6.8</v>
       </c>
       <c r="J41" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="K41" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L41" t="n">
         <v>1.42</v>
@@ -8347,13 +8347,13 @@
         <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="O41" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P41" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Q41" t="n">
         <v>2.08</v>
@@ -8371,7 +8371,7 @@
         <v>1.79</v>
       </c>
       <c r="V41" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W41" t="n">
         <v>2</v>
@@ -8392,7 +8392,7 @@
         <v>8.6</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD41" t="n">
         <v>1000</v>
@@ -8431,62 +8431,62 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AQ41" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AR41" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AV41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ41" t="n">
         <v>4.4</v>
       </c>
-      <c r="AW41" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ41" t="n">
+      <c r="BA41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB41" t="n">
         <v>4.3</v>
       </c>
-      <c r="BA41" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC41" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="BE41" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BF41" t="n">
         <v>4</v>
       </c>
       <c r="BG41" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
         <v>1.32</v>
       </c>
       <c r="P42" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q42" t="n">
         <v>2</v>
@@ -8574,10 +8574,10 @@
         <v>17</v>
       </c>
       <c r="Y42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z42" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA42" t="n">
         <v>160</v>
@@ -8586,40 +8586,40 @@
         <v>10</v>
       </c>
       <c r="AC42" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE42" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF42" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG42" t="n">
         <v>12.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI42" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="n">
         <v>23</v>
       </c>
       <c r="AK42" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AM42" t="n">
         <v>140</v>
       </c>
       <c r="AN42" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AO42" t="n">
         <v>110</v>
@@ -8631,10 +8631,10 @@
         <v>14.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AT42" t="n">
         <v>7.2</v>
@@ -8646,7 +8646,7 @@
         <v>17</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX42" t="n">
         <v>9.199999999999999</v>
@@ -8658,7 +8658,7 @@
         <v>17</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BB42" t="n">
         <v>14</v>
@@ -8667,20 +8667,20 @@
         <v>16</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.4</v>
+        <v>26</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BF42" t="n">
         <v>10</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G44" t="n">
         <v>1.46</v>
@@ -8914,13 +8914,13 @@
         <v>10</v>
       </c>
       <c r="I44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J44" t="n">
         <v>4.6</v>
       </c>
       <c r="K44" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L44" t="n">
         <v>1.33</v>
@@ -8971,7 +8971,7 @@
         <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC44" t="n">
         <v>1000</v>
@@ -8983,10 +8983,10 @@
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG44" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH44" t="n">
         <v>1000</v>
@@ -9007,68 +9007,68 @@
         <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO44" t="n">
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AQ44" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AR44" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AS44" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT44" t="n">
         <v>6</v>
       </c>
       <c r="AU44" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AV44" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AW44" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX44" t="n">
         <v>6.4</v>
       </c>
       <c r="AY44" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC44" t="n">
         <v>4.9</v>
       </c>
-      <c r="BA44" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD44" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF44" t="n">
         <v>6.8</v>
       </c>
       <c r="BG44" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
         <v>1.51</v>
       </c>
       <c r="G45" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H45" t="n">
         <v>7</v>
@@ -9144,7 +9144,7 @@
         <v>1.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V45" t="n">
         <v>1.14</v>
@@ -9177,7 +9177,7 @@
         <v>1000</v>
       </c>
       <c r="AF45" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG45" t="n">
         <v>10.5</v>
@@ -9210,7 +9210,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR45" t="n">
         <v>8</v>
@@ -9225,16 +9225,16 @@
         <v>8.6</v>
       </c>
       <c r="AV45" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW45" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX45" t="n">
         <v>8</v>
       </c>
       <c r="AY45" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ45" t="n">
         <v>6.6</v>
@@ -9249,20 +9249,20 @@
         <v>13.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE45" t="n">
         <v>8.6</v>
       </c>
       <c r="BF45" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BG45" t="n">
         <v>8.6</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
         <v>2.98</v>
       </c>
       <c r="L46" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="M46" t="n">
         <v>1.18</v>
@@ -9326,7 +9326,7 @@
         <v>1.37</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
         <v>1.12</v>
@@ -9335,7 +9335,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="T46" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="U46" t="n">
         <v>1.56</v>
@@ -9377,7 +9377,7 @@
         <v>15</v>
       </c>
       <c r="AH46" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AI46" t="n">
         <v>180</v>
@@ -9392,7 +9392,7 @@
         <v>1000</v>
       </c>
       <c r="AM46" t="n">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AN46" t="n">
         <v>1000</v>
@@ -9440,7 +9440,7 @@
         <v>21</v>
       </c>
       <c r="BC46" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BD46" t="n">
         <v>40</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>
@@ -9505,25 +9505,25 @@
         <v>4.3</v>
       </c>
       <c r="L47" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M47" t="n">
         <v>1.07</v>
       </c>
       <c r="N47" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
         <v>1.34</v>
       </c>
       <c r="P47" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q47" t="n">
         <v>2.02</v>
       </c>
       <c r="R47" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S47" t="n">
         <v>3.65</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-19 21:36:15</t>
+          <t>2026-04-19 23:46:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -763,10 +763,10 @@
         <v>3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -775,46 +775,46 @@
         <v>3.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
         <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W2" t="n">
         <v>1.45</v>
       </c>
       <c r="X2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
         <v>16.5</v>
@@ -829,28 +829,28 @@
         <v>7</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
         <v>40</v>
       </c>
       <c r="AF2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH2" t="n">
         <v>20</v>
       </c>
-      <c r="AG2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ2" t="n">
         <v>55</v>
       </c>
       <c r="AK2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL2" t="n">
         <v>160</v>
@@ -862,43 +862,43 @@
         <v>55</v>
       </c>
       <c r="AO2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
         <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
         <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="AX2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY2" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
         <v>22</v>
@@ -907,7 +907,7 @@
         <v>18</v>
       </c>
       <c r="BD2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
         <v>140</v>
@@ -916,11 +916,11 @@
         <v>19</v>
       </c>
       <c r="BG2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -954,55 +954,55 @@
         <v>1.22</v>
       </c>
       <c r="G3" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="H3" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P3" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="S3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1020,7 +1020,7 @@
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1032,16 +1032,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK3" t="n">
         <v>15</v>
@@ -1053,34 +1053,34 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
@@ -1089,32 +1089,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -1145,61 +1145,61 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G4" t="n">
         <v>1.43</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.44</v>
-      </c>
       <c r="H4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>10.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K4" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
         <v>2.36</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="R4" t="n">
         <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U4" t="n">
         <v>1.92</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
         <v>34</v>
@@ -1223,13 +1223,13 @@
         <v>160</v>
       </c>
       <c r="AF4" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
         <v>260</v>
@@ -1241,31 +1241,31 @@
         <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
         <v>390</v>
       </c>
       <c r="AN4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO4" t="n">
         <v>200</v>
       </c>
       <c r="AP4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
@@ -1274,7 +1274,7 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
@@ -1286,10 +1286,10 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BB4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC4" t="n">
         <v>12</v>
@@ -1298,7 +1298,7 @@
         <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF4" t="n">
         <v>5.2</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -1342,28 +1342,28 @@
         <v>7.4</v>
       </c>
       <c r="G5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H5" t="n">
         <v>1.43</v>
       </c>
       <c r="I5" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="J5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
@@ -1372,22 +1372,22 @@
         <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
@@ -1396,10 +1396,10 @@
         <v>90</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA5" t="n">
         <v>180</v>
@@ -1411,7 +1411,7 @@
         <v>42</v>
       </c>
       <c r="AD5" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1444,22 +1444,22 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>29</v>
+        <v>15.5</v>
       </c>
       <c r="AP5" t="n">
         <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AS5" t="n">
         <v>5.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
@@ -1468,19 +1468,19 @@
         <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="AX5" t="n">
         <v>4.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.9</v>
+        <v>2.32</v>
       </c>
       <c r="BB5" t="n">
         <v>4.2</v>
@@ -1492,17 +1492,17 @@
         <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
         <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
         <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
         <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="Y6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1599,10 +1599,10 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
         <v>1000</v>
@@ -1614,10 +1614,10 @@
         <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AH6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
@@ -1629,40 +1629,40 @@
         <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.2</v>
+        <v>40</v>
       </c>
       <c r="AX6" t="n">
         <v>9.199999999999999</v>
@@ -1671,32 +1671,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
         <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
         <v>12.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="G7" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
         <v>1.43</v>
@@ -1760,55 +1760,55 @@
         <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
         <v>1.86</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
         <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>23</v>
@@ -1817,10 +1817,10 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1829,68 +1829,68 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW7" t="n">
         <v>9.4</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AX7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE7" t="n">
         <v>10</v>
       </c>
-      <c r="AR7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF7" t="n">
-        <v>15.5</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -1921,61 +1921,61 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N8" t="n">
         <v>6.4</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N8" t="n">
-        <v>6</v>
       </c>
       <c r="O8" t="n">
         <v>1.16</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="R8" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="S8" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U8" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2017,40 +2017,40 @@
         <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AX8" t="n">
         <v>9.4</v>
@@ -2062,7 +2062,7 @@
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB8" t="n">
         <v>8.4</v>
@@ -2071,10 +2071,10 @@
         <v>11.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF8" t="n">
         <v>4.7</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -2115,76 +2115,76 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G9" t="n">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="H9" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>3.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
         <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
         <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
         <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
         <v>970</v>
@@ -2193,13 +2193,13 @@
         <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AG9" t="n">
         <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
@@ -2217,58 +2217,58 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO9" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV9" t="n">
         <v>4.8</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW9" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="n">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="AY9" t="n">
         <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="BB9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC9" t="n">
         <v>5.5</v>
       </c>
-      <c r="BC9" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD9" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="BF9" t="n">
         <v>5.1</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -2309,82 +2309,82 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G10" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="I10" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>44</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
         <v>1000</v>
@@ -2393,13 +2393,13 @@
         <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
         <v>1000</v>
@@ -2414,65 +2414,65 @@
         <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="AP10" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.8</v>
+        <v>1.72</v>
       </c>
       <c r="AR10" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>1.84</v>
       </c>
       <c r="AT10" t="n">
-        <v>10.5</v>
+        <v>1.84</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>10.5</v>
+        <v>1.85</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.6</v>
+        <v>1.88</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>1.89</v>
       </c>
       <c r="AZ10" t="n">
-        <v>11.5</v>
+        <v>1.84</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.6</v>
+        <v>1.88</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.6</v>
+        <v>1.92</v>
       </c>
       <c r="BC10" t="n">
-        <v>7</v>
+        <v>1.9</v>
       </c>
       <c r="BD10" t="n">
-        <v>7</v>
+        <v>1.9</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.4</v>
+        <v>1.91</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>5</v>
+        <v>2.38</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -2503,67 +2503,67 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="G11" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="H11" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="X11" t="n">
         <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z11" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2575,28 +2575,28 @@
         <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE11" t="n">
-        <v>400</v>
+        <v>95</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AK11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL11" t="n">
         <v>32</v>
@@ -2605,22 +2605,22 @@
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT11" t="n">
         <v>9.199999999999999</v>
@@ -2632,10 +2632,10 @@
         <v>18</v>
       </c>
       <c r="AW11" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY11" t="n">
         <v>8.6</v>
@@ -2644,29 +2644,29 @@
         <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
         <v>16</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="BG11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="H12" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
         <v>3.55</v>
@@ -2721,7 +2721,7 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.25</v>
@@ -2730,46 +2730,46 @@
         <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
         <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U12" t="n">
         <v>2.46</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
         <v>34</v>
@@ -2787,19 +2787,19 @@
         <v>40</v>
       </c>
       <c r="AJ12" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
         <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO12" t="n">
         <v>28</v>
@@ -2808,43 +2808,43 @@
         <v>15</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AT12" t="n">
         <v>11.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW12" t="n">
         <v>30</v>
       </c>
       <c r="AX12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BB12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>29</v>
@@ -2853,14 +2853,14 @@
         <v>36</v>
       </c>
       <c r="BF12" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -2891,61 +2891,61 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G13" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="H13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I13" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="J13" t="n">
         <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
         <v>1.68</v>
       </c>
       <c r="U13" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y13" t="n">
         <v>13.5</v>
@@ -2960,7 +2960,7 @@
         <v>13</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD13" t="n">
         <v>13</v>
@@ -2978,7 +2978,7 @@
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
         <v>130</v>
@@ -2987,7 +2987,7 @@
         <v>75</v>
       </c>
       <c r="AL13" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
@@ -3008,7 +3008,7 @@
         <v>16.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX13" t="n">
         <v>15.5</v>
@@ -3032,19 +3032,19 @@
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC13" t="n">
         <v>13</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF13" t="n">
         <v>17</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G14" t="n">
         <v>2.16</v>
@@ -3109,34 +3109,34 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
         <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
         <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X14" t="n">
         <v>14.5</v>
@@ -3145,7 +3145,7 @@
         <v>16</v>
       </c>
       <c r="Z14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA14" t="n">
         <v>80</v>
@@ -3157,13 +3157,13 @@
         <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
@@ -3172,7 +3172,7 @@
         <v>18.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ14" t="n">
         <v>26</v>
@@ -3181,10 +3181,10 @@
         <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN14" t="n">
         <v>17</v>
@@ -3205,16 +3205,16 @@
         <v>60</v>
       </c>
       <c r="AT14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AX14" t="n">
         <v>11.5</v>
@@ -3226,10 +3226,10 @@
         <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BB14" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="BC14" t="n">
         <v>19</v>
@@ -3238,17 +3238,17 @@
         <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.5</v>
+        <v>65</v>
       </c>
       <c r="BF14" t="n">
         <v>13</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.4</v>
+        <v>19.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="G15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M15" t="n">
         <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="O15" t="n">
         <v>1.18</v>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
         <v>1.61</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3369,7 +3369,7 @@
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK15" t="n">
         <v>65</v>
@@ -3381,34 +3381,34 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU15" t="n">
         <v>8.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
@@ -3417,13 +3417,13 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BB15" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BC15" t="n">
         <v>12.5</v>
@@ -3432,17 +3432,17 @@
         <v>13</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -3473,31 +3473,31 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H16" t="n">
         <v>3.35</v>
       </c>
       <c r="I16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
         <v>1.25</v>
@@ -3506,137 +3506,137 @@
         <v>2.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="Z16" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
         <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="AG16" t="n">
         <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>18.5</v>
+        <v>60</v>
       </c>
       <c r="AI16" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AJ16" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN16" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AO16" t="n">
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU16" t="n">
         <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="AX16" t="n">
         <v>8.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.8</v>
+        <v>18</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -3667,46 +3667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G17" t="n">
         <v>3.05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J17" t="n">
         <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="T17" t="n">
         <v>1.71</v>
@@ -3718,7 +3718,7 @@
         <v>1.59</v>
       </c>
       <c r="W17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X17" t="n">
         <v>15.5</v>
@@ -3730,7 +3730,7 @@
         <v>17.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB17" t="n">
         <v>13</v>
@@ -3742,10 +3742,10 @@
         <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
         <v>13.5</v>
@@ -3757,10 +3757,10 @@
         <v>38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL17" t="n">
         <v>95</v>
@@ -3769,34 +3769,34 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS17" t="n">
         <v>28</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>23</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AX17" t="n">
         <v>19</v>
@@ -3808,29 +3808,29 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB17" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC17" t="n">
         <v>25</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BD17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF17" t="n">
         <v>20</v>
       </c>
-      <c r="BD17" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF17" t="n">
+      <c r="BG17" t="n">
         <v>18</v>
       </c>
-      <c r="BG17" t="n">
-        <v>19</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -3861,43 +3861,43 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G18" t="n">
         <v>5.2</v>
       </c>
       <c r="H18" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="I18" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="J18" t="n">
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -3906,13 +3906,13 @@
         <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="W18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
@@ -3945,25 +3945,25 @@
         <v>20</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AJ18" t="n">
         <v>900</v>
       </c>
       <c r="AK18" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM18" t="n">
         <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="AO18" t="n">
         <v>10.5</v>
@@ -3972,7 +3972,7 @@
         <v>15</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR18" t="n">
         <v>9.800000000000001</v>
@@ -3981,7 +3981,7 @@
         <v>16</v>
       </c>
       <c r="AT18" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AU18" t="n">
         <v>8</v>
@@ -3993,28 +3993,28 @@
         <v>15</v>
       </c>
       <c r="AX18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY18" t="n">
         <v>16</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>14</v>
       </c>
       <c r="AZ18" t="n">
         <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF18" t="n">
         <v>10.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -4058,55 +4058,55 @@
         <v>2.68</v>
       </c>
       <c r="G19" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="H19" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="I19" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
         <v>3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R19" t="n">
         <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
         <v>1.76</v>
       </c>
       <c r="U19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V19" t="n">
         <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X19" t="n">
         <v>19.5</v>
@@ -4121,13 +4121,13 @@
         <v>120</v>
       </c>
       <c r="AB19" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AC19" t="n">
         <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
@@ -4136,7 +4136,7 @@
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
@@ -4166,13 +4166,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -4184,10 +4184,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AY19" t="n">
         <v>10.5</v>
@@ -4199,26 +4199,26 @@
         <v>7.8</v>
       </c>
       <c r="BB19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD19" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>8</v>
-      </c>
       <c r="BE19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF19" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>7.2</v>
       </c>
       <c r="BG19" t="n">
         <v>7.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -4249,58 +4249,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="G20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.4</v>
       </c>
-      <c r="H20" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.95</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>1.68</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.05</v>
+        <v>1.81</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4333,7 +4333,7 @@
         <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
@@ -4363,10 +4363,10 @@
         <v>5.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AT20" t="n">
         <v>5.6</v>
@@ -4375,44 +4375,44 @@
         <v>4.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BF20" t="n">
         <v>1.55</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -4443,64 +4443,64 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="H21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I21" t="n">
         <v>6.4</v>
       </c>
       <c r="J21" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="U21" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="V21" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="X21" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Y21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Z21" t="n">
         <v>140</v>
@@ -4509,104 +4509,104 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AE21" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG21" t="n">
         <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AM21" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>19.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD21" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AT21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>16</v>
-      </c>
       <c r="BE21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H22" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I22" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J22" t="n">
         <v>3.05</v>
@@ -4655,13 +4655,13 @@
         <v>3.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="M22" t="n">
         <v>1.14</v>
       </c>
       <c r="N22" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
         <v>1.61</v>
@@ -4670,7 +4670,7 @@
         <v>1.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
         <v>1.17</v>
@@ -4679,19 +4679,19 @@
         <v>6.2</v>
       </c>
       <c r="T22" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V22" t="n">
         <v>1.69</v>
       </c>
       <c r="W22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y22" t="n">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>13</v>
       </c>
       <c r="AA22" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AB22" t="n">
         <v>9.6</v>
@@ -4715,7 +4715,7 @@
         <v>36</v>
       </c>
       <c r="AF22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG22" t="n">
         <v>17</v>
@@ -4724,40 +4724,40 @@
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AK22" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="AL22" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM22" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AN22" t="n">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="AO22" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR22" t="n">
         <v>11.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
@@ -4766,16 +4766,16 @@
         <v>11.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX22" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AY22" t="n">
         <v>15.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BA22" t="n">
         <v>38</v>
@@ -4784,7 +4784,7 @@
         <v>38</v>
       </c>
       <c r="BC22" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BD22" t="n">
         <v>38</v>
@@ -4796,11 +4796,11 @@
         <v>36</v>
       </c>
       <c r="BG22" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="G23" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I23" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J23" t="n">
         <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O23" t="n">
         <v>1.15</v>
@@ -4864,22 +4864,22 @@
         <v>2.8</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T23" t="n">
         <v>1.5</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.52</v>
-      </c>
       <c r="U23" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
         <v>2.04</v>
@@ -4888,10 +4888,10 @@
         <v>34</v>
       </c>
       <c r="Y23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA23" t="n">
         <v>160</v>
@@ -4903,16 +4903,16 @@
         <v>11</v>
       </c>
       <c r="AD23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH23" t="n">
         <v>16</v>
@@ -4924,19 +4924,19 @@
         <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO23" t="n">
         <v>26</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>28</v>
       </c>
       <c r="AP23" t="n">
         <v>16</v>
@@ -4948,10 +4948,10 @@
         <v>16</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT23" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU23" t="n">
         <v>9</v>
@@ -4975,7 +4975,7 @@
         <v>18</v>
       </c>
       <c r="BB23" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H24" t="n">
         <v>7</v>
@@ -5037,13 +5037,13 @@
         <v>7.6</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
         <v>4.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
@@ -5052,31 +5052,31 @@
         <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R24" t="n">
         <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T24" t="n">
         <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V24" t="n">
         <v>1.15</v>
       </c>
       <c r="W24" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X24" t="n">
         <v>14.5</v>
@@ -5091,43 +5091,43 @@
         <v>700</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC24" t="n">
         <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE24" t="n">
         <v>120</v>
       </c>
       <c r="AF24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ24" t="n">
         <v>14.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM24" t="n">
         <v>180</v>
       </c>
       <c r="AN24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO24" t="n">
         <v>170</v>
@@ -5142,7 +5142,7 @@
         <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AT24" t="n">
         <v>6.8</v>
@@ -5154,10 +5154,10 @@
         <v>23</v>
       </c>
       <c r="AW24" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY24" t="n">
         <v>9.199999999999999</v>
@@ -5166,7 +5166,7 @@
         <v>21</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BB24" t="n">
         <v>13</v>
@@ -5181,14 +5181,14 @@
         <v>28</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -5222,55 +5222,55 @@
         <v>1.98</v>
       </c>
       <c r="G25" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H25" t="n">
         <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
         <v>3.75</v>
       </c>
       <c r="L25" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P25" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T25" t="n">
         <v>1.77</v>
       </c>
       <c r="U25" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V25" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W25" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X25" t="n">
         <v>16</v>
@@ -5288,10 +5288,10 @@
         <v>10</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD25" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
@@ -5309,7 +5309,7 @@
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
         <v>26</v>
@@ -5324,19 +5324,19 @@
         <v>18.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR25" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -5348,7 +5348,7 @@
         <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
@@ -5360,7 +5360,7 @@
         <v>12</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB25" t="n">
         <v>11.5</v>
@@ -5369,20 +5369,20 @@
         <v>18.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BE25" t="n">
         <v>26</v>
       </c>
       <c r="BF25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>3.6</v>
       </c>
       <c r="G26" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H26" t="n">
         <v>2.3</v>
@@ -5425,19 +5425,19 @@
         <v>2.32</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.43</v>
@@ -5446,7 +5446,7 @@
         <v>1.74</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
         <v>1.28</v>
@@ -5455,7 +5455,7 @@
         <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U26" t="n">
         <v>1.99</v>
@@ -5470,7 +5470,7 @@
         <v>11</v>
       </c>
       <c r="Y26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z26" t="n">
         <v>13.5</v>
@@ -5485,10 +5485,10 @@
         <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF26" t="n">
         <v>23</v>
@@ -5500,7 +5500,7 @@
         <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ26" t="n">
         <v>70</v>
@@ -5515,7 +5515,7 @@
         <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO26" t="n">
         <v>24</v>
@@ -5530,7 +5530,7 @@
         <v>12.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT26" t="n">
         <v>10.5</v>
@@ -5542,10 +5542,10 @@
         <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
         <v>14</v>
@@ -5557,26 +5557,26 @@
         <v>40</v>
       </c>
       <c r="BB26" t="n">
+        <v>65</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>44</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF26" t="n">
         <v>55</v>
       </c>
-      <c r="BC26" t="n">
-        <v>42</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>50</v>
-      </c>
       <c r="BG26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
         <v>3.05</v>
-      </c>
-      <c r="I27" t="n">
-        <v>3.1</v>
       </c>
       <c r="J27" t="n">
         <v>3.5</v>
@@ -5631,40 +5631,40 @@
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T27" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="U27" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W27" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X27" t="n">
         <v>14.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z27" t="n">
         <v>20</v>
@@ -5694,13 +5694,13 @@
         <v>15.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ27" t="n">
         <v>36</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
         <v>36</v>
@@ -5709,7 +5709,7 @@
         <v>70</v>
       </c>
       <c r="AN27" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
         <v>29</v>
@@ -5718,22 +5718,22 @@
         <v>14</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS27" t="n">
         <v>44</v>
       </c>
       <c r="AT27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU27" t="n">
         <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW27" t="n">
         <v>29</v>
@@ -5745,7 +5745,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA27" t="n">
         <v>36</v>
@@ -5757,20 +5757,20 @@
         <v>24</v>
       </c>
       <c r="BD27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE27" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BG27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>3.35</v>
       </c>
       <c r="H28" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I28" t="n">
         <v>2.42</v>
@@ -5819,13 +5819,13 @@
         <v>3.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O28" t="n">
         <v>1.32</v>
@@ -5834,19 +5834,19 @@
         <v>1.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R28" t="n">
         <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T28" t="n">
         <v>1.77</v>
       </c>
       <c r="U28" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V28" t="n">
         <v>1.7</v>
@@ -5867,7 +5867,7 @@
         <v>32</v>
       </c>
       <c r="AB28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC28" t="n">
         <v>8</v>
@@ -5882,13 +5882,13 @@
         <v>22</v>
       </c>
       <c r="AG28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH28" t="n">
         <v>17</v>
       </c>
       <c r="AI28" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ28" t="n">
         <v>60</v>
@@ -5897,7 +5897,7 @@
         <v>42</v>
       </c>
       <c r="AL28" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM28" t="n">
         <v>90</v>
@@ -5906,7 +5906,7 @@
         <v>38</v>
       </c>
       <c r="AO28" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
         <v>13</v>
@@ -5921,7 +5921,7 @@
         <v>14.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU28" t="n">
         <v>7.4</v>
@@ -5954,17 +5954,17 @@
         <v>40</v>
       </c>
       <c r="BE28" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="BF28" t="n">
         <v>30</v>
       </c>
       <c r="BG28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -6001,25 +6001,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="I29" t="n">
         <v>1.68</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K29" t="n">
         <v>4.9</v>
       </c>
       <c r="L29" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O29" t="n">
         <v>1.25</v>
@@ -6028,13 +6028,13 @@
         <v>2.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R29" t="n">
         <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T29" t="n">
         <v>1.82</v>
@@ -6061,7 +6061,7 @@
         <v>16</v>
       </c>
       <c r="AB29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC29" t="n">
         <v>10.5</v>
@@ -6073,7 +6073,7 @@
         <v>17.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
         <v>26</v>
@@ -6091,7 +6091,7 @@
         <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
@@ -6127,7 +6127,7 @@
         <v>12</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AY29" t="n">
         <v>17.5</v>
@@ -6136,29 +6136,29 @@
         <v>15</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BB29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC29" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC29" t="n">
-        <v>5</v>
-      </c>
       <c r="BD29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -6189,13 +6189,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>1.39</v>
       </c>
       <c r="H30" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
@@ -6210,25 +6210,25 @@
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="O30" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="Q30" t="n">
         <v>1.57</v>
       </c>
       <c r="R30" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="S30" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -6240,7 +6240,7 @@
         <v>1.12</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6348,11 +6348,11 @@
         <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -6386,67 +6386,67 @@
         <v>2.54</v>
       </c>
       <c r="G31" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="H31" t="n">
         <v>3.3</v>
       </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J31" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K31" t="n">
         <v>3.25</v>
       </c>
       <c r="L31" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M31" t="n">
         <v>1.12</v>
       </c>
       <c r="N31" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="O31" t="n">
         <v>1.52</v>
       </c>
       <c r="P31" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="R31" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U31" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V31" t="n">
         <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X31" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y31" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA31" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB31" t="n">
         <v>8.199999999999999</v>
@@ -6455,19 +6455,19 @@
         <v>8.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AF31" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
@@ -6476,10 +6476,10 @@
         <v>220</v>
       </c>
       <c r="AK31" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AL31" t="n">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
@@ -6491,16 +6491,16 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ31" t="n">
         <v>7.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT31" t="n">
         <v>6.6</v>
@@ -6509,19 +6509,19 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW31" t="n">
         <v>38</v>
       </c>
       <c r="AX31" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY31" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
         <v>50</v>
@@ -6533,20 +6533,20 @@
         <v>16</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF31" t="n">
         <v>7.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -6580,28 +6580,28 @@
         <v>3.05</v>
       </c>
       <c r="G32" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H32" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I32" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J32" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
         <v>3.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="M32" t="n">
         <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O32" t="n">
         <v>1.51</v>
@@ -6610,13 +6610,13 @@
         <v>1.59</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R32" t="n">
         <v>1.21</v>
       </c>
       <c r="S32" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T32" t="n">
         <v>2.06</v>
@@ -6628,7 +6628,7 @@
         <v>1.53</v>
       </c>
       <c r="W32" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X32" t="n">
         <v>9</v>
@@ -6637,7 +6637,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z32" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AA32" t="n">
         <v>280</v>
@@ -6673,13 +6673,13 @@
         <v>190</v>
       </c>
       <c r="AL32" t="n">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="AM32" t="n">
         <v>500</v>
       </c>
       <c r="AN32" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
@@ -6706,7 +6706,7 @@
         <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AX32" t="n">
         <v>16.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>3.25</v>
       </c>
       <c r="G33" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="H33" t="n">
         <v>2.78</v>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J33" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="K33" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="L33" t="n">
         <v>1.74</v>
@@ -6795,22 +6795,22 @@
         <v>1.18</v>
       </c>
       <c r="N33" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="P33" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="R33" t="n">
         <v>1.12</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="T33" t="n">
         <v>2.48</v>
@@ -6822,28 +6822,28 @@
         <v>1.53</v>
       </c>
       <c r="W33" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X33" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Y33" t="n">
         <v>7</v>
       </c>
       <c r="Z33" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA33" t="n">
         <v>120</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE33" t="n">
         <v>130</v>
@@ -6852,7 +6852,7 @@
         <v>26</v>
       </c>
       <c r="AG33" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH33" t="n">
         <v>110</v>
@@ -6861,7 +6861,7 @@
         <v>540</v>
       </c>
       <c r="AJ33" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK33" t="n">
         <v>85</v>
@@ -6888,28 +6888,28 @@
         <v>14</v>
       </c>
       <c r="AS33" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AT33" t="n">
         <v>7.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV33" t="n">
         <v>13.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX33" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AY33" t="n">
         <v>15</v>
       </c>
       <c r="AZ33" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BA33" t="n">
         <v>40</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -6968,10 +6968,10 @@
         <v>2.62</v>
       </c>
       <c r="G34" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H34" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="I34" t="n">
         <v>3.15</v>
@@ -6980,31 +6980,31 @@
         <v>3.15</v>
       </c>
       <c r="K34" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M34" t="n">
         <v>1.09</v>
       </c>
       <c r="N34" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O34" t="n">
         <v>1.39</v>
       </c>
       <c r="P34" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R34" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
         <v>1.84</v>
@@ -7013,10 +7013,10 @@
         <v>2.02</v>
       </c>
       <c r="V34" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W34" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X34" t="n">
         <v>12.5</v>
@@ -7037,25 +7037,25 @@
         <v>8.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH34" t="n">
-        <v>19.5</v>
+        <v>60</v>
       </c>
       <c r="AI34" t="n">
         <v>120</v>
       </c>
       <c r="AJ34" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
         <v>85</v>
@@ -7067,68 +7067,68 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO34" t="n">
         <v>42</v>
       </c>
       <c r="AP34" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="AR34" t="n">
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="AS34" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT34" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="AU34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>14</v>
-      </c>
       <c r="BA34" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BD34" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF34" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -7159,31 +7159,31 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G35" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H35" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I35" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K35" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L35" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M35" t="n">
         <v>1.11</v>
       </c>
       <c r="N35" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="O35" t="n">
         <v>1.47</v>
@@ -7192,7 +7192,7 @@
         <v>1.59</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R35" t="n">
         <v>1.22</v>
@@ -7207,16 +7207,16 @@
         <v>1.7</v>
       </c>
       <c r="V35" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W35" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X35" t="n">
         <v>12</v>
       </c>
       <c r="Y35" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="Z35" t="n">
         <v>34</v>
@@ -7273,10 +7273,10 @@
         <v>5.8</v>
       </c>
       <c r="AR35" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT35" t="n">
         <v>6.6</v>
@@ -7285,10 +7285,10 @@
         <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX35" t="n">
         <v>9.800000000000001</v>
@@ -7297,32 +7297,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB35" t="n">
         <v>11.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF35" t="n">
         <v>21</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -7353,73 +7353,73 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G36" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H36" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I36" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="J36" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K36" t="n">
         <v>3.7</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M36" t="n">
         <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O36" t="n">
         <v>1.43</v>
       </c>
       <c r="P36" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R36" t="n">
         <v>1.24</v>
       </c>
       <c r="S36" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T36" t="n">
         <v>2.04</v>
       </c>
       <c r="U36" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V36" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W36" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X36" t="n">
         <v>13</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC36" t="n">
         <v>1000</v>
@@ -7431,7 +7431,7 @@
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG36" t="n">
         <v>1000</v>
@@ -7458,65 +7458,65 @@
         <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AP36" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="AQ36" t="n">
         <v>6</v>
       </c>
       <c r="AR36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC36" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV36" t="n">
+      <c r="BD36" t="n">
         <v>4.7</v>
       </c>
-      <c r="AW36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>4</v>
-      </c>
       <c r="BE36" t="n">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="BF36" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="BG36" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G37" t="n">
         <v>1.55</v>
@@ -7559,34 +7559,34 @@
         <v>32</v>
       </c>
       <c r="J37" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K37" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M37" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>1.55</v>
+        <v>3.65</v>
       </c>
       <c r="O37" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P37" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="R37" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="S37" t="n">
-        <v>1.86</v>
+        <v>3.5</v>
       </c>
       <c r="T37" t="n">
         <v>1.03</v>
@@ -7595,7 +7595,7 @@
         <v>1.03</v>
       </c>
       <c r="V37" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W37" t="n">
         <v>2.8</v>
@@ -7694,10 +7694,10 @@
         <v>6.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BE37" t="n">
         <v>1.88</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -7750,46 +7750,46 @@
         <v>2.68</v>
       </c>
       <c r="I38" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J38" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L38" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M38" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N38" t="n">
         <v>2.32</v>
       </c>
       <c r="O38" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="P38" t="n">
         <v>1.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
         <v>1.14</v>
       </c>
       <c r="S38" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="T38" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U38" t="n">
         <v>1.65</v>
       </c>
       <c r="V38" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W38" t="n">
         <v>1.4</v>
@@ -7804,7 +7804,7 @@
         <v>15.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>110</v>
+        <v>400</v>
       </c>
       <c r="AB38" t="n">
         <v>8.4</v>
@@ -7831,7 +7831,7 @@
         <v>240</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK38" t="n">
         <v>150</v>
@@ -7858,16 +7858,16 @@
         <v>14</v>
       </c>
       <c r="AS38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT38" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW38" t="n">
         <v>26</v>
@@ -7876,7 +7876,7 @@
         <v>18.5</v>
       </c>
       <c r="AY38" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ38" t="n">
         <v>24</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -7935,112 +7935,112 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G39" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="H39" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I39" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J39" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K39" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O39" t="n">
         <v>1.58</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.55</v>
       </c>
       <c r="P39" t="n">
         <v>1.47</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
       <c r="R39" t="n">
         <v>1.17</v>
       </c>
       <c r="S39" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U39" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V39" t="n">
         <v>1.37</v>
       </c>
       <c r="W39" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X39" t="n">
         <v>8.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z39" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA39" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG39" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI39" t="n">
         <v>100</v>
       </c>
       <c r="AJ39" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK39" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL39" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO39" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP39" t="n">
         <v>6.8</v>
@@ -8052,7 +8052,7 @@
         <v>15.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT39" t="n">
         <v>6.6</v>
@@ -8064,7 +8064,7 @@
         <v>11.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX39" t="n">
         <v>11.5</v>
@@ -8076,29 +8076,29 @@
         <v>17</v>
       </c>
       <c r="BA39" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB39" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC39" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD39" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF39" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG39" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -8129,46 +8129,46 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G40" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="H40" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="I40" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K40" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L40" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M40" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O40" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P40" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="R40" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T40" t="n">
         <v>1.93</v>
@@ -8177,10 +8177,10 @@
         <v>1.64</v>
       </c>
       <c r="V40" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W40" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8231,7 +8231,7 @@
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
@@ -8243,10 +8243,10 @@
         <v>13.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS40" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT40" t="n">
         <v>5.2</v>
@@ -8255,10 +8255,10 @@
         <v>6.8</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW40" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX40" t="n">
         <v>6.6</v>
@@ -8267,10 +8267,10 @@
         <v>7.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BA40" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB40" t="n">
         <v>11.5</v>
@@ -8279,7 +8279,7 @@
         <v>14.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE40" t="n">
         <v>4.8</v>
@@ -8288,11 +8288,11 @@
         <v>9</v>
       </c>
       <c r="BG40" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -8323,58 +8323,58 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="H41" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I41" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J41" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="M41" t="n">
         <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="O41" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P41" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S41" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="V41" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W41" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8389,10 +8389,10 @@
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD41" t="n">
         <v>1000</v>
@@ -8431,62 +8431,62 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AR41" t="n">
-        <v>4.7</v>
+        <v>2.66</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.55</v>
+        <v>2.76</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AV41" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW41" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="AX41" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AY41" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AZ41" t="n">
-        <v>4.4</v>
+        <v>2.54</v>
       </c>
       <c r="BA41" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="BC41" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.7</v>
+        <v>2.68</v>
       </c>
       <c r="BE41" t="n">
-        <v>3.55</v>
+        <v>2.76</v>
       </c>
       <c r="BF41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG41" t="n">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -8517,58 +8517,58 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G42" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I42" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J42" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K42" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L42" t="n">
         <v>1.39</v>
       </c>
       <c r="M42" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O42" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P42" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="R42" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S42" t="n">
         <v>3.35</v>
       </c>
       <c r="T42" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U42" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W42" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X42" t="n">
         <v>17</v>
@@ -8577,7 +8577,7 @@
         <v>21</v>
       </c>
       <c r="Z42" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA42" t="n">
         <v>160</v>
@@ -8598,7 +8598,7 @@
         <v>11.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH42" t="n">
         <v>22</v>
@@ -8607,7 +8607,7 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK42" t="n">
         <v>21</v>
@@ -8616,13 +8616,13 @@
         <v>40</v>
       </c>
       <c r="AM42" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN42" t="n">
         <v>13</v>
       </c>
       <c r="AO42" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP42" t="n">
         <v>12</v>
@@ -8631,13 +8631,13 @@
         <v>14.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS42" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT42" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU42" t="n">
         <v>7.4</v>
@@ -8646,7 +8646,7 @@
         <v>17</v>
       </c>
       <c r="AW42" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX42" t="n">
         <v>9.199999999999999</v>
@@ -8658,10 +8658,10 @@
         <v>17</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB42" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BC42" t="n">
         <v>16</v>
@@ -8670,17 +8670,17 @@
         <v>26</v>
       </c>
       <c r="BE42" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF42" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG42" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -8714,43 +8714,43 @@
         <v>2.8</v>
       </c>
       <c r="G43" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H43" t="n">
         <v>2.96</v>
       </c>
       <c r="I43" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N43" t="n">
         <v>2.62</v>
       </c>
-      <c r="K43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2.16</v>
-      </c>
       <c r="O43" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="P43" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="R43" t="n">
         <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="T43" t="n">
         <v>1.03</v>
@@ -8759,13 +8759,13 @@
         <v>1.03</v>
       </c>
       <c r="V43" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W43" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X43" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y43" t="n">
         <v>1000</v>
@@ -8822,59 +8822,59 @@
         <v>1.01</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -8905,61 +8905,61 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G44" t="n">
         <v>1.46</v>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="I44" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J44" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K44" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L44" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="M44" t="n">
         <v>1.07</v>
       </c>
       <c r="N44" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O44" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P44" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R44" t="n">
         <v>1.32</v>
       </c>
       <c r="S44" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T44" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="U44" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="V44" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W44" t="n">
         <v>3.15</v>
       </c>
       <c r="X44" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y44" t="n">
         <v>34</v>
@@ -8971,10 +8971,10 @@
         <v>1000</v>
       </c>
       <c r="AB44" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD44" t="n">
         <v>1000</v>
@@ -8983,92 +8983,92 @@
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG44" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP44" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AQ44" t="n">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="AS44" t="n">
-        <v>6.4</v>
+        <v>55</v>
       </c>
       <c r="AT44" t="n">
         <v>6</v>
       </c>
       <c r="AU44" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV44" t="n">
-        <v>5.7</v>
+        <v>23</v>
       </c>
       <c r="AW44" t="n">
-        <v>6.2</v>
+        <v>46</v>
       </c>
       <c r="AX44" t="n">
         <v>6.4</v>
       </c>
       <c r="AY44" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="AZ44" t="n">
-        <v>5.5</v>
+        <v>28</v>
       </c>
       <c r="BA44" t="n">
-        <v>6.2</v>
+        <v>46</v>
       </c>
       <c r="BB44" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BC44" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="BD44" t="n">
-        <v>5.8</v>
+        <v>28</v>
       </c>
       <c r="BE44" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BF44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG44" t="n">
-        <v>6.2</v>
+        <v>55</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -9099,55 +9099,55 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="G45" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I45" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J45" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K45" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L45" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="M45" t="n">
         <v>1.05</v>
       </c>
       <c r="N45" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O45" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P45" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="R45" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T45" t="n">
         <v>1.9</v>
       </c>
       <c r="U45" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V45" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W45" t="n">
         <v>2.78</v>
@@ -9168,7 +9168,7 @@
         <v>9</v>
       </c>
       <c r="AC45" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD45" t="n">
         <v>1000</v>
@@ -9192,7 +9192,7 @@
         <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL45" t="n">
         <v>1000</v>
@@ -9201,7 +9201,7 @@
         <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO45" t="n">
         <v>1000</v>
@@ -9210,13 +9210,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AR45" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS45" t="n">
         <v>8</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AT45" t="n">
         <v>7.4</v>
@@ -9225,10 +9225,10 @@
         <v>8.6</v>
       </c>
       <c r="AV45" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AW45" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX45" t="n">
         <v>8</v>
@@ -9237,10 +9237,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ45" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA45" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB45" t="n">
         <v>12</v>
@@ -9249,20 +9249,20 @@
         <v>13.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BF45" t="n">
         <v>7</v>
       </c>
       <c r="BG45" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G46" t="n">
         <v>2.36</v>
@@ -9302,37 +9302,37 @@
         <v>4.3</v>
       </c>
       <c r="I46" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J46" t="n">
         <v>2.84</v>
       </c>
       <c r="K46" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="L46" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="M46" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N46" t="n">
         <v>2.18</v>
       </c>
       <c r="O46" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="P46" t="n">
         <v>1.37</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R46" t="n">
         <v>1.12</v>
       </c>
       <c r="S46" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="T46" t="n">
         <v>2.64</v>
@@ -9341,7 +9341,7 @@
         <v>1.56</v>
       </c>
       <c r="V46" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W46" t="n">
         <v>1.73</v>
@@ -9350,10 +9350,10 @@
         <v>6.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA46" t="n">
         <v>1000</v>
@@ -9404,7 +9404,7 @@
         <v>5.8</v>
       </c>
       <c r="AQ46" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR46" t="n">
         <v>24</v>
@@ -9419,7 +9419,7 @@
         <v>6.8</v>
       </c>
       <c r="AV46" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW46" t="n">
         <v>38</v>
@@ -9437,7 +9437,7 @@
         <v>46</v>
       </c>
       <c r="BB46" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC46" t="n">
         <v>36</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="G47" t="n">
         <v>1.75</v>
@@ -9496,46 +9496,46 @@
         <v>5.7</v>
       </c>
       <c r="I47" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J47" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K47" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L47" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M47" t="n">
         <v>1.07</v>
       </c>
       <c r="N47" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O47" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P47" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Q47" t="n">
         <v>2.02</v>
       </c>
       <c r="R47" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S47" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T47" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U47" t="n">
         <v>1.91</v>
       </c>
       <c r="V47" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W47" t="n">
         <v>2.32</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-19 23:46:28</t>
+          <t>2026-04-20 01:57:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J2" t="n">
         <v>3.05</v>
@@ -775,46 +775,46 @@
         <v>3.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
         <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W2" t="n">
         <v>1.45</v>
       </c>
       <c r="X2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>16.5</v>
@@ -838,10 +838,10 @@
         <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
         <v>160</v>
@@ -856,7 +856,7 @@
         <v>160</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>55</v>
@@ -865,7 +865,7 @@
         <v>46</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
         <v>8</v>
@@ -874,7 +874,7 @@
         <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AT2" t="n">
         <v>8.6</v>
@@ -889,19 +889,19 @@
         <v>34</v>
       </c>
       <c r="AX2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2" t="n">
         <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="BC2" t="n">
         <v>18</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="G3" t="n">
         <v>1.26</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I3" t="n">
         <v>19</v>
@@ -972,7 +972,7 @@
         <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N3" t="n">
         <v>6</v>
@@ -981,7 +981,7 @@
         <v>1.15</v>
       </c>
       <c r="P3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
         <v>1.48</v>
@@ -993,16 +993,16 @@
         <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1020,7 +1020,7 @@
         <v>11.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1041,7 +1041,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>15</v>
@@ -1053,58 +1053,58 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS3" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AT3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
         <v>2.94</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
         <v>1.33</v>
@@ -1178,58 +1178,58 @@
         <v>2.36</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T4" t="n">
         <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V4" t="n">
         <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z4" t="n">
-        <v>540</v>
+        <v>85</v>
       </c>
       <c r="AA4" t="n">
         <v>360</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
         <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE4" t="n">
         <v>160</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
         <v>260</v>
@@ -1238,7 +1238,7 @@
         <v>12.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL4" t="n">
         <v>34</v>
@@ -1247,25 +1247,25 @@
         <v>390</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AS4" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
@@ -1274,7 +1274,7 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
@@ -1286,7 +1286,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BB4" t="n">
         <v>10.5</v>
@@ -1298,17 +1298,17 @@
         <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG4" t="n">
         <v>15</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
         <v>8.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I5" t="n">
         <v>1.46</v>
       </c>
       <c r="J5" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>1.35</v>
@@ -1387,7 +1387,7 @@
         <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
@@ -1411,7 +1411,7 @@
         <v>42</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1444,10 +1444,10 @@
         <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.1</v>
@@ -1459,7 +1459,7 @@
         <v>5.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
@@ -1468,19 +1468,19 @@
         <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
         <v>4.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.2</v>
+        <v>19.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.32</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>4.2</v>
@@ -1492,17 +1492,17 @@
         <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>2.58</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.44</v>
@@ -1557,31 +1557,31 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
         <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
         <v>1.96</v>
@@ -1614,19 +1614,19 @@
         <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
         <v>500</v>
@@ -1641,28 +1641,28 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ6" t="n">
         <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
         <v>9.199999999999999</v>
@@ -1671,22 +1671,22 @@
         <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC6" t="n">
         <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
         <v>12.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.5</v>
@@ -1751,16 +1751,16 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
         <v>1.43</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
         <v>1.26</v>
@@ -1769,16 +1769,16 @@
         <v>4.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
         <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X7" t="n">
         <v>11</v>
@@ -1787,10 +1787,10 @@
         <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
         <v>7.6</v>
@@ -1799,10 +1799,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
         <v>11.5</v>
@@ -1823,74 +1823,74 @@
         <v>25</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB7" t="n">
         <v>19.5</v>
       </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BC7" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BE7" t="n">
         <v>10</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -1948,25 +1948,25 @@
         <v>6.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
@@ -1990,7 +1990,7 @@
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
         <v>1000</v>
@@ -2002,13 +2002,13 @@
         <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ8" t="n">
         <v>1000</v>
@@ -2017,25 +2017,25 @@
         <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AS8" t="n">
         <v>4.2</v>
@@ -2044,47 +2044,47 @@
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV8" t="n">
         <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="AX8" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE8" t="n">
         <v>11.5</v>
       </c>
-      <c r="BD8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BF8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G9" t="n">
         <v>2.58</v>
@@ -2124,28 +2124,28 @@
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
         <v>1.89</v>
@@ -2157,7 +2157,7 @@
         <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U9" t="n">
         <v>2.2</v>
@@ -2169,37 +2169,37 @@
         <v>1.63</v>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="Y9" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="Z9" t="n">
         <v>500</v>
       </c>
       <c r="AA9" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>70</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>500</v>
@@ -2223,62 +2223,62 @@
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="AS9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV9" t="n">
         <v>6</v>
       </c>
-      <c r="AT9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AW9" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.05</v>
+        <v>9.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.6</v>
+        <v>25</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="G10" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="I10" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.35</v>
@@ -2345,134 +2345,134 @@
         <v>1.73</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
         <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AC10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH10" t="n">
         <v>42</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
         <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
-        <v>85</v>
+        <v>10.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.72</v>
+        <v>9.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.84</v>
+        <v>9.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.84</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.85</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.88</v>
+        <v>16</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.89</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.84</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.88</v>
+        <v>18</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.92</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.9</v>
+        <v>38</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.9</v>
+        <v>23</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.91</v>
+        <v>8.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.9</v>
+        <v>8.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.38</v>
+        <v>8.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2503,67 +2503,67 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="G11" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="I11" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
         <v>1.67</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T11" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="X11" t="n">
         <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Z11" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2572,19 +2572,19 @@
         <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>28</v>
+        <v>170</v>
       </c>
       <c r="AE11" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG11" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
@@ -2593,10 +2593,10 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL11" t="n">
         <v>32</v>
@@ -2605,68 +2605,68 @@
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="AX11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY11" t="n">
         <v>9</v>
       </c>
-      <c r="AY11" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BB11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC11" t="n">
         <v>12.5</v>
       </c>
-      <c r="BC11" t="n">
-        <v>13</v>
-      </c>
       <c r="BD11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>2.44</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
         <v>3.3</v>
@@ -2727,7 +2727,7 @@
         <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
         <v>1.8</v>
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U12" t="n">
         <v>2.46</v>
@@ -2748,7 +2748,7 @@
         <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X12" t="n">
         <v>16.5</v>
@@ -2766,13 +2766,13 @@
         <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
         <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF12" t="n">
         <v>17</v>
@@ -2784,7 +2784,7 @@
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AJ12" t="n">
         <v>32</v>
@@ -2799,19 +2799,19 @@
         <v>70</v>
       </c>
       <c r="AN12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
         <v>28</v>
       </c>
       <c r="AP12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS12" t="n">
         <v>46</v>
@@ -2835,7 +2835,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA12" t="n">
         <v>36</v>
@@ -2856,11 +2856,11 @@
         <v>14.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>2.88</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
         <v>3.85</v>
@@ -2921,22 +2921,22 @@
         <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V13" t="n">
         <v>1.53</v>
@@ -2945,13 +2945,13 @@
         <v>1.59</v>
       </c>
       <c r="X13" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Y13" t="n">
         <v>13.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="AA13" t="n">
         <v>280</v>
@@ -2966,37 +2966,37 @@
         <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AF13" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
         <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="AK13" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO13" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AP13" t="n">
         <v>13.5</v>
@@ -3008,19 +3008,19 @@
         <v>16.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
         <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
         <v>15.5</v>
@@ -3032,29 +3032,29 @@
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
       <c r="BC13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BF13" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.12</v>
       </c>
       <c r="G14" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H14" t="n">
         <v>3.9</v>
@@ -3115,7 +3115,7 @@
         <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
         <v>1.94</v>
@@ -3124,55 +3124,55 @@
         <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
         <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
         <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X14" t="n">
         <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z14" t="n">
         <v>30</v>
       </c>
       <c r="AA14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB14" t="n">
         <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
         <v>44</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG14" t="n">
         <v>10.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ14" t="n">
         <v>26</v>
@@ -3187,10 +3187,10 @@
         <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AP14" t="n">
         <v>13</v>
@@ -3211,7 +3211,7 @@
         <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
@@ -3226,10 +3226,10 @@
         <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BB14" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BC14" t="n">
         <v>19</v>
@@ -3238,17 +3238,17 @@
         <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="BF14" t="n">
         <v>13</v>
       </c>
       <c r="BG14" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
         <v>5.2</v>
@@ -3294,7 +3294,7 @@
         <v>4.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
         <v>1.28</v>
@@ -3330,7 +3330,7 @@
         <v>1.24</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3369,7 +3369,7 @@
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
         <v>65</v>
@@ -3402,10 +3402,10 @@
         <v>10</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G16" t="n">
         <v>2.26</v>
@@ -3482,43 +3482,43 @@
         <v>3.35</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="V16" t="n">
         <v>1.4</v>
@@ -3527,116 +3527,116 @@
         <v>1.79</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
         <v>30</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF16" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>60</v>
+        <v>15.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK16" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="n">
-        <v>320</v>
+        <v>70</v>
       </c>
       <c r="AN16" t="n">
         <v>36</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AR16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT16" t="n">
         <v>11.5</v>
       </c>
-      <c r="AS16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD16" t="n">
         <v>16</v>
       </c>
-      <c r="AX16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BE16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BF16" t="n">
         <v>12</v>
       </c>
-      <c r="BF16" t="n">
-        <v>7</v>
-      </c>
       <c r="BG16" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3673,16 +3673,16 @@
         <v>3.05</v>
       </c>
       <c r="H17" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L17" t="n">
         <v>1.41</v>
@@ -3700,7 +3700,7 @@
         <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
@@ -3709,28 +3709,28 @@
         <v>3.35</v>
       </c>
       <c r="T17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U17" t="n">
         <v>2.26</v>
       </c>
       <c r="V17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="n">
         <v>13</v>
@@ -3739,16 +3739,16 @@
         <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
         <v>28</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH17" t="n">
         <v>16</v>
@@ -3757,34 +3757,34 @@
         <v>38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL17" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR17" t="n">
         <v>15</v>
       </c>
       <c r="AS17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
@@ -3796,10 +3796,10 @@
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY17" t="n">
         <v>11.5</v>
@@ -3808,29 +3808,29 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB17" t="n">
         <v>25</v>
       </c>
-      <c r="BB17" t="n">
-        <v>29</v>
-      </c>
       <c r="BC17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BE17" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BF17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G18" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="J18" t="n">
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.36</v>
@@ -3885,16 +3885,16 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
         <v>1.26</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R18" t="n">
         <v>1.45</v>
@@ -3906,16 +3906,16 @@
         <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V18" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="W18" t="n">
         <v>1.25</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y18" t="n">
         <v>10.5</v>
@@ -3942,10 +3942,10 @@
         <v>40</v>
       </c>
       <c r="AG18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
         <v>30</v>
@@ -3969,16 +3969,16 @@
         <v>10.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AS18" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT18" t="n">
         <v>16.5</v>
@@ -4008,23 +4008,23 @@
         <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BF18" t="n">
         <v>10.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H19" t="n">
         <v>2.68</v>
       </c>
-      <c r="G19" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.82</v>
-      </c>
       <c r="I19" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
         <v>3.6</v>
@@ -4076,7 +4076,7 @@
         <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
         <v>3.6</v>
@@ -4088,10 +4088,10 @@
         <v>1.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
         <v>3.75</v>
@@ -4103,10 +4103,10 @@
         <v>2.12</v>
       </c>
       <c r="V19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.51</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.57</v>
       </c>
       <c r="X19" t="n">
         <v>19.5</v>
@@ -4115,43 +4115,43 @@
         <v>11.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AB19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
         <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AJ19" t="n">
         <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL19" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -4166,59 +4166,59 @@
         <v>11.5</v>
       </c>
       <c r="AQ19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS19" t="n">
         <v>10</v>
       </c>
-      <c r="AR19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AT19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU19" t="n">
         <v>6.8</v>
       </c>
       <c r="AV19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA19" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AW19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY19" t="n">
+      <c r="BB19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE19" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G20" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H20" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="I20" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
         <v>3.4</v>
@@ -4276,13 +4276,13 @@
         <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P20" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R20" t="n">
         <v>1.28</v>
@@ -4291,128 +4291,128 @@
         <v>4.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U20" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
         <v>1.51</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ20" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.48</v>
+        <v>8.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.4</v>
+        <v>38</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.39</v>
+        <v>29</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.45</v>
+        <v>16</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.42</v>
+        <v>10.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.46</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.4</v>
+        <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.39</v>
+        <v>38</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.38</v>
+        <v>16</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.39</v>
+        <v>40</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.4</v>
+        <v>9.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.8</v>
+        <v>29</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4443,64 +4443,64 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G21" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H21" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P21" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="U21" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="V21" t="n">
         <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X21" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z21" t="n">
         <v>140</v>
@@ -4509,104 +4509,104 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
         <v>40</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF21" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
         <v>85</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AR21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU21" t="n">
         <v>8.6</v>
       </c>
-      <c r="AS21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AV21" t="n">
-        <v>7.2</v>
+        <v>18.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX21" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY21" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4637,170 +4637,170 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G22" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="H22" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I22" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="R22" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="S22" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="V22" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="W22" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X22" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z22" t="n">
         <v>13</v>
       </c>
       <c r="AA22" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC22" t="n">
         <v>7.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AF22" t="n">
         <v>24</v>
       </c>
       <c r="AG22" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AI22" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AL22" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AM22" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="AN22" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AO22" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS22" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AX22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY22" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BA22" t="n">
         <v>38</v>
       </c>
       <c r="BB22" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BC22" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BD22" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BE22" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="BF22" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BG22" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="H23" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="I23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J23" t="n">
         <v>4.1</v>
       </c>
-      <c r="J23" t="n">
-        <v>4.2</v>
-      </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
         <v>1.28</v>
@@ -4861,40 +4861,40 @@
         <v>1.15</v>
       </c>
       <c r="P23" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="Q23" t="n">
         <v>1.51</v>
       </c>
       <c r="R23" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T23" t="n">
         <v>1.5</v>
       </c>
       <c r="U23" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W23" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="X23" t="n">
         <v>34</v>
       </c>
       <c r="Y23" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Z23" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA23" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AB23" t="n">
         <v>17.5</v>
@@ -4903,52 +4903,52 @@
         <v>11</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF23" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH23" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AL23" t="n">
         <v>25</v>
       </c>
       <c r="AM23" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AN23" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AO23" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AP23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="AT23" t="n">
         <v>14.5</v>
@@ -4960,41 +4960,41 @@
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY23" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BB23" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD23" t="n">
         <v>18.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="BF23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BG23" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G24" t="n">
         <v>1.59</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I24" t="n">
         <v>7.6</v>
@@ -5049,7 +5049,7 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>1.33</v>
@@ -5058,19 +5058,19 @@
         <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
         <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V24" t="n">
         <v>1.15</v>
@@ -5082,28 +5082,28 @@
         <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z24" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA24" t="n">
-        <v>700</v>
+        <v>240</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE24" t="n">
         <v>120</v>
       </c>
       <c r="AF24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG24" t="n">
         <v>9.4</v>
@@ -5118,7 +5118,7 @@
         <v>14.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL24" t="n">
         <v>40</v>
@@ -5127,46 +5127,46 @@
         <v>180</v>
       </c>
       <c r="AN24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO24" t="n">
         <v>170</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>19</v>
       </c>
       <c r="AR24" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AS24" t="n">
         <v>18</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AV24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW24" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BB24" t="n">
         <v>13</v>
@@ -5181,14 +5181,14 @@
         <v>28</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5219,64 +5219,64 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G25" t="n">
         <v>1.98</v>
       </c>
-      <c r="G25" t="n">
-        <v>2.02</v>
-      </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
         <v>3.75</v>
       </c>
       <c r="L25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P25" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R25" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U25" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V25" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W25" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X25" t="n">
         <v>16</v>
       </c>
       <c r="Y25" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="Z25" t="n">
         <v>75</v>
@@ -5285,10 +5285,10 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD25" t="n">
         <v>1000</v>
@@ -5306,13 +5306,13 @@
         <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL25" t="n">
         <v>46</v>
@@ -5321,10 +5321,10 @@
         <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP25" t="n">
         <v>11</v>
@@ -5333,22 +5333,22 @@
         <v>14</v>
       </c>
       <c r="AR25" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV25" t="n">
         <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
@@ -5357,13 +5357,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB25" t="n">
         <v>12</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>11.5</v>
       </c>
       <c r="BC25" t="n">
         <v>18.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G26" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I26" t="n">
         <v>2.3</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.32</v>
       </c>
       <c r="J26" t="n">
         <v>3.4</v>
@@ -5431,37 +5431,37 @@
         <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N26" t="n">
         <v>3.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U26" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V26" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W26" t="n">
         <v>1.37</v>
@@ -5473,7 +5473,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z26" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA26" t="n">
         <v>32</v>
@@ -5485,28 +5485,28 @@
         <v>7.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE26" t="n">
         <v>27</v>
       </c>
       <c r="AF26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH26" t="n">
         <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ26" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK26" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL26" t="n">
         <v>65</v>
@@ -5524,10 +5524,10 @@
         <v>10</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS26" t="n">
         <v>28</v>
@@ -5542,16 +5542,16 @@
         <v>10.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY26" t="n">
         <v>14</v>
       </c>
       <c r="AZ26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA26" t="n">
         <v>40</v>
@@ -5563,7 +5563,7 @@
         <v>44</v>
       </c>
       <c r="BD26" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE26" t="n">
         <v>85</v>
@@ -5572,11 +5572,11 @@
         <v>55</v>
       </c>
       <c r="BG26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G27" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H27" t="n">
         <v>3</v>
@@ -5619,10 +5619,10 @@
         <v>3.05</v>
       </c>
       <c r="J27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.55</v>
       </c>
       <c r="L27" t="n">
         <v>1.41</v>
@@ -5631,19 +5631,19 @@
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
         <v>1.95</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
         <v>3.35</v>
@@ -5655,22 +5655,22 @@
         <v>2.28</v>
       </c>
       <c r="V27" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y27" t="n">
         <v>12.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB27" t="n">
         <v>12</v>
@@ -5712,10 +5712,10 @@
         <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>12</v>
@@ -5724,7 +5724,7 @@
         <v>19</v>
       </c>
       <c r="AS27" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT27" t="n">
         <v>11</v>
@@ -5751,7 +5751,7 @@
         <v>36</v>
       </c>
       <c r="BB27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC27" t="n">
         <v>24</v>
@@ -5763,14 +5763,14 @@
         <v>65</v>
       </c>
       <c r="BF27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG27" t="n">
         <v>26</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5804,19 +5804,19 @@
         <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H28" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="I28" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J28" t="n">
         <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
         <v>1.41</v>
@@ -5825,82 +5825,82 @@
         <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P28" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T28" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="U28" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V28" t="n">
         <v>1.7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X28" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y28" t="n">
         <v>11</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA28" t="n">
         <v>32</v>
       </c>
       <c r="AB28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF28" t="n">
         <v>22</v>
       </c>
       <c r="AG28" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH28" t="n">
         <v>17</v>
       </c>
       <c r="AI28" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ28" t="n">
         <v>60</v>
       </c>
       <c r="AK28" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL28" t="n">
         <v>48</v>
       </c>
       <c r="AM28" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN28" t="n">
         <v>38</v>
@@ -5912,13 +5912,13 @@
         <v>13</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR28" t="n">
         <v>14</v>
       </c>
       <c r="AS28" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AT28" t="n">
         <v>11.5</v>
@@ -5930,7 +5930,7 @@
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AX28" t="n">
         <v>19</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>5.9</v>
       </c>
       <c r="G29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="H29" t="n">
         <v>1.57</v>
@@ -6019,13 +6019,13 @@
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O29" t="n">
         <v>1.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
         <v>1.77</v>
@@ -6046,28 +6046,28 @@
         <v>2.46</v>
       </c>
       <c r="W29" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X29" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y29" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA29" t="n">
         <v>16</v>
       </c>
       <c r="AB29" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AC29" t="n">
         <v>10.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE29" t="n">
         <v>17.5</v>
@@ -6100,65 +6100,65 @@
         <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AP29" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>11</v>
+        <v>5.7</v>
       </c>
       <c r="AT29" t="n">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AW29" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="AX29" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG29" t="n">
         <v>7</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -6192,43 +6192,43 @@
         <v>1.25</v>
       </c>
       <c r="G30" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H30" t="n">
         <v>2.88</v>
       </c>
       <c r="I30" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="J30" t="n">
         <v>5.1</v>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O30" t="n">
         <v>1.18</v>
       </c>
       <c r="P30" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q30" t="n">
         <v>1.57</v>
       </c>
       <c r="R30" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S30" t="n">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -6240,10 +6240,10 @@
         <v>1.12</v>
       </c>
       <c r="W30" t="n">
-        <v>1.84</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y30" t="n">
         <v>1000</v>
@@ -6291,68 +6291,68 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -6386,58 +6386,58 @@
         <v>2.54</v>
       </c>
       <c r="G31" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H31" t="n">
         <v>3.3</v>
       </c>
       <c r="I31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J31" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K31" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="M31" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="O31" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="P31" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="T31" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="U31" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="V31" t="n">
         <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y31" t="n">
         <v>10.5</v>
@@ -6449,10 +6449,10 @@
         <v>900</v>
       </c>
       <c r="AB31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD31" t="n">
         <v>15.5</v>
@@ -6461,22 +6461,22 @@
         <v>130</v>
       </c>
       <c r="AF31" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>220</v>
+        <v>44</v>
       </c>
       <c r="AK31" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AL31" t="n">
         <v>460</v>
@@ -6491,19 +6491,19 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AR31" t="n">
         <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU31" t="n">
         <v>6</v>
@@ -6521,7 +6521,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="BA31" t="n">
         <v>50</v>
@@ -6533,20 +6533,20 @@
         <v>16</v>
       </c>
       <c r="BD31" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BF31" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG31" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H32" t="n">
         <v>2.82</v>
@@ -6589,19 +6589,19 @@
         <v>2.86</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L32" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M32" t="n">
         <v>1.12</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O32" t="n">
         <v>1.51</v>
@@ -6610,10 +6610,10 @@
         <v>1.59</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R32" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
         <v>5.3</v>
@@ -6628,19 +6628,19 @@
         <v>1.53</v>
       </c>
       <c r="W32" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X32" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y32" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z32" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AA32" t="n">
-        <v>280</v>
+        <v>48</v>
       </c>
       <c r="AB32" t="n">
         <v>9.199999999999999</v>
@@ -6649,13 +6649,13 @@
         <v>7</v>
       </c>
       <c r="AD32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE32" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AF32" t="n">
-        <v>46</v>
+        <v>18.5</v>
       </c>
       <c r="AG32" t="n">
         <v>14</v>
@@ -6664,25 +6664,25 @@
         <v>55</v>
       </c>
       <c r="AI32" t="n">
-        <v>380</v>
+        <v>65</v>
       </c>
       <c r="AJ32" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK32" t="n">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="AL32" t="n">
         <v>70</v>
       </c>
       <c r="AM32" t="n">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AN32" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP32" t="n">
         <v>8.199999999999999</v>
@@ -6694,53 +6694,53 @@
         <v>15</v>
       </c>
       <c r="AS32" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AT32" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AX32" t="n">
         <v>16.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ32" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BB32" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD32" t="n">
         <v>46</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>34</v>
       </c>
       <c r="BE32" t="n">
         <v>70</v>
       </c>
       <c r="BF32" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BG32" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
         <v>2.94</v>
       </c>
       <c r="L33" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="M33" t="n">
         <v>1.18</v>
@@ -6801,7 +6801,7 @@
         <v>1.79</v>
       </c>
       <c r="P33" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q33" t="n">
         <v>3.55</v>
@@ -6831,25 +6831,25 @@
         <v>7</v>
       </c>
       <c r="Z33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA33" t="n">
         <v>120</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC33" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE33" t="n">
         <v>130</v>
       </c>
       <c r="AF33" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AG33" t="n">
         <v>17.5</v>
@@ -6864,7 +6864,7 @@
         <v>160</v>
       </c>
       <c r="AK33" t="n">
-        <v>85</v>
+        <v>440</v>
       </c>
       <c r="AL33" t="n">
         <v>540</v>
@@ -6909,32 +6909,32 @@
         <v>15</v>
       </c>
       <c r="AZ33" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA33" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BB33" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BC33" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BD33" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BE33" t="n">
         <v>110</v>
       </c>
       <c r="BF33" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BG33" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -6965,19 +6965,19 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G34" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H34" t="n">
         <v>2.88</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2.86</v>
       </c>
       <c r="I34" t="n">
         <v>3.15</v>
       </c>
       <c r="J34" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K34" t="n">
         <v>3.5</v>
@@ -6992,37 +6992,37 @@
         <v>3.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P34" t="n">
         <v>1.74</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R34" t="n">
         <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T34" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U34" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="V34" t="n">
         <v>1.47</v>
       </c>
       <c r="W34" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X34" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z34" t="n">
         <v>22</v>
@@ -7037,10 +7037,10 @@
         <v>8.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF34" t="n">
         <v>17.5</v>
@@ -7055,10 +7055,10 @@
         <v>120</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
         <v>55</v>
@@ -7067,68 +7067,68 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO34" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP34" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ34" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AR34" t="n">
         <v>6</v>
       </c>
       <c r="AS34" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT34" t="n">
         <v>4.8</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AW34" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX34" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY34" t="n">
         <v>5.1</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB34" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB34" t="n">
-        <v>7</v>
-      </c>
       <c r="BC34" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG34" t="n">
         <v>7.2</v>
       </c>
-      <c r="BE34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>7</v>
-      </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -7159,13 +7159,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G35" t="n">
         <v>2.38</v>
       </c>
       <c r="H35" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I35" t="n">
         <v>4.1</v>
@@ -7183,31 +7183,31 @@
         <v>1.11</v>
       </c>
       <c r="N35" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O35" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P35" t="n">
         <v>1.59</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R35" t="n">
         <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T35" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U35" t="n">
         <v>1.7</v>
       </c>
       <c r="V35" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W35" t="n">
         <v>1.72</v>
@@ -7225,10 +7225,10 @@
         <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD35" t="n">
         <v>21</v>
@@ -7243,16 +7243,16 @@
         <v>14</v>
       </c>
       <c r="AH35" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
         <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK35" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AL35" t="n">
         <v>1000</v>
@@ -7261,7 +7261,7 @@
         <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AO35" t="n">
         <v>1000</v>
@@ -7273,10 +7273,10 @@
         <v>5.8</v>
       </c>
       <c r="AR35" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT35" t="n">
         <v>6.6</v>
@@ -7285,44 +7285,44 @@
         <v>6.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AX35" t="n">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AY35" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BB35" t="n">
-        <v>11.5</v>
+        <v>5.2</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BF35" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BG35" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="G36" t="n">
         <v>5.7</v>
@@ -7362,13 +7362,13 @@
         <v>1.89</v>
       </c>
       <c r="I36" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="J36" t="n">
         <v>3.4</v>
       </c>
       <c r="K36" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L36" t="n">
         <v>1.5</v>
@@ -7401,7 +7401,7 @@
         <v>1.8</v>
       </c>
       <c r="V36" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W36" t="n">
         <v>1.22</v>
@@ -7416,10 +7416,10 @@
         <v>12.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB36" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AC36" t="n">
         <v>1000</v>
@@ -7431,49 +7431,49 @@
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
         <v>55</v>
       </c>
-      <c r="AG36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>85</v>
-      </c>
       <c r="AP36" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AQ36" t="n">
         <v>6</v>
       </c>
       <c r="AR36" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AT36" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AU36" t="n">
         <v>7</v>
@@ -7482,41 +7482,41 @@
         <v>9</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AX36" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY36" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="BB36" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BC36" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BF36" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -7547,58 +7547,58 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="G37" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="H37" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I37" t="n">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K37" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="L37" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M37" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N37" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="R37" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="S37" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="U37" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="V37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W37" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -7613,7 +7613,7 @@
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC37" t="n">
         <v>1000</v>
@@ -7625,10 +7625,10 @@
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH37" t="n">
         <v>1000</v>
@@ -7637,7 +7637,7 @@
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK37" t="n">
         <v>1000</v>
@@ -7649,7 +7649,7 @@
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
@@ -7658,7 +7658,7 @@
         <v>6.2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR37" t="n">
         <v>4.2</v>
@@ -7673,7 +7673,7 @@
         <v>5.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AW37" t="n">
         <v>4.2</v>
@@ -7682,10 +7682,10 @@
         <v>4.4</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.73</v>
+        <v>7</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="BA37" t="n">
         <v>4.2</v>
@@ -7694,23 +7694,23 @@
         <v>6.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.82</v>
+        <v>5.3</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.85</v>
+        <v>2.56</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.88</v>
+        <v>2.56</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.98</v>
+        <v>3.8</v>
       </c>
       <c r="BG37" t="n">
         <v>4.2</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -7750,13 +7750,13 @@
         <v>2.68</v>
       </c>
       <c r="I38" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J38" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K38" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L38" t="n">
         <v>1.71</v>
@@ -7768,10 +7768,10 @@
         <v>2.32</v>
       </c>
       <c r="O38" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="P38" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q38" t="n">
         <v>3.3</v>
@@ -7780,7 +7780,7 @@
         <v>1.14</v>
       </c>
       <c r="S38" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="T38" t="n">
         <v>2.38</v>
@@ -7798,34 +7798,34 @@
         <v>7</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z38" t="n">
         <v>15.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="AB38" t="n">
         <v>8.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD38" t="n">
         <v>14.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF38" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AG38" t="n">
         <v>17</v>
       </c>
       <c r="AH38" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AI38" t="n">
         <v>240</v>
@@ -7834,19 +7834,19 @@
         <v>160</v>
       </c>
       <c r="AK38" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AL38" t="n">
-        <v>540</v>
+        <v>240</v>
       </c>
       <c r="AM38" t="n">
         <v>500</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO38" t="n">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="AP38" t="n">
         <v>6.2</v>
@@ -7870,16 +7870,16 @@
         <v>13</v>
       </c>
       <c r="AW38" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AX38" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY38" t="n">
         <v>15</v>
       </c>
       <c r="AZ38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA38" t="n">
         <v>38</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -7935,100 +7935,100 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="G39" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I39" t="n">
         <v>3.75</v>
       </c>
       <c r="J39" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="L39" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="M39" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="N39" t="n">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="O39" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="P39" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T39" t="n">
-        <v>2.16</v>
+        <v>1.03</v>
       </c>
       <c r="U39" t="n">
-        <v>1.71</v>
+        <v>1.03</v>
       </c>
       <c r="V39" t="n">
         <v>1.37</v>
       </c>
       <c r="W39" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X39" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y39" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z39" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC39" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD39" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG39" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH39" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI39" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK39" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL39" t="n">
         <v>1000</v>
@@ -8037,68 +8037,68 @@
         <v>1000</v>
       </c>
       <c r="AN39" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO39" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR39" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS39" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV39" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF39" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -8129,58 +8129,58 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="G40" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="H40" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I40" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="K40" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="L40" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M40" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N40" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O40" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="P40" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S40" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="U40" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="V40" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="W40" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8195,10 +8195,10 @@
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC40" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD40" t="n">
         <v>1000</v>
@@ -8207,10 +8207,10 @@
         <v>1000</v>
       </c>
       <c r="AF40" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG40" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH40" t="n">
         <v>1000</v>
@@ -8222,7 +8222,7 @@
         <v>1000</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL40" t="n">
         <v>1000</v>
@@ -8231,68 +8231,68 @@
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AQ40" t="n">
-        <v>13.5</v>
+        <v>5.3</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AS40" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="AT40" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AU40" t="n">
         <v>6.8</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AW40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC40" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX40" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD40" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.8</v>
+        <v>2.74</v>
       </c>
       <c r="BF40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BG40" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G41" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H41" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I41" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J41" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K41" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L41" t="n">
         <v>1.47</v>
@@ -8347,34 +8347,34 @@
         <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O41" t="n">
         <v>1.4</v>
       </c>
       <c r="P41" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q41" t="n">
         <v>2.2</v>
       </c>
       <c r="R41" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S41" t="n">
         <v>4.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U41" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V41" t="n">
         <v>1.2</v>
       </c>
       <c r="W41" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8431,62 +8431,62 @@
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ41" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ41" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AX41" t="n">
+      <c r="BA41" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BB41" t="n">
         <v>4.2</v>
       </c>
-      <c r="AY41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>3.2</v>
-      </c>
       <c r="BC41" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BD41" t="n">
-        <v>2.68</v>
+        <v>3.35</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="BF41" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BG41" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -8517,170 +8517,170 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="G42" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="H42" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="J42" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K42" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L42" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M42" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V42" t="n">
         <v>1.3</v>
       </c>
-      <c r="P42" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.22</v>
-      </c>
       <c r="W42" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="X42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH42" t="n">
         <v>21</v>
       </c>
-      <c r="Z42" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>22</v>
-      </c>
       <c r="AI42" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ42" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AK42" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AL42" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM42" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP42" t="n">
         <v>13</v>
       </c>
-      <c r="AO42" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV42" t="n">
         <v>14.5</v>
       </c>
-      <c r="AR42" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>17</v>
-      </c>
       <c r="AW42" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX42" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ42" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BB42" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BC42" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>26</v>
+        <v>4.7</v>
       </c>
       <c r="BE42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BF42" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -8711,16 +8711,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G43" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H43" t="n">
         <v>2.96</v>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>2.86</v>
@@ -8738,52 +8738,52 @@
         <v>2.62</v>
       </c>
       <c r="O43" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P43" t="n">
         <v>1.51</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R43" t="n">
         <v>1.18</v>
       </c>
       <c r="S43" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T43" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="U43" t="n">
-        <v>1.03</v>
+        <v>1.75</v>
       </c>
       <c r="V43" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W43" t="n">
         <v>1.48</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y43" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA43" t="n">
         <v>1000</v>
       </c>
       <c r="AB43" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD43" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE43" t="n">
         <v>1000</v>
@@ -8792,19 +8792,19 @@
         <v>1000</v>
       </c>
       <c r="AG43" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH43" t="n">
         <v>1000</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ43" t="n">
         <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL43" t="n">
         <v>1000</v>
@@ -8819,62 +8819,62 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -8905,25 +8905,25 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="G44" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H44" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I44" t="n">
         <v>11</v>
       </c>
       <c r="J44" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K44" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L44" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M44" t="n">
         <v>1.07</v>
@@ -8932,37 +8932,37 @@
         <v>3.6</v>
       </c>
       <c r="O44" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P44" t="n">
         <v>1.87</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R44" t="n">
         <v>1.32</v>
       </c>
       <c r="S44" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T44" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="U44" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="V44" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W44" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="X44" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Y44" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z44" t="n">
         <v>1000</v>
@@ -8974,7 +8974,7 @@
         <v>6.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD44" t="n">
         <v>1000</v>
@@ -8983,7 +8983,7 @@
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG44" t="n">
         <v>11</v>
@@ -8995,10 +8995,10 @@
         <v>1000</v>
       </c>
       <c r="AJ44" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL44" t="n">
         <v>1000</v>
@@ -9013,13 +9013,13 @@
         <v>1000</v>
       </c>
       <c r="AP44" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ44" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AS44" t="n">
         <v>55</v>
@@ -9028,7 +9028,7 @@
         <v>6</v>
       </c>
       <c r="AU44" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV44" t="n">
         <v>23</v>
@@ -9037,38 +9037,38 @@
         <v>46</v>
       </c>
       <c r="AX44" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY44" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ44" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BA44" t="n">
         <v>46</v>
       </c>
       <c r="BB44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC44" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD44" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE44" t="n">
         <v>50</v>
       </c>
       <c r="BF44" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG44" t="n">
         <v>55</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -9099,25 +9099,25 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G45" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H45" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I45" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J45" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K45" t="n">
         <v>4.8</v>
       </c>
       <c r="L45" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M45" t="n">
         <v>1.05</v>
@@ -9141,22 +9141,22 @@
         <v>3.15</v>
       </c>
       <c r="T45" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U45" t="n">
         <v>1.92</v>
       </c>
       <c r="V45" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W45" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="X45" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y45" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z45" t="n">
         <v>1000</v>
@@ -9189,7 +9189,7 @@
         <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK45" t="n">
         <v>16.5</v>
@@ -9201,22 +9201,22 @@
         <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO45" t="n">
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ45" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AR45" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS45" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AT45" t="n">
         <v>7.4</v>
@@ -9225,10 +9225,10 @@
         <v>8.6</v>
       </c>
       <c r="AV45" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW45" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AX45" t="n">
         <v>8</v>
@@ -9237,10 +9237,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ45" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BA45" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BB45" t="n">
         <v>12</v>
@@ -9249,20 +9249,20 @@
         <v>13.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE45" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF45" t="n">
         <v>7</v>
       </c>
       <c r="BG45" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -9293,28 +9293,28 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G46" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="H46" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I46" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J46" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="K46" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="L46" t="n">
         <v>1.77</v>
       </c>
       <c r="M46" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="N46" t="n">
         <v>2.18</v>
@@ -9323,10 +9323,10 @@
         <v>1.81</v>
       </c>
       <c r="P46" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R46" t="n">
         <v>1.12</v>
@@ -9335,64 +9335,64 @@
         <v>8.6</v>
       </c>
       <c r="T46" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U46" t="n">
         <v>1.56</v>
       </c>
       <c r="V46" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W46" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X46" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Y46" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA46" t="n">
         <v>1000</v>
       </c>
       <c r="AB46" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AC46" t="n">
         <v>7.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE46" t="n">
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AG46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH46" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AI46" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK46" t="n">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="AL46" t="n">
         <v>1000</v>
       </c>
       <c r="AM46" t="n">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="AN46" t="n">
         <v>1000</v>
@@ -9404,10 +9404,10 @@
         <v>5.8</v>
       </c>
       <c r="AQ46" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR46" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AS46" t="n">
         <v>40</v>
@@ -9416,31 +9416,31 @@
         <v>5.5</v>
       </c>
       <c r="AU46" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV46" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW46" t="n">
         <v>38</v>
       </c>
       <c r="AX46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY46" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BA46" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB46" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BC46" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD46" t="n">
         <v>40</v>
@@ -9449,14 +9449,14 @@
         <v>95</v>
       </c>
       <c r="BF46" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG46" t="n">
         <v>46</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>
@@ -9499,10 +9499,10 @@
         <v>6.2</v>
       </c>
       <c r="J47" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K47" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L47" t="n">
         <v>1.43</v>
@@ -9520,7 +9520,7 @@
         <v>1.9</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R47" t="n">
         <v>1.34</v>
@@ -9541,7 +9541,7 @@
         <v>2.32</v>
       </c>
       <c r="X47" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y47" t="n">
         <v>19</v>
@@ -9553,7 +9553,7 @@
         <v>190</v>
       </c>
       <c r="AB47" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC47" t="n">
         <v>9.199999999999999</v>
@@ -9604,7 +9604,7 @@
         <v>38</v>
       </c>
       <c r="AS47" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT47" t="n">
         <v>6.8</v>
@@ -9616,19 +9616,19 @@
         <v>19</v>
       </c>
       <c r="AW47" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX47" t="n">
         <v>8.4</v>
       </c>
       <c r="AY47" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ47" t="n">
         <v>18.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB47" t="n">
         <v>14.5</v>
@@ -9640,17 +9640,17 @@
         <v>32</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF47" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG47" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-20 01:57:39</t>
+          <t>2026-04-20 04:08:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH47"/>
+  <dimension ref="A1:BH48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
         <v>3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="M2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="O2" t="n">
         <v>1.52</v>
       </c>
       <c r="P2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.58</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.52</v>
       </c>
       <c r="W2" t="n">
         <v>1.45</v>
       </c>
       <c r="X2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK2" t="n">
         <v>48</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AL2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV2" t="n">
         <v>11</v>
       </c>
-      <c r="AC2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AW2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC2" t="n">
         <v>40</v>
       </c>
-      <c r="AF2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="BD2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF2" t="n">
         <v>21</v>
       </c>
-      <c r="AI2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="BG2" t="n">
         <v>34</v>
       </c>
-      <c r="AX2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>46</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>140</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>20</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>1.21</v>
       </c>
       <c r="G3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="H3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="J3" t="n">
         <v>6.6</v>
@@ -972,7 +972,7 @@
         <v>1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N3" t="n">
         <v>6</v>
@@ -993,16 +993,16 @@
         <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V3" t="n">
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1032,7 +1032,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
         <v>1000</v>
@@ -1041,10 +1041,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AK3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1053,46 +1053,46 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.4</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AV3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX3" t="n">
         <v>7.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>7.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BB3" t="n">
         <v>8</v>
@@ -1101,20 +1101,20 @@
         <v>11.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="BE3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BG3" t="n">
         <v>15</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K4" t="n">
         <v>5.5</v>
@@ -1175,16 +1175,16 @@
         <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
         <v>1.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T4" t="n">
         <v>1.93</v>
@@ -1193,122 +1193,122 @@
         <v>1.94</v>
       </c>
       <c r="V4" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W4" t="n">
         <v>3.25</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
         <v>32</v>
       </c>
       <c r="Z4" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA4" t="n">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE4" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK4" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AL4" t="n">
         <v>34</v>
       </c>
       <c r="AM4" t="n">
-        <v>390</v>
+        <v>130</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU4" t="n">
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AW4" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="I5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.35</v>
@@ -1363,40 +1363,40 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
         <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="V5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
         <v>90</v>
       </c>
       <c r="Y5" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
         <v>40</v>
@@ -1420,7 +1420,7 @@
         <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1447,7 +1447,7 @@
         <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>5.1</v>
@@ -1459,7 +1459,7 @@
         <v>5.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
@@ -1468,19 +1468,19 @@
         <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>4.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="BB5" t="n">
         <v>4.2</v>
@@ -1489,20 +1489,20 @@
         <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.58</v>
+        <v>19.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG5" t="n">
         <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
         <v>3.75</v>
@@ -1572,31 +1572,31 @@
         <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.89</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.96</v>
-      </c>
       <c r="X6" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
         <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
         <v>13.5</v>
@@ -1605,7 +1605,7 @@
         <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1626,7 +1626,7 @@
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
         <v>500</v>
@@ -1641,62 +1641,62 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
         <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="AT6" t="n">
         <v>7.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BA6" t="n">
         <v>11.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
         <v>10.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BG6" t="n">
         <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G7" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>3.6</v>
@@ -1748,7 +1748,7 @@
         <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
         <v>3.2</v>
@@ -1772,25 +1772,25 @@
         <v>2.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V7" t="n">
         <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="X7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y7" t="n">
         <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
         <v>7.6</v>
@@ -1799,7 +1799,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -1811,28 +1811,28 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
         <v>25</v>
       </c>
       <c r="AL7" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
         <v>9.4</v>
@@ -1844,10 +1844,10 @@
         <v>14.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU7" t="n">
         <v>7</v>
@@ -1856,41 +1856,41 @@
         <v>16.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AX7" t="n">
         <v>9.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
         <v>18.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
         <v>16.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
         <v>1.54</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K8" t="n">
         <v>5.8</v>
@@ -1942,43 +1942,43 @@
         <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O8" t="n">
         <v>1.15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T8" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,43 +1987,43 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC8" t="n">
         <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
         <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>8.6</v>
+        <v>5.2</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2032,37 +2032,37 @@
         <v>13.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
         <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
         <v>8.6</v>
@@ -2071,20 +2071,20 @@
         <v>7.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BE8" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.38</v>
       </c>
       <c r="G9" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
@@ -2139,55 +2139,55 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
         <v>1.89</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
         <v>32</v>
       </c>
       <c r="Y9" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>46</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
@@ -2223,62 +2223,62 @@
         <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AV9" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
         <v>22</v>
       </c>
       <c r="BC9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG9" t="n">
         <v>7.6</v>
       </c>
-      <c r="BD9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>25</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -2309,31 +2309,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="I10" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="L10" t="n">
         <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.24</v>
@@ -2345,49 +2345,49 @@
         <v>1.73</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
         <v>2.84</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="Y10" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z10" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z10" t="n">
-        <v>21</v>
-      </c>
       <c r="AA10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AB10" t="n">
         <v>500</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AG10" t="n">
         <v>100</v>
@@ -2396,49 +2396,49 @@
         <v>42</v>
       </c>
       <c r="AI10" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="n">
         <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
         <v>260</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>260</v>
       </c>
       <c r="AN10" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AP10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AR10" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX10" t="n">
         <v>16</v>
@@ -2447,32 +2447,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA10" t="n">
         <v>18</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="BC10" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="BD10" t="n">
         <v>23</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -2503,64 +2503,64 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="H11" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="R11" t="n">
         <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W11" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="X11" t="n">
         <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2572,31 +2572,31 @@
         <v>12</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
         <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AK11" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AL11" t="n">
         <v>32</v>
@@ -2605,19 +2605,19 @@
         <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
         <v>18</v>
       </c>
       <c r="AR11" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS11" t="n">
         <v>10</v>
@@ -2626,28 +2626,28 @@
         <v>9.4</v>
       </c>
       <c r="AU11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW11" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AV11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>40</v>
-      </c>
       <c r="AX11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY11" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY11" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC11" t="n">
         <v>12.5</v>
@@ -2659,14 +2659,14 @@
         <v>10</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
         <v>3.3</v>
@@ -2712,7 +2712,7 @@
         <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
         <v>1.37</v>
@@ -2721,7 +2721,7 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.25</v>
@@ -2757,7 +2757,7 @@
         <v>15.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
         <v>55</v>
@@ -2766,7 +2766,7 @@
         <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>13.5</v>
@@ -2778,13 +2778,13 @@
         <v>17</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH12" t="n">
         <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ12" t="n">
         <v>32</v>
@@ -2796,13 +2796,13 @@
         <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP12" t="n">
         <v>15.5</v>
@@ -2829,7 +2829,7 @@
         <v>30</v>
       </c>
       <c r="AX12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
@@ -2838,10 +2838,10 @@
         <v>12.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC12" t="n">
         <v>21</v>
@@ -2850,17 +2850,17 @@
         <v>29</v>
       </c>
       <c r="BE12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BF12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BG12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I13" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J13" t="n">
         <v>3.7</v>
@@ -2909,7 +2909,7 @@
         <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
@@ -2921,46 +2921,46 @@
         <v>1.29</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
         <v>1.87</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X13" t="n">
         <v>22</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
         <v>280</v>
       </c>
       <c r="AB13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD13" t="n">
         <v>13</v>
@@ -2969,7 +2969,7 @@
         <v>36</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AG13" t="n">
         <v>12.5</v>
@@ -2981,37 +2981,37 @@
         <v>95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="AK13" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="n">
         <v>95</v>
       </c>
       <c r="AM13" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN13" t="n">
         <v>42</v>
       </c>
       <c r="AO13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR13" t="n">
         <v>16.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU13" t="n">
         <v>7.2</v>
@@ -3020,16 +3020,16 @@
         <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
         <v>15.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA13" t="n">
         <v>32</v>
@@ -3038,30 +3038,30 @@
         <v>30</v>
       </c>
       <c r="BC13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE13" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BF13" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BG13" t="n">
         <v>20</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Danish Superliga</t>
+          <t>Norwegian 1st Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="S14" t="n">
-        <v>3.35</v>
+        <v>2.34</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="X14" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG14" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AH14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB14" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="BC14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD14" t="n">
         <v>13</v>
       </c>
-      <c r="AG14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>30</v>
-      </c>
       <c r="BE14" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="BF14" t="n">
-        <v>13</v>
+        <v>5.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>22</v>
+        <v>8.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Norwegian 1st Division</t>
+          <t>Danish Superliga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="G15" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="L15" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.66</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.56</v>
+        <v>1.94</v>
       </c>
       <c r="R15" t="n">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.42</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>2.32</v>
+        <v>1.88</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB15" t="n">
         <v>24</v>
       </c>
-      <c r="AC15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BC15" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="BE15" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="BG15" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -3482,13 +3482,13 @@
         <v>3.35</v>
       </c>
       <c r="I16" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>1.34</v>
@@ -3503,37 +3503,37 @@
         <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R16" t="n">
         <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U16" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
         <v>1.79</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y16" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AA16" t="n">
         <v>60</v>
@@ -3545,7 +3545,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
         <v>34</v>
@@ -3563,67 +3563,67 @@
         <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="AK16" t="n">
         <v>21</v>
       </c>
       <c r="AL16" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="AM16" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="n">
-        <v>36</v>
+        <v>13.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP16" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ16" t="n">
         <v>14.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AT16" t="n">
         <v>11.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
         <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="BB16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC16" t="n">
         <v>19</v>
       </c>
       <c r="BD16" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BE16" t="n">
         <v>21</v>
@@ -3632,11 +3632,11 @@
         <v>12</v>
       </c>
       <c r="BG16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
         <v>2.62</v>
@@ -3679,7 +3679,7 @@
         <v>2.7</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
         <v>3.55</v>
@@ -3691,46 +3691,46 @@
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
         <v>1.3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
         <v>1.7</v>
       </c>
       <c r="U17" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X17" t="n">
         <v>15</v>
       </c>
       <c r="Y17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AB17" t="n">
         <v>13</v>
@@ -3739,16 +3739,16 @@
         <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
         <v>28</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
         <v>16</v>
@@ -3757,16 +3757,16 @@
         <v>38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>85</v>
       </c>
       <c r="AN17" t="n">
         <v>28</v>
@@ -3775,28 +3775,28 @@
         <v>22</v>
       </c>
       <c r="AP17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
         <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX17" t="n">
         <v>18.5</v>
@@ -3808,29 +3808,29 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB17" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="BC17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD17" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BE17" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BF17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BG17" t="n">
         <v>19</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-20 04:08:36</t>
+          <t>2026-04-20 06:19:34</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="I18" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="J18" t="n">
         <v>4</v>
@@ -3885,7 +3885,7 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.26</v>
@@ -3897,19 +3897,19 @@
         <v>1.78</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="U18" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="W18" t="n">
         <v>1.25</v>
@@ -3942,7 +3942,7 @@
         <v>40</v>
       </c>
       <c r="AG18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH18" t="n">
         <v>19</v>
@@ -3963,7 +3963,7 @@
         <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>140</v>
+        <v>290</v>
       </c>
       <c r="AO18" t="n">
         <v>10.5</v>
@@ -3972,7 +3972,7 @@
         <v>17</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v